--- a/AAII_Financials/Quarterly/FAF_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FAF_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="92">
   <si>
     <t>FAF</t>
   </si>
@@ -656,232 +656,238 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1432400</v>
+      </c>
+      <c r="E8" s="3">
         <v>1620000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1643600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1462500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1715000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1975000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2139000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2105000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2533100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2555900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2266400</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2025700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2151300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1913700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1608700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1412900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1728700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1671200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1498600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1303600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1417100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1542200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1491200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1297400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1481300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1519600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1454400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1317000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1504300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1508300</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -972,8 +978,11 @@
       <c r="AF9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1064,8 +1073,11 @@
       <c r="AF10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1098,8 +1110,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1190,8 +1203,11 @@
       <c r="AF12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,8 +1298,11 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1296,11 +1315,11 @@
       <c r="F14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>5</v>
+      <c r="G14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="3">
+        <v>0</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>5</v>
@@ -1308,27 +1327,27 @@
       <c r="J14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>5</v>
+      <c r="M14" s="3">
+        <v>0</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P14" s="3">
         <v>-18300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>73300</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1344,8 +1363,8 @@
       <c r="V14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="X14" s="3">
         <v>0</v>
@@ -1374,100 +1393,106 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>49600</v>
+      </c>
+      <c r="E15" s="3">
         <v>47300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>46100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>45500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>43000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>41000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>42000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>41000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>39500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>39200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>40900</v>
-      </c>
-      <c r="N15" s="3">
-        <v>38300</v>
       </c>
       <c r="O15" s="3">
         <v>38300</v>
       </c>
       <c r="P15" s="3">
+        <v>38300</v>
+      </c>
+      <c r="Q15" s="3">
         <v>38200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>41000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>31400</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>31500</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>31700</v>
-      </c>
-      <c r="U15" s="3">
-        <v>32900</v>
       </c>
       <c r="V15" s="3">
         <v>32900</v>
       </c>
       <c r="W15" s="3">
+        <v>32900</v>
+      </c>
+      <c r="X15" s="3">
         <v>33400</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>31700</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>31100</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>29700</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>31800</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>36000</v>
-      </c>
-      <c r="AC15" s="3">
-        <v>30100</v>
       </c>
       <c r="AD15" s="3">
         <v>30100</v>
       </c>
       <c r="AE15" s="3">
+        <v>30100</v>
+      </c>
+      <c r="AF15" s="3">
         <v>28100</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>24500</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1522,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1357600</v>
+      </c>
+      <c r="E17" s="3">
         <v>1447100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1434500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1357400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1597000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1803000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1902000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1884000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2019500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1933500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1850700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1703200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1753000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1654400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1370000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1328500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1428400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1413600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1257200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1150000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1287200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1335800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1279200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1195100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1312800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1492500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1261300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1224400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1414000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1333600</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>74800</v>
+      </c>
+      <c r="E18" s="3">
         <v>172900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>209100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>105100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>118000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>172000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>237000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>221000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>513600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>622400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>415700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>322500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>398300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>259300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>238700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>84400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>300300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>257600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>241400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>153600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>129900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>206400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>212000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>102300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>168500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>27100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>193100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>92600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>90300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>174700</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,38 +1747,39 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-138800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>3300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-16400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-30000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-151000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-77000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-71000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-160100</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
         <v>0</v>
       </c>
@@ -1807,376 +1840,391 @@
       <c r="AF20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>121300</v>
+      </c>
+      <c r="E21" s="3">
         <v>81400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>258500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>134200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>131000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>62000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>202000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>191000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>393000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>661600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>456600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>360800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>436600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>297600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>279700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>115900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>331700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>289300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>274300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>186500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>163300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>238100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>243000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>132000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>200300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>63100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>223300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>122700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>118400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>199300</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>33300</v>
+      </c>
+      <c r="E22" s="3">
         <v>35800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>34300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>29100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>30000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>24000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>19000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>20000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>20100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>19200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>16200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>16500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>15900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>16000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>13400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>12100</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>11700</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>12200</v>
-      </c>
-      <c r="U22" s="3">
-        <v>11900</v>
       </c>
       <c r="V22" s="3">
         <v>11900</v>
       </c>
       <c r="W22" s="3">
+        <v>11900</v>
+      </c>
+      <c r="X22" s="3">
         <v>11000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>10800</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>10000</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>9200</v>
       </c>
       <c r="AA22" s="3">
         <v>9200</v>
       </c>
       <c r="AB22" s="3">
+        <v>9200</v>
+      </c>
+      <c r="AC22" s="3">
         <v>9100</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>9000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>8700</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>8800</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>7800</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>38400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-1700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>178100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>59600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>58000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-3000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>141000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>130000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>333400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>603200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>399400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>306000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>382300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>243400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>225300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>72300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>288500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>245300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>229500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>141700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>118900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>195600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>202000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>93100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>159300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>18000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>184200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>83900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>81500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>166900</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E24" s="3">
         <v>-500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>41700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>13600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>4000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-6000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>31000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>32000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>72700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>152700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>96000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>71600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>100900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>59800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>53600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>8500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>63900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>57200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>42200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>31900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>25700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>44100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>46900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>16900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>52700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-3200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>62300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>25800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>59500</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2315,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>34300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-1200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>136400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>46000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>54000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>110000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>98000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>260700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>450500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>303400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>234500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>281400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>183600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>171700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>63800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>224600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>188200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>187300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>109800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>93200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>151500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>155100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>76200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>106600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>21200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>121900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>58100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>81000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>107400</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>34100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>138500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>45900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>54000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>2000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>109000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>98000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>259800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>445300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>302300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>233600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>280300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>182300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>170700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>63200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>224000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>187200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>186700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>109600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>91600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>151500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>155100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>76200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>107000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>21400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>122300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>58300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>81000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>107300</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2600,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2599,8 +2659,8 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>5</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>5</v>
@@ -2617,12 +2677,12 @@
       <c r="Z29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB29" s="3">
         <v>114100</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AC29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2635,8 +2695,11 @@
       <c r="AF29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2790,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,38 +2885,41 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>3100</v>
+      </c>
+      <c r="E32" s="3">
         <v>138800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-3300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>16400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>30000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>151000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>77000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>71000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>160100</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
         <v>0</v>
       </c>
@@ -2911,100 +2980,106 @@
       <c r="AF32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>34100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-1700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>138500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>45900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>54000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>2000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>109000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>98000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>259800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>445300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>302300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>233600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>280300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>182300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>170700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>63200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>224000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>187200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>186700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>109600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>91600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>151500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>155100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>76200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>221100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>21400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>122300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>58300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>81000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>107300</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3170,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>34100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-1700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>138500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>45900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>54000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>2000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>109000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>98000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>259800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>445300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>302300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>233600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>280300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>182300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>170700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>63200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>224000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>187200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>186700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>109600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>91600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>151500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>155100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>76200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>221100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>21400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>122300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>58300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>81000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>107300</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3402,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,100 +3437,104 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3605300</v>
+      </c>
+      <c r="E41" s="3">
         <v>1579100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2245900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1983400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1224000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2361000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1745000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1704000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1228000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1954000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2222700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2026000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1275500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1512400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1523300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1050000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1486000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1711000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1412000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1337100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1467100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>2205300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1226500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1176600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1387200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1141900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1166800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1047500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1006100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1443300</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3536,8 +3625,11 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3628,8 +3720,11 @@
       <c r="AF43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3720,8 +3815,11 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3812,8 +3910,11 @@
       <c r="AF45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -3904,284 +4005,296 @@
       <c r="AF46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>9170500</v>
+      </c>
+      <c r="E47" s="3">
         <v>9068800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>9484400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>9432400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>9799000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>10234000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>10657000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>11249000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>11613000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>11450200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>9954100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>9253100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>8349200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>7823500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>7593200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>7445500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>7212300</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>7277700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>7200600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>6991800</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>6638500</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>6637000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>6196700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>5893500</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>5728100</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>5743600</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>5789900</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>5493600</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>5508500</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>5489500</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>978900</v>
+      </c>
+      <c r="E48" s="3">
         <v>967900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>943600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>907000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>885000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>851000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>824000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>766000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>755000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>716200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>705300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>700400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>715000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>714800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>741000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>783900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>738200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>740300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>756400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>767600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>457800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>457500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>446300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>435900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>439600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>438100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>433000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>429000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>434100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>430600</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1961300</v>
+      </c>
+      <c r="E49" s="3">
         <v>1962500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1976700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1990300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1992000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2016000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2023000</v>
-      </c>
-      <c r="J49" s="3">
-        <v>1806000</v>
       </c>
       <c r="K49" s="3">
         <v>1806000</v>
       </c>
       <c r="L49" s="3">
+        <v>1806000</v>
+      </c>
+      <c r="M49" s="3">
         <v>1604900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1556000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1558200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1573100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1552000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1591900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1565500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1242700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1242600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1246700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1247800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1253500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1256700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1271200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1229400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1212900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1220600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1109800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1095800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1096300</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1066200</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4385,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,13 +4480,16 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>54500</v>
+        <v>50100</v>
       </c>
       <c r="E52" s="3">
         <v>54500</v>
@@ -4379,10 +4498,10 @@
         <v>54500</v>
       </c>
       <c r="G52" s="3">
+        <v>54500</v>
+      </c>
+      <c r="H52" s="3">
         <v>54000</v>
-      </c>
-      <c r="H52" s="3">
-        <v>14000</v>
       </c>
       <c r="I52" s="3">
         <v>14000</v>
@@ -4394,7 +4513,7 @@
         <v>14000</v>
       </c>
       <c r="L52" s="3">
-        <v>14500</v>
+        <v>14000</v>
       </c>
       <c r="M52" s="3">
         <v>14500</v>
@@ -4406,10 +4525,10 @@
         <v>14500</v>
       </c>
       <c r="P52" s="3">
+        <v>14500</v>
+      </c>
+      <c r="Q52" s="3">
         <v>216600</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>18300</v>
       </c>
       <c r="R52" s="3">
         <v>18300</v>
@@ -4418,7 +4537,7 @@
         <v>18300</v>
       </c>
       <c r="T52" s="3">
-        <v>16600</v>
+        <v>18300</v>
       </c>
       <c r="U52" s="3">
         <v>16600</v>
@@ -4430,7 +4549,7 @@
         <v>16600</v>
       </c>
       <c r="X52" s="3">
-        <v>22800</v>
+        <v>16600</v>
       </c>
       <c r="Y52" s="3">
         <v>22800</v>
@@ -4442,7 +4561,7 @@
         <v>22800</v>
       </c>
       <c r="AB52" s="3">
-        <v>20000</v>
+        <v>22800</v>
       </c>
       <c r="AC52" s="3">
         <v>20000</v>
@@ -4454,10 +4573,13 @@
         <v>20000</v>
       </c>
       <c r="AF52" s="3">
+        <v>20000</v>
+      </c>
+      <c r="AG52" s="3">
         <v>22000</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4670,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>16802800</v>
+      </c>
+      <c r="E54" s="3">
         <v>14677600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>15730900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>15383500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>14955000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>16486000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>16262000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>16527000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>16451000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>16686100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>15426900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>14431900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>12796000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>12638800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>12288000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>11675500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>11519200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>11804100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>11443200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>11160300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>10630600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>11380100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>9959400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>9546800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>9573200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>9347000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>9314300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>8874400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>8831800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>9246500</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4802,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,100 +4837,104 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>879500</v>
+      </c>
+      <c r="E57" s="3">
         <v>810900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>789700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>720500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>915000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1115000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1015000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1051000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1262000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1252000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1070800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1113400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>979700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>830100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>781500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>664000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>820400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>812500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>709300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>631500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>778700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>826700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>770700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>709600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>793200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>741600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>697000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>675800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>794000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>813900</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4892,100 +5025,106 @@
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>8852900</v>
+      </c>
+      <c r="E59" s="3">
         <v>7175600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>7963300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>7783800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>7124000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>8324000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>7723000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>7346000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>6651000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>7043200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>6920600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>6154000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>4804500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4918800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4925200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>4850100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>4748700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>5305000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>5265900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>5344000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>4837900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>5581000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>4326100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>4187700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>4104100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>4079900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>4208900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>3926300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>3815700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>4302200</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5076,105 +5215,111 @@
       <c r="AF60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1947200</v>
+      </c>
+      <c r="E61" s="3">
         <v>1922600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1979000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1897400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2012000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1988000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2075000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2205000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2186000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2242500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1619200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1655000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1526900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1538300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1489200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1288800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1006600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>961800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>919700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>858600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>808300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>821800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>832600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>731500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>732800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>734100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>734500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>735500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>736700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>737900</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>18800</v>
+        <v>63600</v>
       </c>
       <c r="E62" s="3">
         <v>18800</v>
@@ -5183,22 +5328,22 @@
         <v>18800</v>
       </c>
       <c r="G62" s="3">
+        <v>18800</v>
+      </c>
+      <c r="H62" s="3">
         <v>19000</v>
-      </c>
-      <c r="H62" s="3">
-        <v>314000</v>
       </c>
       <c r="I62" s="3">
         <v>314000</v>
       </c>
       <c r="J62" s="3">
-        <v>345000</v>
+        <v>314000</v>
       </c>
       <c r="K62" s="3">
         <v>345000</v>
       </c>
       <c r="L62" s="3">
-        <v>291200</v>
+        <v>345000</v>
       </c>
       <c r="M62" s="3">
         <v>291200</v>
@@ -5210,10 +5355,10 @@
         <v>291200</v>
       </c>
       <c r="P62" s="3">
+        <v>291200</v>
+      </c>
+      <c r="Q62" s="3">
         <v>414400</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>266100</v>
       </c>
       <c r="R62" s="3">
         <v>266100</v>
@@ -5222,7 +5367,7 @@
         <v>266100</v>
       </c>
       <c r="T62" s="3">
-        <v>217100</v>
+        <v>266100</v>
       </c>
       <c r="U62" s="3">
         <v>217100</v>
@@ -5234,7 +5379,7 @@
         <v>217100</v>
       </c>
       <c r="X62" s="3">
-        <v>219300</v>
+        <v>217100</v>
       </c>
       <c r="Y62" s="3">
         <v>219300</v>
@@ -5246,7 +5391,7 @@
         <v>219300</v>
       </c>
       <c r="AB62" s="3">
-        <v>242200</v>
+        <v>219300</v>
       </c>
       <c r="AC62" s="3">
         <v>242200</v>
@@ -5258,10 +5403,13 @@
         <v>242200</v>
       </c>
       <c r="AF62" s="3">
+        <v>242200</v>
+      </c>
+      <c r="AG62" s="3">
         <v>133100</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5500,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5595,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,100 +5690,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>11954700</v>
+      </c>
+      <c r="E66" s="3">
         <v>10150400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>10958500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>10627000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>10290000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>11978000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>11346000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>11164000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>10684000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>11088900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>10163100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>9476600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>7886000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>7915000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>7722600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>7316100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>7098700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>7562000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>7358300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>7282200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>6888800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>7705900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>6389900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>6076300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>6093300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>6053200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>6120900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>5802000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>5823600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>6224200</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5822,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5915,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6010,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6105,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,100 +6200,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3710600</v>
+      </c>
+      <c r="E72" s="3">
         <v>3739000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>3796200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3712300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3721000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>3722000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>3775000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>3721000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>3680000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>3476900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>3088600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2837200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2655500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2426900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2294600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2173700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2161000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>1985100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>1845900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>1707100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>1644200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>1600300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1496600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1384700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1311100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1129000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1150600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>1066700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1046800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>1012500</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6390,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6485,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6580,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4848100</v>
+      </c>
+      <c r="E76" s="3">
         <v>4527200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4772400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4756500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4665000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4508000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4916000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>5363000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5767000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5597100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5263700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4955300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4910000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4723800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4565400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>4359300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>4420500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>4242100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>4084900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>3878000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>3741900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>3674200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>3569500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>3470500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>3480000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>3293900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>3193400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>3072500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>3008200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>3022300</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6770,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>34100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-1700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>138500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>45900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>54000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>2000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>109000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>98000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>259800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>445300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>302300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>233600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>280300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>182300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>170700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>63200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>224000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>187200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>186700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>109600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>91600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>151500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>155100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>76200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>221100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>21400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>122300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>58300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>81000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>107300</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,100 +7002,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>49600</v>
+      </c>
+      <c r="E83" s="3">
         <v>47300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>46100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>45500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>43000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>41000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>42000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>41000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>39500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>39200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>40900</v>
-      </c>
-      <c r="N83" s="3">
-        <v>38300</v>
       </c>
       <c r="O83" s="3">
         <v>38300</v>
       </c>
       <c r="P83" s="3">
+        <v>38300</v>
+      </c>
+      <c r="Q83" s="3">
         <v>38200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>41000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>31400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>31500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>31700</v>
-      </c>
-      <c r="U83" s="3">
-        <v>32900</v>
       </c>
       <c r="V83" s="3">
         <v>32900</v>
       </c>
       <c r="W83" s="3">
+        <v>32900</v>
+      </c>
+      <c r="X83" s="3">
         <v>33400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>31700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>31100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>29700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>31800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>36000</v>
-      </c>
-      <c r="AC83" s="3">
-        <v>30100</v>
       </c>
       <c r="AD83" s="3">
         <v>30100</v>
       </c>
       <c r="AE83" s="3">
+        <v>30100</v>
+      </c>
+      <c r="AF83" s="3">
         <v>28100</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>24500</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7190,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7285,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7380,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7475,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7570,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-41700</v>
+      </c>
+      <c r="E89" s="3">
         <v>219300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>269000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-92300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>247000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>304000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>189000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>40000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>344000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>399000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>253100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>223900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>425200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>291500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>343800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>24200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>301400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>310600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>266600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>34500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>308300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>230800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>210900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>43200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>176600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>220900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>228500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>6100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>237200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>105800</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,100 +7702,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-58100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-65800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-76400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-63100</v>
-      </c>
-      <c r="G91" s="3">
-        <v>-71000</v>
       </c>
       <c r="H91" s="3">
         <v>-71000</v>
       </c>
       <c r="I91" s="3">
+        <v>-71000</v>
+      </c>
+      <c r="J91" s="3">
         <v>-75000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-43000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-49900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-43500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-39000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-28600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-22500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-33600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-28800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-29200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-28800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-24200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-26600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-27400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-30900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-31600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-33400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-22300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-31100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-33500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-39700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-29900</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-28500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-42800</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7890,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,100 +7985,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>414700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-61100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-181000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>426900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-140000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-62000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-86000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-107000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-565000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1296100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-752600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-779300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-319500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-390100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-12700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-692800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-27200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-57700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-76700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-290600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-205900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-446800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-279300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-288700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>5000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-76400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-292000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-23700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-194200</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-145100</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,100 +8117,104 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-54500</v>
+      </c>
+      <c r="E96" s="3">
         <v>-54700</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-53600</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-53800</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-53000</v>
-      </c>
-      <c r="H96" s="3">
-        <v>-54000</v>
       </c>
       <c r="I96" s="3">
         <v>-54000</v>
       </c>
       <c r="J96" s="3">
+        <v>-54000</v>
+      </c>
+      <c r="K96" s="3">
         <v>-56000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-55900</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-56000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-50100</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-51000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-50900</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-49100</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-49000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-49700</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-47200</v>
-      </c>
-      <c r="T96" s="3">
-        <v>-47100</v>
       </c>
       <c r="U96" s="3">
         <v>-47100</v>
       </c>
       <c r="V96" s="3">
+        <v>-47100</v>
+      </c>
+      <c r="W96" s="3">
         <v>-47000</v>
-      </c>
-      <c r="W96" s="3">
-        <v>-46900</v>
       </c>
       <c r="X96" s="3">
         <v>-46900</v>
       </c>
       <c r="Y96" s="3">
+        <v>-46900</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-42400</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-42300</v>
-      </c>
-      <c r="AA96" s="3">
-        <v>-42100</v>
       </c>
       <c r="AB96" s="3">
         <v>-42100</v>
       </c>
       <c r="AC96" s="3">
+        <v>-42100</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-37600</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-37500</v>
-      </c>
-      <c r="AE96" s="3">
-        <v>-37300</v>
       </c>
       <c r="AF96" s="3">
         <v>-37300</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>-37300</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8305,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8400,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,280 +8495,292 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1648000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-820000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>171400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>423700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1250000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>385000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-54000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>543000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-507400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>634100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>694200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1305100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-351800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>83300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>137800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>244600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-503200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>49600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-115400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>124000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-836700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>1197000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>120500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>33900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>63100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-172600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>179800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>57700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-475400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>241200</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E101" s="3">
         <v>-5000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>3100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>1600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>6000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-11000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-8000</v>
       </c>
-      <c r="J101" s="3">
-        <v>0</v>
-      </c>
       <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3">
         <v>2800</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-5600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>2000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>9200</v>
-      </c>
-      <c r="P101" s="3">
-        <v>4400</v>
       </c>
       <c r="Q101" s="3">
         <v>4400</v>
       </c>
       <c r="R101" s="3">
+        <v>4400</v>
+      </c>
+      <c r="S101" s="3">
         <v>-11900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>4000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-3400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>2000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-3900</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-2200</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>1000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>600</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>3300</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>3000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>1300</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-4800</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2026200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-666800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>262500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>759900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1137000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>616000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>41000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>476000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-725500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-268700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>196700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>750600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-236900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-11000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>473400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-436000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-225000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>299000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>74900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-130100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-738200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>978800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>49900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-210600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>245300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-24800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>119300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>41300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-437200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>201500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FAF_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FAF_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="92">
   <si>
     <t>FAF</t>
   </si>
@@ -656,238 +656,245 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1435600</v>
+      </c>
+      <c r="E8" s="3">
         <v>1432400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1620000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1643600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1462500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1715000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1975000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2139000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2105000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2533100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2555900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2266400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2025700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2151300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1913700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1608700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1412900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1728700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1671200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1498600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1303600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1417100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1542200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1491200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1297400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1481300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1519600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1454400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1317000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1504300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1508300</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -981,8 +988,11 @@
       <c r="AG9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1076,8 +1086,11 @@
       <c r="AG10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1111,8 +1124,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1206,8 +1220,11 @@
       <c r="AG12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1301,56 +1318,59 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>5</v>
+      <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
+        <v>0</v>
       </c>
       <c r="H14" s="3">
         <v>0</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>5</v>
+      <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
+        <v>0</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>5</v>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P14" s="3">
+      <c r="P14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-18300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>73300</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="S14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1366,8 +1386,8 @@
       <c r="W14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
@@ -1396,103 +1416,109 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>50100</v>
+      </c>
+      <c r="E15" s="3">
         <v>49600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>47300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>46100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>45500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>43000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>41000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>42000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>41000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>39500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>39200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>40900</v>
-      </c>
-      <c r="O15" s="3">
-        <v>38300</v>
       </c>
       <c r="P15" s="3">
         <v>38300</v>
       </c>
       <c r="Q15" s="3">
+        <v>38300</v>
+      </c>
+      <c r="R15" s="3">
         <v>38200</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>41000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>31400</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>31500</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>31700</v>
-      </c>
-      <c r="V15" s="3">
-        <v>32900</v>
       </c>
       <c r="W15" s="3">
         <v>32900</v>
       </c>
       <c r="X15" s="3">
+        <v>32900</v>
+      </c>
+      <c r="Y15" s="3">
         <v>33400</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>31700</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>31100</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>29700</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>31800</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>36000</v>
-      </c>
-      <c r="AD15" s="3">
-        <v>30100</v>
       </c>
       <c r="AE15" s="3">
         <v>30100</v>
       </c>
       <c r="AF15" s="3">
+        <v>30100</v>
+      </c>
+      <c r="AG15" s="3">
         <v>28100</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>24500</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1523,198 +1549,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1332000</v>
+      </c>
+      <c r="E17" s="3">
         <v>1357600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1447100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1434500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1357400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1597000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1803000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1902000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1884000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2019500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1933500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1850700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1703200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1753000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1654400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1370000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1328500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1428400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1413600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1257200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1150000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1287200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1335800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1279200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1195100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1312800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1492500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1261300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1224400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1414000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1333600</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>103600</v>
+      </c>
+      <c r="E18" s="3">
         <v>74800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>172900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>209100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>105100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>118000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>172000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>237000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>221000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>513600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>622400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>415700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>322500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>398300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>259300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>238700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>84400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>300300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>257600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>241400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>153600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>129900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>206400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>212000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>102300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>168500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>27100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>193100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>92600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>90300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>174700</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1748,41 +1781,42 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-3100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-138800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>3300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-16400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-30000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-151000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-77000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-71000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-160100</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
         <v>0</v>
       </c>
@@ -1843,388 +1877,403 @@
       <c r="AG20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>142700</v>
+      </c>
+      <c r="E21" s="3">
         <v>121300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>81400</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>258500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>134200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>131000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>62000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>202000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>191000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>393000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>661600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>456600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>360800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>436600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>297600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>279700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>115900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>331700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>289300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>274300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>186500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>163300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>238100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>243000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>132000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>200300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>63100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>223300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>122700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>118400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>199300</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>34300</v>
+      </c>
+      <c r="E22" s="3">
         <v>33300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>35800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>34300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>29100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>30000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>24000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>19000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>20000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>20100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>19200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>16200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>16500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>15900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>16000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>13400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>12100</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>11700</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>12200</v>
-      </c>
-      <c r="V22" s="3">
-        <v>11900</v>
       </c>
       <c r="W22" s="3">
         <v>11900</v>
       </c>
       <c r="X22" s="3">
+        <v>11900</v>
+      </c>
+      <c r="Y22" s="3">
         <v>11000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>10800</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>10000</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>9200</v>
       </c>
       <c r="AB22" s="3">
         <v>9200</v>
       </c>
       <c r="AC22" s="3">
+        <v>9200</v>
+      </c>
+      <c r="AD22" s="3">
         <v>9100</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>9000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>8700</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>8800</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>7800</v>
       </c>
     </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>58300</v>
+      </c>
+      <c r="E23" s="3">
         <v>38400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-1700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>178100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>59600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>58000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-3000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>141000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>130000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>333400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>603200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>399400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>306000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>382300</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>243400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>225300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>72300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>288500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>245300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>229500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>141700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>118900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>195600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>202000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>93100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>159300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>18000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>184200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>83900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>81500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>166900</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>11600</v>
+      </c>
+      <c r="E24" s="3">
         <v>4100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>41700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>13600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>4000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-6000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>31000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>32000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>72700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>152700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>96000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>71600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>100900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>59800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>53600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>8500</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>63900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>57200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>42200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>31900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>25700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>44100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>46900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>16900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>52700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-3200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>62300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>25800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>500</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>59500</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2318,198 +2367,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>46700</v>
+      </c>
+      <c r="E26" s="3">
         <v>34300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-1200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>136400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>46000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>54000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>3000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>110000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>98000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>260700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>450500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>303400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>234500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>281400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>183600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>171700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>63800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>224600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>188200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>187300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>109800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>93200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>151500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>155100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>76200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>106600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>21200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>121900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>58100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>81000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>107400</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>46700</v>
+      </c>
+      <c r="E27" s="3">
         <v>34100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>138500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>45900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>54000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>109000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>98000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>259800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>445300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>302300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>233600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>280300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>182300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>170700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>63200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>224000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>187200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>186700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>109600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>91600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>151500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>155100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>76200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>107000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>21400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>122300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>58300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>81000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>107300</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2603,8 +2661,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2662,8 +2723,8 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>5</v>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>5</v>
@@ -2680,12 +2741,12 @@
       <c r="AA29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AC29" s="3">
         <v>114100</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AD29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2698,8 +2759,11 @@
       <c r="AG29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2793,8 +2857,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2888,41 +2955,44 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>11000</v>
+      </c>
+      <c r="E32" s="3">
         <v>3100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>138800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-3300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>16400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>30000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>151000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>77000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>71000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>160100</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
         <v>0</v>
       </c>
@@ -2983,103 +3053,109 @@
       <c r="AG32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>46700</v>
+      </c>
+      <c r="E33" s="3">
         <v>34100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-1700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>138500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>45900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>54000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>109000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>98000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>259800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>445300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>302300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>233600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>280300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>182300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>170700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>63200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>224000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>187200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>186700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>109600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>91600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>151500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>155100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>76200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>221100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>21400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>122300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>58300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>81000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>107300</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3173,203 +3249,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>46700</v>
+      </c>
+      <c r="E35" s="3">
         <v>34100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-1700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>138500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>45900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>54000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>109000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>98000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>259800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>445300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>302300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>233600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>280300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>182300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>170700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>63200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>224000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>187200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>186700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>109600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>91600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>151500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>155100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>76200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>221100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>21400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>122300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>58300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>81000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>107300</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3403,8 +3488,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3438,103 +3524,107 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1506400</v>
+      </c>
+      <c r="E41" s="3">
         <v>3605300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1579100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2245900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1983400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1224000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2361000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1745000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1704000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1228000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1954000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2222700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2026000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1275500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1512400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1523300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1050000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1486000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1711000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1412000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1337100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1467100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>2205300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1226500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1176600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1387200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1141900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1166800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1047500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1006100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1443300</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3628,8 +3718,11 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3723,8 +3816,11 @@
       <c r="AG43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3818,8 +3914,11 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3913,8 +4012,11 @@
       <c r="AG45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -4008,293 +4110,305 @@
       <c r="AG46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>9132700</v>
+      </c>
+      <c r="E47" s="3">
         <v>9170500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>9068800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>9484400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>9432400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>9799000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>10234000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>10657000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>11249000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>11613000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>11450200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>9954100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>9253100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>8349200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>7823500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>7593200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>7445500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>7212300</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>7277700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>7200600</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>6991800</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>6638500</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>6637000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>6196700</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>5893500</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>5728100</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>5743600</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>5789900</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>5493600</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>5508500</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>5489500</v>
       </c>
     </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>984000</v>
+      </c>
+      <c r="E48" s="3">
         <v>978900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>967900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>943600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>907000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>885000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>851000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>824000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>766000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>755000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>716200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>705300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>700400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>715000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>714800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>741000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>783900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>738200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>740300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>756400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>767600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>457800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>457500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>446300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>435900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>439600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>438100</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>433000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>429000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>434100</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>430600</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1954900</v>
+      </c>
+      <c r="E49" s="3">
         <v>1961300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1962500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1976700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1990300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1992000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2016000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2023000</v>
-      </c>
-      <c r="K49" s="3">
-        <v>1806000</v>
       </c>
       <c r="L49" s="3">
         <v>1806000</v>
       </c>
       <c r="M49" s="3">
+        <v>1806000</v>
+      </c>
+      <c r="N49" s="3">
         <v>1604900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1556000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1558200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1573100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1552000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1591900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1565500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1242700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1242600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1246700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1247800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1253500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1256700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1271200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1229400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1212900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1220600</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1109800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1095800</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1096300</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1066200</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4388,8 +4502,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4483,8 +4600,11 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4492,7 +4612,7 @@
         <v>50100</v>
       </c>
       <c r="E52" s="3">
-        <v>54500</v>
+        <v>50100</v>
       </c>
       <c r="F52" s="3">
         <v>54500</v>
@@ -4501,10 +4621,10 @@
         <v>54500</v>
       </c>
       <c r="H52" s="3">
+        <v>54500</v>
+      </c>
+      <c r="I52" s="3">
         <v>54000</v>
-      </c>
-      <c r="I52" s="3">
-        <v>14000</v>
       </c>
       <c r="J52" s="3">
         <v>14000</v>
@@ -4516,7 +4636,7 @@
         <v>14000</v>
       </c>
       <c r="M52" s="3">
-        <v>14500</v>
+        <v>14000</v>
       </c>
       <c r="N52" s="3">
         <v>14500</v>
@@ -4528,10 +4648,10 @@
         <v>14500</v>
       </c>
       <c r="Q52" s="3">
+        <v>14500</v>
+      </c>
+      <c r="R52" s="3">
         <v>216600</v>
-      </c>
-      <c r="R52" s="3">
-        <v>18300</v>
       </c>
       <c r="S52" s="3">
         <v>18300</v>
@@ -4540,7 +4660,7 @@
         <v>18300</v>
       </c>
       <c r="U52" s="3">
-        <v>16600</v>
+        <v>18300</v>
       </c>
       <c r="V52" s="3">
         <v>16600</v>
@@ -4552,7 +4672,7 @@
         <v>16600</v>
       </c>
       <c r="Y52" s="3">
-        <v>22800</v>
+        <v>16600</v>
       </c>
       <c r="Z52" s="3">
         <v>22800</v>
@@ -4564,7 +4684,7 @@
         <v>22800</v>
       </c>
       <c r="AC52" s="3">
-        <v>20000</v>
+        <v>22800</v>
       </c>
       <c r="AD52" s="3">
         <v>20000</v>
@@ -4576,10 +4696,13 @@
         <v>20000</v>
       </c>
       <c r="AG52" s="3">
+        <v>20000</v>
+      </c>
+      <c r="AH52" s="3">
         <v>22000</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4673,103 +4796,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>14697800</v>
+      </c>
+      <c r="E54" s="3">
         <v>16802800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>14677600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>15730900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>15383500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>14955000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>16486000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>16262000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>16527000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>16451000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>16686100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>15426900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>14431900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>12796000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>12638800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>12288000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>11675500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>11519200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>11804100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>11443200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>11160300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>10630600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>11380100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>9959400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>9546800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>9573200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>9347000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>9314300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>8874400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>8831800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>9246500</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4803,8 +4932,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4838,103 +4968,107 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>745000</v>
+      </c>
+      <c r="E57" s="3">
         <v>879500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>810900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>789700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>720500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>915000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1115000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1015000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1051000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1262000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1252000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1070800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1113400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>979700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>830100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>781500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>664000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>820400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>812500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>709300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>631500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>778700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>826700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>770700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>709600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>793200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>741600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>697000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>675800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>794000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>813900</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5028,103 +5162,109 @@
       <c r="AG58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6815500</v>
+      </c>
+      <c r="E59" s="3">
         <v>8852900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>7175600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>7963300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>7783800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>7124000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>8324000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>7723000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>7346000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>6651000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>7043200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>6920600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>6154000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>4804500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4918800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>4925200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>4850100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>4748700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>5305000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>5265900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>5344000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>4837900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>5581000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>4326100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>4187700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>4104100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>4079900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>4208900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>3926300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>3815700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>4302200</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5218,103 +5358,109 @@
       <c r="AG60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2084800</v>
+      </c>
+      <c r="E61" s="3">
         <v>1947200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1922600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1979000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1897400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2012000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1988000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2075000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2205000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2186000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2242500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1619200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1655000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1526900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1538300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1489200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1288800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1006600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>961800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>919700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>858600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>808300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>821800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>832600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>731500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>732800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>734100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>734500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>735500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>736700</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>737900</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5322,7 +5468,7 @@
         <v>63600</v>
       </c>
       <c r="E62" s="3">
-        <v>18800</v>
+        <v>63600</v>
       </c>
       <c r="F62" s="3">
         <v>18800</v>
@@ -5331,22 +5477,22 @@
         <v>18800</v>
       </c>
       <c r="H62" s="3">
+        <v>18800</v>
+      </c>
+      <c r="I62" s="3">
         <v>19000</v>
-      </c>
-      <c r="I62" s="3">
-        <v>314000</v>
       </c>
       <c r="J62" s="3">
         <v>314000</v>
       </c>
       <c r="K62" s="3">
-        <v>345000</v>
+        <v>314000</v>
       </c>
       <c r="L62" s="3">
         <v>345000</v>
       </c>
       <c r="M62" s="3">
-        <v>291200</v>
+        <v>345000</v>
       </c>
       <c r="N62" s="3">
         <v>291200</v>
@@ -5358,10 +5504,10 @@
         <v>291200</v>
       </c>
       <c r="Q62" s="3">
+        <v>291200</v>
+      </c>
+      <c r="R62" s="3">
         <v>414400</v>
-      </c>
-      <c r="R62" s="3">
-        <v>266100</v>
       </c>
       <c r="S62" s="3">
         <v>266100</v>
@@ -5370,7 +5516,7 @@
         <v>266100</v>
       </c>
       <c r="U62" s="3">
-        <v>217100</v>
+        <v>266100</v>
       </c>
       <c r="V62" s="3">
         <v>217100</v>
@@ -5382,7 +5528,7 @@
         <v>217100</v>
       </c>
       <c r="Y62" s="3">
-        <v>219300</v>
+        <v>217100</v>
       </c>
       <c r="Z62" s="3">
         <v>219300</v>
@@ -5394,7 +5540,7 @@
         <v>219300</v>
       </c>
       <c r="AC62" s="3">
-        <v>242200</v>
+        <v>219300</v>
       </c>
       <c r="AD62" s="3">
         <v>242200</v>
@@ -5406,10 +5552,13 @@
         <v>242200</v>
       </c>
       <c r="AG62" s="3">
+        <v>242200</v>
+      </c>
+      <c r="AH62" s="3">
         <v>133100</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5503,8 +5652,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5598,8 +5750,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5693,103 +5848,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>9910700</v>
+      </c>
+      <c r="E66" s="3">
         <v>11954700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>10150400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>10958500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>10627000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>10290000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>11978000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>11346000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>11164000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>10684000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>11088900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>10163100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>9476600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>7886000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>7915000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>7722600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>7316100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>7098700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>7562000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>7358300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>7282200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>6888800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>7705900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>6389900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>6076300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>6093300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>6053200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>6120900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>5802000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>5823600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>6224200</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5823,8 +5984,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5918,8 +6080,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6013,8 +6178,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6108,8 +6276,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6203,103 +6374,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3701600</v>
+      </c>
+      <c r="E72" s="3">
         <v>3710600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>3739000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3796200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3712300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>3721000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>3722000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>3775000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>3721000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>3680000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>3476900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>3088600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2837200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2655500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2426900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2294600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2173700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2161000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>1985100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>1845900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>1707100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>1644200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1600300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1496600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1384700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1311100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1129000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>1150600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1066700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>1046800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>1012500</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6393,8 +6570,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6488,8 +6668,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6583,103 +6766,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4787100</v>
+      </c>
+      <c r="E76" s="3">
         <v>4848100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4527200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4772400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4756500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4665000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4508000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4916000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>5363000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5767000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5597100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>5263700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4955300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4910000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4723800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>4565400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>4359300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>4420500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>4242100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>4084900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>3878000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>3741900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>3674200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>3569500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>3470500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>3480000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>3293900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>3193400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>3072500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>3008200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>3022300</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6773,203 +6962,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>46700</v>
+      </c>
+      <c r="E81" s="3">
         <v>34100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-1700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>138500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>45900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>54000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>109000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>98000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>259800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>445300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>302300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>233600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>280300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>182300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>170700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>63200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>224000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>187200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>186700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>109600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>91600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>151500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>155100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>76200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>221100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>21400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>122300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>58300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>81000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>107300</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7003,103 +7201,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>50100</v>
+      </c>
+      <c r="E83" s="3">
         <v>49600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>47300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>46100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>45500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>43000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>41000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>42000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>41000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>39500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>39200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>40900</v>
-      </c>
-      <c r="O83" s="3">
-        <v>38300</v>
       </c>
       <c r="P83" s="3">
         <v>38300</v>
       </c>
       <c r="Q83" s="3">
+        <v>38300</v>
+      </c>
+      <c r="R83" s="3">
         <v>38200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>41000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>31400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>31500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>31700</v>
-      </c>
-      <c r="V83" s="3">
-        <v>32900</v>
       </c>
       <c r="W83" s="3">
         <v>32900</v>
       </c>
       <c r="X83" s="3">
+        <v>32900</v>
+      </c>
+      <c r="Y83" s="3">
         <v>33400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>31700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>31100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>29700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>31800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>36000</v>
-      </c>
-      <c r="AD83" s="3">
-        <v>30100</v>
       </c>
       <c r="AE83" s="3">
         <v>30100</v>
       </c>
       <c r="AF83" s="3">
+        <v>30100</v>
+      </c>
+      <c r="AG83" s="3">
         <v>28100</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>24500</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7193,8 +7395,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7288,8 +7493,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7383,8 +7591,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7478,8 +7689,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7573,103 +7787,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>69300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-41700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>219300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>269000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-92300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>247000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>304000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>189000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>40000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>344000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>399000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>253100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>223900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>425200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>291500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>343800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>24200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>301400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>310600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>266600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>34500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>308300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>230800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>210900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>43200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>176600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>220900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>228500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>6100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>237200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>105800</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7703,103 +7923,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-51700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-58100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-65800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-76400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-63100</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-71000</v>
       </c>
       <c r="I91" s="3">
         <v>-71000</v>
       </c>
       <c r="J91" s="3">
+        <v>-71000</v>
+      </c>
+      <c r="K91" s="3">
         <v>-75000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-43000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-49900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-43500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-39000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-28600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-22500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-33600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-28800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-29200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-28800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-24200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-26600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-27400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-30900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-31600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-33400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-22300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-31100</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-33500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-39700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-29900</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-28500</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-42800</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7893,8 +8117,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7988,103 +8215,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-231400</v>
+      </c>
+      <c r="E94" s="3">
         <v>414700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-61100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-181000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>426900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-140000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-62000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-86000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-107000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-565000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1296100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-752600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-779300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-319500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-390100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-12700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-692800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-27200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-57700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-76700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-290600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-205900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-446800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-279300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-288700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>5000</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-76400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-292000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-23700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-194200</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-145100</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8118,103 +8351,107 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-54900</v>
+      </c>
+      <c r="E96" s="3">
         <v>-54500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-54700</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-53600</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-53800</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-53000</v>
-      </c>
-      <c r="I96" s="3">
-        <v>-54000</v>
       </c>
       <c r="J96" s="3">
         <v>-54000</v>
       </c>
       <c r="K96" s="3">
+        <v>-54000</v>
+      </c>
+      <c r="L96" s="3">
         <v>-56000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-55900</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-56000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-50100</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-51000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-50900</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-49100</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-49000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-49700</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-47200</v>
-      </c>
-      <c r="U96" s="3">
-        <v>-47100</v>
       </c>
       <c r="V96" s="3">
         <v>-47100</v>
       </c>
       <c r="W96" s="3">
+        <v>-47100</v>
+      </c>
+      <c r="X96" s="3">
         <v>-47000</v>
-      </c>
-      <c r="X96" s="3">
-        <v>-46900</v>
       </c>
       <c r="Y96" s="3">
         <v>-46900</v>
       </c>
       <c r="Z96" s="3">
+        <v>-46900</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-42400</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-42300</v>
-      </c>
-      <c r="AB96" s="3">
-        <v>-42100</v>
       </c>
       <c r="AC96" s="3">
         <v>-42100</v>
       </c>
       <c r="AD96" s="3">
+        <v>-42100</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-37600</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-37500</v>
-      </c>
-      <c r="AF96" s="3">
-        <v>-37300</v>
       </c>
       <c r="AG96" s="3">
         <v>-37300</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>-37300</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8308,8 +8545,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8403,8 +8643,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8498,289 +8741,301 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1932200</v>
+      </c>
+      <c r="E100" s="3">
         <v>1648000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-820000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>171400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>423700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1250000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>385000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-54000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>543000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-507400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>634100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>694200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1305100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-351800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>83300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>137800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>244600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-503200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>49600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-115400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>124000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-836700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>1197000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>120500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>33900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>63100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-172600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>179800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>57700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-475400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>241200</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="E101" s="3">
         <v>5200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-5000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>3100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>6000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-11000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-8000</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
       <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
         <v>2800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-5600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>2000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>9200</v>
-      </c>
-      <c r="Q101" s="3">
-        <v>4400</v>
       </c>
       <c r="R101" s="3">
         <v>4400</v>
       </c>
       <c r="S101" s="3">
+        <v>4400</v>
+      </c>
+      <c r="T101" s="3">
         <v>-11900</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>4000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-3400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>2000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-3900</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-2200</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-2300</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>1000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>600</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>3300</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>3000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>1300</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-4800</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2098900</v>
+      </c>
+      <c r="E102" s="3">
         <v>2026200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-666800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>262500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>759900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1137000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>616000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>41000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>476000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-725500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-268700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>196700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>750600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-236900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-11000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>473400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-436000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-225000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>299000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>74900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-130100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-738200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>978800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>49900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-210600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>245300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-24800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>119300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>41300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-437200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>201500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FAF_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FAF_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="92">
   <si>
     <t>FAF</t>
   </si>
@@ -656,245 +656,252 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1631100</v>
+      </c>
+      <c r="E8" s="3">
         <v>1435600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1432400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1620000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1643600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1462500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1715000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1975000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2139000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2105000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2533100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2555900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2266400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2025700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2151300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1913700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1608700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1412900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1728700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1671200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1498600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1303600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1417100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1542200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1491200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1297400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1481300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1519600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1454400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1317000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1504300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1508300</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -991,8 +998,11 @@
       <c r="AH9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -1089,8 +1099,11 @@
       <c r="AH10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1125,8 +1138,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1223,8 +1237,11 @@
       <c r="AH12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1321,8 +1338,11 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1347,33 +1367,33 @@
       <c r="J14" s="3">
         <v>0</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>5</v>
+      <c r="K14" s="3">
+        <v>0</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>5</v>
+      <c r="O14" s="3">
+        <v>0</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="Q14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R14" s="3">
         <v>-18300</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>73300</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1389,8 +1409,8 @@
       <c r="X14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
@@ -1419,106 +1439,112 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>52100</v>
+      </c>
+      <c r="E15" s="3">
         <v>50100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>49600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>47300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>46100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>45500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>43000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>41000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>42000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>41000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>39500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>39200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>40900</v>
-      </c>
-      <c r="P15" s="3">
-        <v>38300</v>
       </c>
       <c r="Q15" s="3">
         <v>38300</v>
       </c>
       <c r="R15" s="3">
+        <v>38300</v>
+      </c>
+      <c r="S15" s="3">
         <v>38200</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>41000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>31400</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>31500</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>31700</v>
-      </c>
-      <c r="W15" s="3">
-        <v>32900</v>
       </c>
       <c r="X15" s="3">
         <v>32900</v>
       </c>
       <c r="Y15" s="3">
+        <v>32900</v>
+      </c>
+      <c r="Z15" s="3">
         <v>33400</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>31700</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>31100</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>29700</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>31800</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>36000</v>
-      </c>
-      <c r="AE15" s="3">
-        <v>30100</v>
       </c>
       <c r="AF15" s="3">
         <v>30100</v>
       </c>
       <c r="AG15" s="3">
+        <v>30100</v>
+      </c>
+      <c r="AH15" s="3">
         <v>28100</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>24500</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,204 +1576,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1425300</v>
+      </c>
+      <c r="E17" s="3">
         <v>1332000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1357600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1447100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1434500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1357400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1597000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1803000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1902000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1884000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2019500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1933500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1850700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1703200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1753000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1654400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1370000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1328500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1428400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1413600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1257200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1150000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1287200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1335800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1279200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1195100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1312800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1492500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1261300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1224400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1414000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1333600</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>205800</v>
+      </c>
+      <c r="E18" s="3">
         <v>103600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>74800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>172900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>209100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>105100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>118000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>172000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>237000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>221000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>513600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>622400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>415700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>322500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>398300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>259300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>238700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>84400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>300300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>257600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>241400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>153600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>129900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>206400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>212000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>102300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>168500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>27100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>193100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>92600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>90300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>174700</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,44 +1815,45 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-18800</v>
+      </c>
+      <c r="E20" s="3">
         <v>-11000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-3100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-138800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>3300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-16400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-30000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-151000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-77000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-71000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-160100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
         <v>0</v>
       </c>
@@ -1880,400 +1914,415 @@
       <c r="AH20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>239100</v>
+      </c>
+      <c r="E21" s="3">
         <v>142700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>121300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>81400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>258500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>134200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>131000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>62000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>202000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>191000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>393000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>661600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>456600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>360800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>436600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>297600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>279700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>115900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>331700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>289300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>274300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>186500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>163300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>238100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>243000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>132000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>200300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>63100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>223300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>122700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>118400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>199300</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>35400</v>
+      </c>
+      <c r="E22" s="3">
         <v>34300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>33300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>35800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>34300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>29100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>30000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>24000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>19000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>20000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>20100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>19200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>16200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>16500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>15900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>16000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>13400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>12100</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>11700</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>12200</v>
-      </c>
-      <c r="W22" s="3">
-        <v>11900</v>
       </c>
       <c r="X22" s="3">
         <v>11900</v>
       </c>
       <c r="Y22" s="3">
+        <v>11900</v>
+      </c>
+      <c r="Z22" s="3">
         <v>11000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>10800</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>10000</v>
-      </c>
-      <c r="AB22" s="3">
-        <v>9200</v>
       </c>
       <c r="AC22" s="3">
         <v>9200</v>
       </c>
       <c r="AD22" s="3">
+        <v>9200</v>
+      </c>
+      <c r="AE22" s="3">
         <v>9100</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>9000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>8700</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>8800</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>7800</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>151600</v>
+      </c>
+      <c r="E23" s="3">
         <v>58300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>38400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>178100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>59600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>58000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-3000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>141000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>130000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>333400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>603200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>399400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>306000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>382300</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>243400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>225300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>72300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>288500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>245300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>229500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>141700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>118900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>195600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>202000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>93100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>159300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>18000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>184200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>83900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>81500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>166900</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>35200</v>
+      </c>
+      <c r="E24" s="3">
         <v>11600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>4100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>41700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>13600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>4000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-6000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>31000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>32000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>72700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>152700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>96000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>71600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>100900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>59800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>53600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>8500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>63900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>57200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>42200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>31900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>25700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>44100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>46900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>16900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>52700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-3200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>62300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>25800</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>500</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>59500</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>116400</v>
+      </c>
+      <c r="E26" s="3">
         <v>46700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>34300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>136400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>46000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>54000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>3000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>110000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>98000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>260700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>450500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>303400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>234500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>281400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>183600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>171700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>63800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>224600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>188200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>187300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>109800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>93200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>151500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>155100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>76200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>106600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>21200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>121900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>58100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>81000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>107400</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>116000</v>
+      </c>
+      <c r="E27" s="3">
         <v>46700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>34100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>138500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>45900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>54000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>109000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>98000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>259800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>445300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>302300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>233600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>280300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>182300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>170700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>63200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>224000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>187200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>186700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>109600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>91600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>151500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>155100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>76200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>107000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>21400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>122300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>58300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>81000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>107300</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,8 +2722,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2726,8 +2787,8 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>5</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>5</v>
@@ -2744,12 +2805,12 @@
       <c r="AB29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AD29" s="3">
         <v>114100</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AE29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2762,8 +2823,11 @@
       <c r="AH29" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,44 +3025,47 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>18800</v>
+      </c>
+      <c r="E32" s="3">
         <v>11000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>3100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>138800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-3300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>16400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>30000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>151000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>77000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>71000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>160100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
         <v>0</v>
       </c>
@@ -3056,106 +3126,112 @@
       <c r="AH32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>116000</v>
+      </c>
+      <c r="E33" s="3">
         <v>46700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>34100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>138500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>45900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>54000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>109000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>98000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>259800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>445300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>302300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>233600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>280300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>182300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>170700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>63200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>224000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>187200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>186700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>109600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>91600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>151500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>155100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>76200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>221100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>21400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>122300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>58300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>81000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>107300</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>116000</v>
+      </c>
+      <c r="E35" s="3">
         <v>46700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>34100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>138500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>45900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>54000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>109000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>98000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>259800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>445300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>302300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>233600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>280300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>182300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>170700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>63200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>224000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>187200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>186700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>109600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>91600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>151500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>155100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>76200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>221100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>21400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>122300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>58300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>81000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>107300</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,106 +3611,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2048600</v>
+      </c>
+      <c r="E41" s="3">
         <v>1506400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>3605300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1579100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2245900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1983400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1224000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2361000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1745000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1704000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1228000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1954000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2222700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2026000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1275500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1512400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1523300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1050000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1486000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1711000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1412000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1337100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1467100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>2205300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1226500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1176600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1387200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1141900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1166800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1047500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1006100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1443300</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3721,8 +3811,11 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -3819,8 +3912,11 @@
       <c r="AH43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3917,8 +4013,11 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4015,8 +4114,11 @@
       <c r="AH45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -4113,302 +4215,314 @@
       <c r="AH46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>9039600</v>
+      </c>
+      <c r="E47" s="3">
         <v>9132700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>9170500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>9068800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>9484400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>9432400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>9799000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>10234000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>10657000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>11249000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>11613000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>11450200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>9954100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>9253100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>8349200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>7823500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>7593200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>7445500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>7212300</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>7277700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>7200600</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>6991800</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>6638500</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>6637000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>6196700</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>5893500</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>5728100</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>5743600</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>5789900</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>5493600</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>5508500</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>5489500</v>
       </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>996900</v>
+      </c>
+      <c r="E48" s="3">
         <v>984000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>978900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>967900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>943600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>907000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>885000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>851000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>824000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>766000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>755000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>716200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>705300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>700400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>715000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>714800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>741000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>783900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>738200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>740300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>756400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>767600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>457800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>457500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>446300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>435900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>439600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>438100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>433000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>429000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>434100</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>430600</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1945700</v>
+      </c>
+      <c r="E49" s="3">
         <v>1954900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1961300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1962500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1976700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1990300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1992000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2016000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2023000</v>
-      </c>
-      <c r="L49" s="3">
-        <v>1806000</v>
       </c>
       <c r="M49" s="3">
         <v>1806000</v>
       </c>
       <c r="N49" s="3">
+        <v>1806000</v>
+      </c>
+      <c r="O49" s="3">
         <v>1604900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1556000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1558200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1573100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1552000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1591900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1565500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1242700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1242600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1246700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1247800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1253500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1256700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1271200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1229400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1212900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1220600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1109800</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1095800</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1096300</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1066200</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,8 +4720,11 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4615,7 +4735,7 @@
         <v>50100</v>
       </c>
       <c r="F52" s="3">
-        <v>54500</v>
+        <v>50100</v>
       </c>
       <c r="G52" s="3">
         <v>54500</v>
@@ -4624,10 +4744,10 @@
         <v>54500</v>
       </c>
       <c r="I52" s="3">
+        <v>54500</v>
+      </c>
+      <c r="J52" s="3">
         <v>54000</v>
-      </c>
-      <c r="J52" s="3">
-        <v>14000</v>
       </c>
       <c r="K52" s="3">
         <v>14000</v>
@@ -4639,7 +4759,7 @@
         <v>14000</v>
       </c>
       <c r="N52" s="3">
-        <v>14500</v>
+        <v>14000</v>
       </c>
       <c r="O52" s="3">
         <v>14500</v>
@@ -4651,10 +4771,10 @@
         <v>14500</v>
       </c>
       <c r="R52" s="3">
+        <v>14500</v>
+      </c>
+      <c r="S52" s="3">
         <v>216600</v>
-      </c>
-      <c r="S52" s="3">
-        <v>18300</v>
       </c>
       <c r="T52" s="3">
         <v>18300</v>
@@ -4663,7 +4783,7 @@
         <v>18300</v>
       </c>
       <c r="V52" s="3">
-        <v>16600</v>
+        <v>18300</v>
       </c>
       <c r="W52" s="3">
         <v>16600</v>
@@ -4675,7 +4795,7 @@
         <v>16600</v>
       </c>
       <c r="Z52" s="3">
-        <v>22800</v>
+        <v>16600</v>
       </c>
       <c r="AA52" s="3">
         <v>22800</v>
@@ -4687,7 +4807,7 @@
         <v>22800</v>
       </c>
       <c r="AD52" s="3">
-        <v>20000</v>
+        <v>22800</v>
       </c>
       <c r="AE52" s="3">
         <v>20000</v>
@@ -4699,10 +4819,13 @@
         <v>20000</v>
       </c>
       <c r="AH52" s="3">
+        <v>20000</v>
+      </c>
+      <c r="AI52" s="3">
         <v>22000</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,106 +4922,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>15157300</v>
+      </c>
+      <c r="E54" s="3">
         <v>14697800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>16802800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>14677600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>15730900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>15383500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>14955000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>16486000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>16262000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>16527000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>16451000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>16686100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>15426900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>14431900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>12796000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>12638800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>12288000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>11675500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>11519200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>11804100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>11443200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>11160300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>10630600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>11380100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>9959400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>9546800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>9573200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>9347000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>9314300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>8874400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>8831800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>9246500</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,106 +5099,110 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>907000</v>
+      </c>
+      <c r="E57" s="3">
         <v>745000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>879500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>810900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>789700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>720500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>915000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1115000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1015000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1051000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1262000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1252000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1070800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1113400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>979700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>830100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>781500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>664000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>820400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>812500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>709300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>631500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>778700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>826700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>770700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>709600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>793200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>741600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>697000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>675800</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>794000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>813900</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5165,106 +5299,112 @@
       <c r="AH58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>7122400</v>
+      </c>
+      <c r="E59" s="3">
         <v>6815500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>8852900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>7175600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>7963300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>7783800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>7124000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>8324000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>7723000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>7346000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>6651000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>7043200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>6920600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>6154000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>4804500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>4918800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>4925200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>4850100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>4748700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>5305000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>5265900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>5344000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>4837900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>5581000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>4326100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>4187700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>4104100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>4079900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>4208900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>3926300</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>3815700</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>4302200</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -5361,106 +5501,112 @@
       <c r="AH60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2041200</v>
+      </c>
+      <c r="E61" s="3">
         <v>2084800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1947200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1922600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1979000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1897400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2012000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1988000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2075000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2205000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2186000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2242500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1619200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1655000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1526900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1538300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1489200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1288800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1006600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>961800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>919700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>858600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>808300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>821800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>832600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>731500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>732800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>734100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>734500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>735500</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>736700</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>737900</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5471,7 +5617,7 @@
         <v>63600</v>
       </c>
       <c r="F62" s="3">
-        <v>18800</v>
+        <v>63600</v>
       </c>
       <c r="G62" s="3">
         <v>18800</v>
@@ -5480,22 +5626,22 @@
         <v>18800</v>
       </c>
       <c r="I62" s="3">
+        <v>18800</v>
+      </c>
+      <c r="J62" s="3">
         <v>19000</v>
-      </c>
-      <c r="J62" s="3">
-        <v>314000</v>
       </c>
       <c r="K62" s="3">
         <v>314000</v>
       </c>
       <c r="L62" s="3">
-        <v>345000</v>
+        <v>314000</v>
       </c>
       <c r="M62" s="3">
         <v>345000</v>
       </c>
       <c r="N62" s="3">
-        <v>291200</v>
+        <v>345000</v>
       </c>
       <c r="O62" s="3">
         <v>291200</v>
@@ -5507,10 +5653,10 @@
         <v>291200</v>
       </c>
       <c r="R62" s="3">
+        <v>291200</v>
+      </c>
+      <c r="S62" s="3">
         <v>414400</v>
-      </c>
-      <c r="S62" s="3">
-        <v>266100</v>
       </c>
       <c r="T62" s="3">
         <v>266100</v>
@@ -5519,7 +5665,7 @@
         <v>266100</v>
       </c>
       <c r="V62" s="3">
-        <v>217100</v>
+        <v>266100</v>
       </c>
       <c r="W62" s="3">
         <v>217100</v>
@@ -5531,7 +5677,7 @@
         <v>217100</v>
       </c>
       <c r="Z62" s="3">
-        <v>219300</v>
+        <v>217100</v>
       </c>
       <c r="AA62" s="3">
         <v>219300</v>
@@ -5543,7 +5689,7 @@
         <v>219300</v>
       </c>
       <c r="AD62" s="3">
-        <v>242200</v>
+        <v>219300</v>
       </c>
       <c r="AE62" s="3">
         <v>242200</v>
@@ -5555,10 +5701,13 @@
         <v>242200</v>
       </c>
       <c r="AH62" s="3">
+        <v>242200</v>
+      </c>
+      <c r="AI62" s="3">
         <v>133100</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,106 +6006,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>10343700</v>
+      </c>
+      <c r="E66" s="3">
         <v>9910700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>11954700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>10150400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>10958500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>10627000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>10290000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>11978000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>11346000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>11164000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>10684000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>11088900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>10163100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>9476600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>7886000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>7915000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>7722600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>7316100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>7098700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>7562000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>7358300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>7282200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>6888800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>7705900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>6389900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>6076300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>6093300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>6053200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>6120900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>5802000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>5823600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>6224200</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,8 +6346,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,106 +6548,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3761900</v>
+      </c>
+      <c r="E72" s="3">
         <v>3701600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>3710600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3739000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3796200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>3712300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>3721000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>3722000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>3775000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>3721000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>3680000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>3476900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>3088600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2837200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2655500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2426900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2294600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2173700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2161000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>1985100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>1845900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>1707100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1644200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1600300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1496600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1384700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1311100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>1129000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1150600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>1066700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>1046800</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>1012500</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,106 +6952,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4813600</v>
+      </c>
+      <c r="E76" s="3">
         <v>4787100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4848100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4527200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4772400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4756500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4665000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4508000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4916000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>5363000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5767000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>5597100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>5263700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4955300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4910000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>4723800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>4565400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>4359300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>4420500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>4242100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>4084900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>3878000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>3741900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>3674200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>3569500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>3470500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>3480000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>3293900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>3193400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>3072500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>3008200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>3022300</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>116000</v>
+      </c>
+      <c r="E81" s="3">
         <v>46700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>34100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>138500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>45900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>54000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>109000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>98000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>259800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>445300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>302300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>233600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>280300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>182300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>170700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>63200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>224000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>187200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>186700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>109600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>91600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>151500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>155100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>76200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>221100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>21400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>122300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>58300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>81000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>107300</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,106 +7400,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>52100</v>
+      </c>
+      <c r="E83" s="3">
         <v>50100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>49600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>47300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>46100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>45500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>43000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>41000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>42000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>41000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>39500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>39200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>40900</v>
-      </c>
-      <c r="P83" s="3">
-        <v>38300</v>
       </c>
       <c r="Q83" s="3">
         <v>38300</v>
       </c>
       <c r="R83" s="3">
+        <v>38300</v>
+      </c>
+      <c r="S83" s="3">
         <v>38200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>41000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>31400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>31500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>31700</v>
-      </c>
-      <c r="W83" s="3">
-        <v>32900</v>
       </c>
       <c r="X83" s="3">
         <v>32900</v>
       </c>
       <c r="Y83" s="3">
+        <v>32900</v>
+      </c>
+      <c r="Z83" s="3">
         <v>33400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>31700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>31100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>29700</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>31800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>36000</v>
-      </c>
-      <c r="AE83" s="3">
-        <v>30100</v>
       </c>
       <c r="AF83" s="3">
         <v>30100</v>
       </c>
       <c r="AG83" s="3">
+        <v>30100</v>
+      </c>
+      <c r="AH83" s="3">
         <v>28100</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>24500</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,106 +8004,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>266700</v>
+      </c>
+      <c r="E89" s="3">
         <v>69300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-41700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>219300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>269000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-92300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>247000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>304000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>189000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>40000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>344000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>399000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>253100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>223900</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>425200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>291500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>343800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>24200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>301400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>310600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>266600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>34500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>308300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>230800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>210900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>43200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>176600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>220900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>228500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>6100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>237200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>105800</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,106 +8144,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-56700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-51700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-58100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-65800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-76400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-63100</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-71000</v>
       </c>
       <c r="J91" s="3">
         <v>-71000</v>
       </c>
       <c r="K91" s="3">
+        <v>-71000</v>
+      </c>
+      <c r="L91" s="3">
         <v>-75000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-43000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-49900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-43500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-39000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-28600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-22500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-33600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-28800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-29200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-28800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-24200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-26600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-27400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-30900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-31600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-33400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-22300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-31100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-33500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-39700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-29900</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-28500</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-42800</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,106 +8445,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>100800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-231400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>414700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-61100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-181000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>426900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-140000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-62000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-86000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-107000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-565000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1296100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-752600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-779300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-319500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-390100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-12700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-692800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-27200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-57700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-76700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-290600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-205900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-446800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-279300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-288700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>5000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-76400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-292000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-23700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-194200</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-145100</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,106 +8585,110 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-54700</v>
+      </c>
+      <c r="E96" s="3">
         <v>-54900</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-54500</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-54700</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-53600</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-53800</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-53000</v>
-      </c>
-      <c r="J96" s="3">
-        <v>-54000</v>
       </c>
       <c r="K96" s="3">
         <v>-54000</v>
       </c>
       <c r="L96" s="3">
+        <v>-54000</v>
+      </c>
+      <c r="M96" s="3">
         <v>-56000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-55900</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-56000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-50100</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-51000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-50900</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-49100</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-49000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-49700</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-47200</v>
-      </c>
-      <c r="V96" s="3">
-        <v>-47100</v>
       </c>
       <c r="W96" s="3">
         <v>-47100</v>
       </c>
       <c r="X96" s="3">
+        <v>-47100</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-47000</v>
-      </c>
-      <c r="Y96" s="3">
-        <v>-46900</v>
       </c>
       <c r="Z96" s="3">
         <v>-46900</v>
       </c>
       <c r="AA96" s="3">
+        <v>-46900</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-42400</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-42300</v>
-      </c>
-      <c r="AC96" s="3">
-        <v>-42100</v>
       </c>
       <c r="AD96" s="3">
         <v>-42100</v>
       </c>
       <c r="AE96" s="3">
+        <v>-42100</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-37600</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-37500</v>
-      </c>
-      <c r="AG96" s="3">
-        <v>-37300</v>
       </c>
       <c r="AH96" s="3">
         <v>-37300</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>-37300</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,298 +8987,310 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>175000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1932200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>1648000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-820000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>171400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>423700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-1250000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>385000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-54000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>543000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-507400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>634100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>694200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1305100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-351800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>83300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>137800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>244600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-503200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>49600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-115400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>124000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-836700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>1197000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>120500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>33900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>63100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-172600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>179800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>57700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-475400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>241200</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E101" s="3">
         <v>-4600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>5200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-5000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>3100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>1600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>6000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-11000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-8000</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
-      </c>
       <c r="M101" s="3">
+        <v>0</v>
+      </c>
+      <c r="N101" s="3">
         <v>2800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-5600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>2000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>9200</v>
-      </c>
-      <c r="R101" s="3">
-        <v>4400</v>
       </c>
       <c r="S101" s="3">
         <v>4400</v>
       </c>
       <c r="T101" s="3">
+        <v>4400</v>
+      </c>
+      <c r="U101" s="3">
         <v>-11900</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>4000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-3400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>2000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-3900</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-2200</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-2300</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>1000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>600</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>3300</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>3000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>1300</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-4800</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>542200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2098900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2026200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-666800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>262500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>759900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1137000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>616000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>41000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>476000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-725500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-268700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>196700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>750600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-236900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-11000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>473400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-436000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-225000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>299000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>74900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-130100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-738200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>978800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>49900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-210600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>245300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-24800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>119300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>41300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-437200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>201500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FAF_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FAF_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="92">
   <si>
     <t>FAF</t>
   </si>
@@ -656,275 +656,282 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>1631100</v>
+        <v>1406100</v>
       </c>
       <c r="E8" s="3">
-        <v>1435600</v>
+        <v>1612300</v>
       </c>
       <c r="F8" s="3">
-        <v>1432400</v>
+        <v>1424600</v>
       </c>
       <c r="G8" s="3">
-        <v>1620000</v>
+        <v>1429300</v>
       </c>
       <c r="H8" s="3">
-        <v>1643600</v>
+        <v>1481200</v>
       </c>
       <c r="I8" s="3">
-        <v>1462500</v>
+        <v>1646900</v>
       </c>
       <c r="J8" s="3">
+        <v>1446100</v>
+      </c>
+      <c r="K8" s="3">
         <v>1715000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1975000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2139000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2105000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2533100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2555900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2266400</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2025700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2151300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1913700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1608700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1412900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1728700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1671200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1498600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1303600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1417100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1542200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1491200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1297400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1481300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1519600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1454400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1317000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1504300</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1508300</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>5</v>
+      <c r="D9" s="3">
+        <v>638500</v>
+      </c>
+      <c r="E9" s="3">
+        <v>571700</v>
+      </c>
+      <c r="F9" s="3">
+        <v>517300</v>
+      </c>
+      <c r="G9" s="3">
+        <v>528800</v>
+      </c>
+      <c r="H9" s="3">
+        <v>622500</v>
+      </c>
+      <c r="I9" s="3">
+        <v>585900</v>
+      </c>
+      <c r="J9" s="3">
+        <v>551300</v>
       </c>
       <c r="K9" s="3" t="s">
         <v>5</v>
@@ -1001,31 +1008,34 @@
       <c r="AI9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>5</v>
+      <c r="D10" s="3">
+        <v>767600</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1040600</v>
+      </c>
+      <c r="F10" s="3">
+        <v>907300</v>
+      </c>
+      <c r="G10" s="3">
+        <v>900500</v>
+      </c>
+      <c r="H10" s="3">
+        <v>858700</v>
+      </c>
+      <c r="I10" s="3">
+        <v>1061000</v>
+      </c>
+      <c r="J10" s="3">
+        <v>894800</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>5</v>
@@ -1102,8 +1112,11 @@
       <c r="AI10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1139,8 +1152,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1240,8 +1254,11 @@
       <c r="AI12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1341,62 +1358,65 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>5</v>
+      <c r="L14" s="3">
+        <v>0</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>5</v>
+      <c r="P14" s="3">
+        <v>0</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="R14" s="3">
+      <c r="R14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="S14" s="3">
         <v>-18300</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>73300</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="U14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1412,8 +1432,8 @@
       <c r="Y14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
+      <c r="Z14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AA14" s="3">
         <v>0</v>
@@ -1442,109 +1462,115 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>53200</v>
+      </c>
+      <c r="E15" s="3">
         <v>52100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>50100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>49600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>47300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>46100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>45500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>43000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>41000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>42000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>41000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>39500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>39200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>40900</v>
-      </c>
-      <c r="Q15" s="3">
-        <v>38300</v>
       </c>
       <c r="R15" s="3">
         <v>38300</v>
       </c>
       <c r="S15" s="3">
+        <v>38300</v>
+      </c>
+      <c r="T15" s="3">
         <v>38200</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>41000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>31400</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>31500</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>31700</v>
-      </c>
-      <c r="X15" s="3">
-        <v>32900</v>
       </c>
       <c r="Y15" s="3">
         <v>32900</v>
       </c>
       <c r="Z15" s="3">
+        <v>32900</v>
+      </c>
+      <c r="AA15" s="3">
         <v>33400</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>31700</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>31100</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>29700</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>31800</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>36000</v>
-      </c>
-      <c r="AF15" s="3">
-        <v>30100</v>
       </c>
       <c r="AG15" s="3">
         <v>30100</v>
       </c>
       <c r="AH15" s="3">
+        <v>30100</v>
+      </c>
+      <c r="AI15" s="3">
         <v>28100</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>24500</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,210 +1603,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1514300</v>
+      </c>
+      <c r="E17" s="3">
         <v>1425300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1332000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1357600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1447100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1434500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1357400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1597000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1803000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1902000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1884000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2019500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1933500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1850700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1703200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1753000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1654400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1370000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1328500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1428400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1413600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1257200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1150000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1287200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1335800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1279200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1195100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1312800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1492500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1261300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1224400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1414000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1333600</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>205800</v>
+        <v>-108200</v>
       </c>
       <c r="E18" s="3">
-        <v>103600</v>
+        <v>187000</v>
       </c>
       <c r="F18" s="3">
-        <v>74800</v>
+        <v>92600</v>
       </c>
       <c r="G18" s="3">
-        <v>172900</v>
+        <v>71700</v>
       </c>
       <c r="H18" s="3">
-        <v>209100</v>
+        <v>34100</v>
       </c>
       <c r="I18" s="3">
-        <v>105100</v>
+        <v>212400</v>
       </c>
       <c r="J18" s="3">
+        <v>88700</v>
+      </c>
+      <c r="K18" s="3">
         <v>118000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>172000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>237000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>221000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>513600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>622400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>415700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>322500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>398300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>259300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>238700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>84400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>300300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>257600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>241400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>153600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>129900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>206400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>212000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>102300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>168500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>27100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>193100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>92600</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>90300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>174700</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1816,47 +1849,48 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>-18800</v>
-      </c>
-      <c r="E20" s="3">
-        <v>-11000</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-3100</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-138800</v>
-      </c>
-      <c r="H20" s="3">
-        <v>3300</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-16400</v>
-      </c>
-      <c r="J20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K20" s="3">
         <v>-30000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-151000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-77000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-71000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-160100</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
@@ -1917,412 +1951,427 @@
       <c r="AI20" s="3">
         <v>0</v>
       </c>
+      <c r="AJ20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-55000</v>
+      </c>
+      <c r="E21" s="3">
         <v>239100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>142700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>121300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>81400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>258500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>134200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>131000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>62000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>202000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>191000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>393000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>661600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>456600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>360800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>436600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>297600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>279700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>115900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>331700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>289300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>274300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>186500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>163300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>238100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>243000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>132000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>200300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>63100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>223300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>122700</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>118400</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>199300</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>36200</v>
+      </c>
+      <c r="E22" s="3">
         <v>35400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>34300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>33300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>35800</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>34300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>29100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>30000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>24000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>19000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>20000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>20100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>19200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>16200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>16500</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>15900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>16000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>13400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>12100</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>11700</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>12200</v>
-      </c>
-      <c r="X22" s="3">
-        <v>11900</v>
       </c>
       <c r="Y22" s="3">
         <v>11900</v>
       </c>
       <c r="Z22" s="3">
+        <v>11900</v>
+      </c>
+      <c r="AA22" s="3">
         <v>11000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>10800</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>10000</v>
-      </c>
-      <c r="AC22" s="3">
-        <v>9200</v>
       </c>
       <c r="AD22" s="3">
         <v>9200</v>
       </c>
       <c r="AE22" s="3">
+        <v>9200</v>
+      </c>
+      <c r="AF22" s="3">
         <v>9100</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>9000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>8700</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>8800</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>7800</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-144400</v>
+      </c>
+      <c r="E23" s="3">
         <v>151600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>58300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>38400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>178100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>59600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>58000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-3000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>141000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>130000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>333400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>603200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>399400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>306000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>382300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>243400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>225300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>72300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>288500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>245300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>229500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>141700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>118900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>195600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>202000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>93100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>159300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>18000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>184200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>83900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>81500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>166900</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-41000</v>
+      </c>
+      <c r="E24" s="3">
         <v>35200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>11600</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>4100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>41700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>13600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>4000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-6000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>31000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>32000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>72700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>152700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>96000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>71600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>100900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>59800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>53600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>8500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>63900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>57200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>42200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>31900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>25700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>44100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>46900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>16900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>52700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-3200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>62300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>25800</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>500</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>59500</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,210 +2471,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-103400</v>
+      </c>
+      <c r="E26" s="3">
         <v>116400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>46700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>34300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>136400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>46000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>54000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>110000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>98000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>260700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>450500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>303400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>234500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>281400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>183600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>171700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>63800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>224600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>188200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>187300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>109800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>93200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>151500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>155100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>76200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>106600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>21200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>121900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>58100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>81000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>107400</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-104000</v>
+      </c>
+      <c r="E27" s="3">
         <v>116000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>46700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>34100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>138500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>45900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>54000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>109000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>98000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>259800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>445300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>302300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>233600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>280300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>182300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>170700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>63200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>224000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>187200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>186700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>109600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>91600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>151500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>155100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>76200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>107000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>21400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>122300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>58300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>81000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>107300</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,8 +2783,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2790,8 +2851,8 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>5</v>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>5</v>
@@ -2808,12 +2869,12 @@
       <c r="AC29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AD29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AE29" s="3">
         <v>114100</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AF29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2826,8 +2887,11 @@
       <c r="AI29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +2991,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,47 +3095,50 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>18800</v>
-      </c>
-      <c r="E32" s="3">
-        <v>11000</v>
-      </c>
-      <c r="F32" s="3">
-        <v>3100</v>
-      </c>
-      <c r="G32" s="3">
-        <v>138800</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-3300</v>
-      </c>
-      <c r="I32" s="3">
-        <v>16400</v>
-      </c>
-      <c r="J32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K32" s="3">
         <v>30000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>151000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>77000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>71000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>160100</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
@@ -3129,109 +3199,115 @@
       <c r="AI32" s="3">
         <v>0</v>
       </c>
+      <c r="AJ32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-104000</v>
+      </c>
+      <c r="E33" s="3">
         <v>116000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>46700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>34100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>138500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>45900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>54000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>109000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>98000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>259800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>445300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>302300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>233600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>280300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>182300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>170700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>63200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>224000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>187200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>186700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>109600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>91600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>151500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>155100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>76200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>221100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>21400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>122300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>58300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>81000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>107300</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,215 +3407,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-104000</v>
+      </c>
+      <c r="E35" s="3">
         <v>116000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>46700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>34100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>138500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>45900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>54000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>109000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>98000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>259800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>445300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>302300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>233600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>280300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>182300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>170700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>63200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>224000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>187200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>186700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>109600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>91600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>151500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>155100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>76200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>221100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>21400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>122300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>58300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>81000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>107300</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3660,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,132 +3698,136 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2953400</v>
+      </c>
+      <c r="E41" s="3">
         <v>2048600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1506400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3605300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1579100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2245900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1983400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1224000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2361000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1745000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1704000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1228000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1954000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2222700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2026000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1275500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1512400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1523300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1050000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1486000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1711000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1412000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1337100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1467100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>2205300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1226500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1176600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1387200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1141900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1166800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1047500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1006100</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1443300</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>55400</v>
       </c>
       <c r="E42" s="3">
-        <v>0</v>
+        <v>56400</v>
       </c>
       <c r="F42" s="3">
-        <v>0</v>
+        <v>77100</v>
       </c>
       <c r="G42" s="3">
-        <v>0</v>
+        <v>55800</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>55300</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>55900</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>53500</v>
       </c>
       <c r="K42" s="3">
         <v>0</v>
@@ -3814,31 +3904,34 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>0</v>
+        <v>1429300</v>
       </c>
       <c r="E43" s="3">
-        <v>0</v>
+        <v>1192400</v>
       </c>
       <c r="F43" s="3">
-        <v>0</v>
+        <v>1268200</v>
       </c>
       <c r="G43" s="3">
-        <v>0</v>
+        <v>1221600</v>
       </c>
       <c r="H43" s="3">
-        <v>0</v>
+        <v>1077600</v>
       </c>
       <c r="I43" s="3">
-        <v>0</v>
+        <v>1106900</v>
       </c>
       <c r="J43" s="3">
-        <v>0</v>
+        <v>980300</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -3915,31 +4008,34 @@
       <c r="AI43" s="3">
         <v>0</v>
       </c>
+      <c r="AJ43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -4016,31 +4112,34 @@
       <c r="AI44" s="3">
         <v>0</v>
       </c>
+      <c r="AJ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>0</v>
-      </c>
-      <c r="E45" s="3">
-        <v>0</v>
-      </c>
-      <c r="F45" s="3">
-        <v>0</v>
-      </c>
-      <c r="G45" s="3">
-        <v>0</v>
-      </c>
-      <c r="H45" s="3">
-        <v>0</v>
-      </c>
-      <c r="I45" s="3">
-        <v>0</v>
-      </c>
-      <c r="J45" s="3">
-        <v>0</v>
+      <c r="D45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -4117,31 +4216,34 @@
       <c r="AI45" s="3">
         <v>0</v>
       </c>
+      <c r="AJ45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>4438100</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>3297400</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>2851700</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>4882700</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>2712000</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>3408700</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>3017200</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -4218,311 +4320,323 @@
       <c r="AI46" s="3">
         <v>0</v>
       </c>
+      <c r="AJ46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>9039600</v>
+        <v>7641800</v>
       </c>
       <c r="E47" s="3">
-        <v>9132700</v>
+        <v>7696100</v>
       </c>
       <c r="F47" s="3">
-        <v>9170500</v>
+        <v>7697500</v>
       </c>
       <c r="G47" s="3">
-        <v>9068800</v>
+        <v>7786100</v>
       </c>
       <c r="H47" s="3">
-        <v>9484400</v>
+        <v>7837100</v>
       </c>
       <c r="I47" s="3">
-        <v>9432400</v>
+        <v>8224800</v>
       </c>
       <c r="J47" s="3">
+        <v>8307600</v>
+      </c>
+      <c r="K47" s="3">
         <v>9799000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>10234000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>10657000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>11249000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>11613000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>11450200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>9954100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>9253100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>8349200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>7823500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>7593200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>7445500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>7212300</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>7277700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>7200600</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>6991800</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>6638500</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>6637000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>6196700</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>5893500</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>5728100</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>5743600</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>5789900</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>5493600</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>5508500</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>5489500</v>
       </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1013100</v>
+      </c>
+      <c r="E48" s="3">
         <v>996900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>984000</v>
       </c>
-      <c r="F48" s="3">
-        <v>978900</v>
-      </c>
       <c r="G48" s="3">
+        <v>982100</v>
+      </c>
+      <c r="H48" s="3">
         <v>967900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>943600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>907000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>885000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>851000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>824000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>766000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>755000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>716200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>705300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>700400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>715000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>714800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>741000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>783900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>738200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>740300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>756400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>767600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>457800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>457500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>446300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>435900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>439600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>438100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>433000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>429000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>434100</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>430600</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>1945700</v>
+        <v>2613800</v>
       </c>
       <c r="E49" s="3">
-        <v>1954900</v>
+        <v>2609600</v>
       </c>
       <c r="F49" s="3">
-        <v>1961300</v>
+        <v>2611100</v>
       </c>
       <c r="G49" s="3">
-        <v>1962500</v>
+        <v>2613700</v>
       </c>
       <c r="H49" s="3">
-        <v>1976700</v>
+        <v>2610300</v>
       </c>
       <c r="I49" s="3">
-        <v>1990300</v>
+        <v>2620700</v>
       </c>
       <c r="J49" s="3">
+        <v>2634200</v>
+      </c>
+      <c r="K49" s="3">
         <v>1992000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2016000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2023000</v>
-      </c>
-      <c r="M49" s="3">
-        <v>1806000</v>
       </c>
       <c r="N49" s="3">
         <v>1806000</v>
       </c>
       <c r="O49" s="3">
+        <v>1806000</v>
+      </c>
+      <c r="P49" s="3">
         <v>1604900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1556000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1558200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1573100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1552000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1591900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1565500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1242700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1242600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1246700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1247800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1253500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1256700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1271200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1229400</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1212900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1220600</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1109800</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1095800</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1096300</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>1066200</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4736,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,34 +4840,37 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>50100</v>
+        <v>809500</v>
       </c>
       <c r="E52" s="3">
-        <v>50100</v>
+        <v>507200</v>
       </c>
       <c r="F52" s="3">
-        <v>50100</v>
+        <v>503400</v>
       </c>
       <c r="G52" s="3">
-        <v>54500</v>
+        <v>465700</v>
       </c>
       <c r="H52" s="3">
-        <v>54500</v>
+        <v>495800</v>
       </c>
       <c r="I52" s="3">
-        <v>54500</v>
+        <v>478600</v>
       </c>
       <c r="J52" s="3">
+        <v>463000</v>
+      </c>
+      <c r="K52" s="3">
         <v>54000</v>
-      </c>
-      <c r="K52" s="3">
-        <v>14000</v>
       </c>
       <c r="L52" s="3">
         <v>14000</v>
@@ -4762,7 +4882,7 @@
         <v>14000</v>
       </c>
       <c r="O52" s="3">
-        <v>14500</v>
+        <v>14000</v>
       </c>
       <c r="P52" s="3">
         <v>14500</v>
@@ -4774,10 +4894,10 @@
         <v>14500</v>
       </c>
       <c r="S52" s="3">
+        <v>14500</v>
+      </c>
+      <c r="T52" s="3">
         <v>216600</v>
-      </c>
-      <c r="T52" s="3">
-        <v>18300</v>
       </c>
       <c r="U52" s="3">
         <v>18300</v>
@@ -4786,7 +4906,7 @@
         <v>18300</v>
       </c>
       <c r="W52" s="3">
-        <v>16600</v>
+        <v>18300</v>
       </c>
       <c r="X52" s="3">
         <v>16600</v>
@@ -4798,7 +4918,7 @@
         <v>16600</v>
       </c>
       <c r="AA52" s="3">
-        <v>22800</v>
+        <v>16600</v>
       </c>
       <c r="AB52" s="3">
         <v>22800</v>
@@ -4810,7 +4930,7 @@
         <v>22800</v>
       </c>
       <c r="AE52" s="3">
-        <v>20000</v>
+        <v>22800</v>
       </c>
       <c r="AF52" s="3">
         <v>20000</v>
@@ -4822,10 +4942,13 @@
         <v>20000</v>
       </c>
       <c r="AI52" s="3">
+        <v>20000</v>
+      </c>
+      <c r="AJ52" s="3">
         <v>22000</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,109 +5048,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>16566400</v>
+      </c>
+      <c r="E54" s="3">
         <v>15157300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>14697800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>16802800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>14677600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>15730900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>15383500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>14955000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>16486000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>16262000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>16527000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>16451000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>16686100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>15426900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>14431900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>12796000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>12638800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>12288000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>11675500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>11519200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>11804100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>11443200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>11160300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>10630600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>11380100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>9959400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>9546800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>9573200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>9347000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>9314300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>8874400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>8831800</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>9246500</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5192,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,132 +5230,136 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>907000</v>
+        <v>2127200</v>
       </c>
       <c r="E57" s="3">
-        <v>745000</v>
+        <v>2159200</v>
       </c>
       <c r="F57" s="3">
-        <v>879500</v>
+        <v>2006600</v>
       </c>
       <c r="G57" s="3">
-        <v>810900</v>
+        <v>1345700</v>
       </c>
       <c r="H57" s="3">
-        <v>789700</v>
+        <v>2110400</v>
       </c>
       <c r="I57" s="3">
-        <v>720500</v>
+        <v>2111900</v>
       </c>
       <c r="J57" s="3">
+        <v>2035000</v>
+      </c>
+      <c r="K57" s="3">
         <v>915000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1115000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1015000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1051000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1262000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1252000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1070800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1113400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>979700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>830100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>781500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>664000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>820400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>812500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>709300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>631500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>778700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>826700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>770700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>709600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>793200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>741600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>697000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>675800</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>794000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>813900</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>878200</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>641500</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>688800</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>638800</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>530400</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>585700</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>502900</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -5302,132 +5436,138 @@
       <c r="AI58" s="3">
         <v>0</v>
       </c>
+      <c r="AJ58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>7122400</v>
+        <v>6086900</v>
       </c>
       <c r="E59" s="3">
-        <v>6815500</v>
+        <v>5633200</v>
       </c>
       <c r="F59" s="3">
-        <v>8852900</v>
+        <v>5318500</v>
       </c>
       <c r="G59" s="3">
-        <v>7175600</v>
+        <v>7484300</v>
       </c>
       <c r="H59" s="3">
-        <v>7963300</v>
+        <v>5621300</v>
       </c>
       <c r="I59" s="3">
-        <v>7783800</v>
+        <v>6377900</v>
       </c>
       <c r="J59" s="3">
+        <v>6204700</v>
+      </c>
+      <c r="K59" s="3">
         <v>7124000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>8324000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>7723000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>7346000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>6651000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>7043200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>6920600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>6154000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>4804500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>4918800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>4925200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>4850100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>4748700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>5305000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>5265900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>5344000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>4837900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>5581000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>4326100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>4187700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>4104100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>4079900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>4208900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>3926300</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>3815700</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>4302200</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>9092300</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>8433900</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>8013900</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>10124600</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>8262100</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>9075500</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>8742600</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -5504,147 +5644,153 @@
       <c r="AI60" s="3">
         <v>0</v>
       </c>
+      <c r="AJ60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2041200</v>
+        <v>2089900</v>
       </c>
       <c r="E61" s="3">
-        <v>2084800</v>
+        <v>1636700</v>
       </c>
       <c r="F61" s="3">
-        <v>1947200</v>
+        <v>1631400</v>
       </c>
       <c r="G61" s="3">
-        <v>1922600</v>
+        <v>1555000</v>
       </c>
       <c r="H61" s="3">
-        <v>1979000</v>
+        <v>1647000</v>
       </c>
       <c r="I61" s="3">
-        <v>1897400</v>
+        <v>1656500</v>
       </c>
       <c r="J61" s="3">
+        <v>1659100</v>
+      </c>
+      <c r="K61" s="3">
         <v>2012000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1988000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2075000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2205000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2186000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2242500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1619200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1655000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1526900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1538300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1489200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1288800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1006600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>961800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>919700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>858600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>808300</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>821800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>832600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>731500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>732800</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>734100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>734500</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>735500</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>736700</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>737900</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="D62" s="3">
-        <v>63600</v>
-      </c>
-      <c r="E62" s="3">
-        <v>63600</v>
-      </c>
-      <c r="F62" s="3">
-        <v>63600</v>
-      </c>
-      <c r="G62" s="3">
-        <v>18800</v>
-      </c>
-      <c r="H62" s="3">
-        <v>18800</v>
-      </c>
-      <c r="I62" s="3">
-        <v>18800</v>
-      </c>
-      <c r="J62" s="3">
+      <c r="D62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K62" s="3">
         <v>19000</v>
-      </c>
-      <c r="K62" s="3">
-        <v>314000</v>
       </c>
       <c r="L62" s="3">
         <v>314000</v>
       </c>
       <c r="M62" s="3">
-        <v>345000</v>
+        <v>314000</v>
       </c>
       <c r="N62" s="3">
         <v>345000</v>
       </c>
       <c r="O62" s="3">
-        <v>291200</v>
+        <v>345000</v>
       </c>
       <c r="P62" s="3">
         <v>291200</v>
@@ -5656,10 +5802,10 @@
         <v>291200</v>
       </c>
       <c r="S62" s="3">
+        <v>291200</v>
+      </c>
+      <c r="T62" s="3">
         <v>414400</v>
-      </c>
-      <c r="T62" s="3">
-        <v>266100</v>
       </c>
       <c r="U62" s="3">
         <v>266100</v>
@@ -5668,7 +5814,7 @@
         <v>266100</v>
       </c>
       <c r="W62" s="3">
-        <v>217100</v>
+        <v>266100</v>
       </c>
       <c r="X62" s="3">
         <v>217100</v>
@@ -5680,7 +5826,7 @@
         <v>217100</v>
       </c>
       <c r="AA62" s="3">
-        <v>219300</v>
+        <v>217100</v>
       </c>
       <c r="AB62" s="3">
         <v>219300</v>
@@ -5692,7 +5838,7 @@
         <v>219300</v>
       </c>
       <c r="AE62" s="3">
-        <v>242200</v>
+        <v>219300</v>
       </c>
       <c r="AF62" s="3">
         <v>242200</v>
@@ -5704,10 +5850,13 @@
         <v>242200</v>
       </c>
       <c r="AI62" s="3">
+        <v>242200</v>
+      </c>
+      <c r="AJ62" s="3">
         <v>133100</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +5956,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6060,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,109 +6164,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>10343700</v>
+        <v>11455800</v>
       </c>
       <c r="E66" s="3">
-        <v>9910700</v>
+        <v>10324700</v>
       </c>
       <c r="F66" s="3">
-        <v>11954700</v>
+        <v>9891900</v>
       </c>
       <c r="G66" s="3">
-        <v>10150400</v>
+        <v>11940000</v>
       </c>
       <c r="H66" s="3">
-        <v>10958500</v>
+        <v>10135600</v>
       </c>
       <c r="I66" s="3">
-        <v>10627000</v>
+        <v>10944000</v>
       </c>
       <c r="J66" s="3">
+        <v>10604600</v>
+      </c>
+      <c r="K66" s="3">
         <v>10290000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>11978000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>11346000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>11164000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>10684000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>11088900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>10163100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>9476600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>7886000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>7915000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>7722600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>7316100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>7098700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>7562000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>7358300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>7282200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>6888800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>7705900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>6389900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>6076300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>6093300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>6053200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>6120900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>5802000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>5823600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>6224200</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6308,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6410,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,8 +6514,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6450,8 +6618,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,109 +6722,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3601400</v>
+      </c>
+      <c r="E72" s="3">
         <v>3761900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>3701600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3710600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3739000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>3796200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>3712300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>3721000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>3722000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>3775000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>3721000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>3680000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>3476900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>3088600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2837200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2655500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2426900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2294600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2173700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2161000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>1985100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>1845900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1707100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1644200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1600300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1496600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1384700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>1311100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1129000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>1150600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>1066700</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>1046800</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>1012500</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +6930,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7034,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,109 +7138,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5092200</v>
+      </c>
+      <c r="E76" s="3">
         <v>4813600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4787100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4848100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4527200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4772400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4756500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4665000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4508000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4916000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>5363000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>5767000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>5597100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>5263700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4955300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>4910000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>4723800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>4565400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>4359300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>4420500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>4242100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>4084900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>3878000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>3741900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>3674200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>3569500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>3470500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>3480000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>3293900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>3193400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>3072500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>3008200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>3022300</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,215 +7346,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-104000</v>
+      </c>
+      <c r="E81" s="3">
         <v>116000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>46700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>34100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>138500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>45900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>54000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>109000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>98000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>259800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>445300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>302300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>233600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>280300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>182300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>170700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>63200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>224000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>187200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>186700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>109600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>91600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>151500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>155100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>76200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>221100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>21400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>122300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>58300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>81000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>107300</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,109 +7599,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>52100</v>
+        <v>34400</v>
       </c>
       <c r="E83" s="3">
-        <v>50100</v>
+        <v>33500</v>
       </c>
       <c r="F83" s="3">
-        <v>49600</v>
+        <v>32000</v>
       </c>
       <c r="G83" s="3">
-        <v>47300</v>
+        <v>30800</v>
       </c>
       <c r="H83" s="3">
-        <v>46100</v>
+        <v>29700</v>
       </c>
       <c r="I83" s="3">
-        <v>45500</v>
+        <v>27700</v>
       </c>
       <c r="J83" s="3">
+        <v>26100</v>
+      </c>
+      <c r="K83" s="3">
         <v>43000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>41000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>42000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>41000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>39500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>39200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>40900</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>38300</v>
       </c>
       <c r="R83" s="3">
         <v>38300</v>
       </c>
       <c r="S83" s="3">
+        <v>38300</v>
+      </c>
+      <c r="T83" s="3">
         <v>38200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>41000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>31400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>31500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>31700</v>
-      </c>
-      <c r="X83" s="3">
-        <v>32900</v>
       </c>
       <c r="Y83" s="3">
         <v>32900</v>
       </c>
       <c r="Z83" s="3">
+        <v>32900</v>
+      </c>
+      <c r="AA83" s="3">
         <v>33400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>31700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>31100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>29700</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>31800</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>36000</v>
-      </c>
-      <c r="AF83" s="3">
-        <v>30100</v>
       </c>
       <c r="AG83" s="3">
         <v>30100</v>
       </c>
       <c r="AH83" s="3">
+        <v>30100</v>
+      </c>
+      <c r="AI83" s="3">
         <v>28100</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>24500</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +7805,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +7909,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8013,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8117,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,109 +8221,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>236900</v>
+      </c>
+      <c r="E89" s="3">
         <v>266700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>69300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-41700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>219300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>269000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-92300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>247000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>304000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>189000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>40000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>344000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>399000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>253100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>223900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>425200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>291500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>343800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>24200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>301400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>310600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>266600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>34500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>308300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>230800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>210900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>43200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>176600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>220900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>228500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>6100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>237200</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>105800</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,109 +8365,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-51500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-56700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-51700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-58100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-65800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-76400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-63100</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-71000</v>
       </c>
       <c r="K91" s="3">
         <v>-71000</v>
       </c>
       <c r="L91" s="3">
+        <v>-71000</v>
+      </c>
+      <c r="M91" s="3">
         <v>-75000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-43000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-49900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-43500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-39000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-28600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-22500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-33600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-28800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-29200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-28800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-24200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-26600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-27400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-30900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-31600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-33400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-22300</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-31100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-33500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-39700</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-29900</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-28500</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-42800</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8571,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,109 +8675,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-295000</v>
+      </c>
+      <c r="E94" s="3">
         <v>100800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-231400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>414700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-61100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-181000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>426900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-140000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-62000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-86000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-107000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-565000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1296100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-752600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-779300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-319500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-390100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-12700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-692800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-27200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-57700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-76700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-290600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-205900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-446800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-279300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-288700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>5000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-76400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-292000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-23700</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-194200</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-145100</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,109 +8819,113 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-54700</v>
+        <v>55600</v>
       </c>
       <c r="E96" s="3">
-        <v>-54900</v>
+        <v>54700</v>
       </c>
       <c r="F96" s="3">
-        <v>-54500</v>
+        <v>54900</v>
       </c>
       <c r="G96" s="3">
-        <v>-54700</v>
+        <v>54500</v>
       </c>
       <c r="H96" s="3">
-        <v>-53600</v>
+        <v>54700</v>
       </c>
       <c r="I96" s="3">
-        <v>-53800</v>
+        <v>53600</v>
       </c>
       <c r="J96" s="3">
+        <v>53800</v>
+      </c>
+      <c r="K96" s="3">
         <v>-53000</v>
-      </c>
-      <c r="K96" s="3">
-        <v>-54000</v>
       </c>
       <c r="L96" s="3">
         <v>-54000</v>
       </c>
       <c r="M96" s="3">
+        <v>-54000</v>
+      </c>
+      <c r="N96" s="3">
         <v>-56000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-55900</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-56000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-50100</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-51000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-50900</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-49100</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-49000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-49700</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-47200</v>
-      </c>
-      <c r="W96" s="3">
-        <v>-47100</v>
       </c>
       <c r="X96" s="3">
         <v>-47100</v>
       </c>
       <c r="Y96" s="3">
+        <v>-47100</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-47000</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>-46900</v>
       </c>
       <c r="AA96" s="3">
         <v>-46900</v>
       </c>
       <c r="AB96" s="3">
+        <v>-46900</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-42400</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-42300</v>
-      </c>
-      <c r="AD96" s="3">
-        <v>-42100</v>
       </c>
       <c r="AE96" s="3">
         <v>-42100</v>
       </c>
       <c r="AF96" s="3">
+        <v>-42100</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-37600</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-37500</v>
-      </c>
-      <c r="AH96" s="3">
-        <v>-37300</v>
       </c>
       <c r="AI96" s="3">
         <v>-37300</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>-37300</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9025,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9129,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,307 +9233,319 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>957000</v>
+      </c>
+      <c r="E100" s="3">
         <v>175000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1932200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1648000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-820000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>171400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>423700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1250000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>385000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-54000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>543000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-507400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>634100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>694200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1305100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-351800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>83300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>137800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>244600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-503200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>49600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-115400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>124000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-836700</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>1197000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>120500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>33900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>63100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-172600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>179800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>57700</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-475400</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>241200</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-300</v>
+        <v>-5000</v>
       </c>
       <c r="E101" s="3">
-        <v>-4600</v>
+        <v>3100</v>
       </c>
       <c r="F101" s="3">
-        <v>5200</v>
+        <v>1600</v>
       </c>
       <c r="G101" s="3">
-        <v>-5000</v>
+        <v>6200</v>
       </c>
       <c r="H101" s="3">
-        <v>3100</v>
+        <v>-10600</v>
       </c>
       <c r="I101" s="3">
-        <v>1600</v>
+        <v>-8600</v>
       </c>
       <c r="J101" s="3">
+        <v>300</v>
+      </c>
+      <c r="K101" s="3">
         <v>6000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-11000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-8000</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
-      </c>
       <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3">
         <v>2800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-5600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>2000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>800</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>9200</v>
-      </c>
-      <c r="S101" s="3">
-        <v>4400</v>
       </c>
       <c r="T101" s="3">
         <v>4400</v>
       </c>
       <c r="U101" s="3">
+        <v>4400</v>
+      </c>
+      <c r="V101" s="3">
         <v>-11900</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>4000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-3400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>2000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-3900</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-2200</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-2300</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>1000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>600</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>3300</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>3000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>1300</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-4800</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>904800</v>
+      </c>
+      <c r="E102" s="3">
         <v>542200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-2098900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>2026200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-666800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>262500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>759900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1137000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>616000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>41000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>476000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-725500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-268700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>196700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>750600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-236900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-11000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>473400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-436000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-225000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>299000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>74900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-130100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-738200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>978800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>49900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-210600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>245300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-24800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>119300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>41300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-437200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>201500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FAF_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FAF_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="92">
   <si>
     <t>FAF</t>
   </si>
@@ -656,286 +656,292 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43738</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42916</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42825</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1685100</v>
+      </c>
+      <c r="E8" s="3">
         <v>1406100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1612300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1424600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1429300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1481200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1646900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1446100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1715000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1975000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2139000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2105000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2533100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2555900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2266400</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2025700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2151300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1913700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1608700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1412900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1728700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1671200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1498600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1303600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1417100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1542200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1491200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1297400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1481300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1519600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1454400</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1317000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1504300</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1508300</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>637100</v>
+      </c>
+      <c r="E9" s="3">
         <v>638500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>571700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>517300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>528800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>622500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>585900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>551300</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L9" s="3" t="s">
         <v>5</v>
       </c>
@@ -1011,35 +1017,38 @@
       <c r="AJ9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1048000</v>
+      </c>
+      <c r="E10" s="3">
         <v>767600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1040600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>907300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>900500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>858700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1061000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>894800</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="L10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1115,8 +1124,11 @@
       <c r="AJ10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1153,8 +1165,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1257,8 +1270,11 @@
       <c r="AJ12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1361,8 +1377,11 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1387,39 +1406,39 @@
       <c r="J14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>5</v>
+      <c r="M14" s="3">
+        <v>0</v>
       </c>
       <c r="N14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>5</v>
+      <c r="Q14" s="3">
+        <v>0</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S14" s="3">
+      <c r="S14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="T14" s="3">
         <v>-18300</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>73300</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="V14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1435,8 +1454,8 @@
       <c r="Z14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
+      <c r="AA14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AB14" s="3">
         <v>0</v>
@@ -1465,112 +1484,118 @@
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>52000</v>
+      </c>
+      <c r="E15" s="3">
         <v>53200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>52100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>50100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>49600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>47300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>46100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>45500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>43000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>41000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>42000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>41000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>39500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>39200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>40900</v>
-      </c>
-      <c r="R15" s="3">
-        <v>38300</v>
       </c>
       <c r="S15" s="3">
         <v>38300</v>
       </c>
       <c r="T15" s="3">
+        <v>38300</v>
+      </c>
+      <c r="U15" s="3">
         <v>38200</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>41000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>31400</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>31500</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>31700</v>
-      </c>
-      <c r="Y15" s="3">
-        <v>32900</v>
       </c>
       <c r="Z15" s="3">
         <v>32900</v>
       </c>
       <c r="AA15" s="3">
+        <v>32900</v>
+      </c>
+      <c r="AB15" s="3">
         <v>33400</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>31700</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>31100</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>29700</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>31800</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>36000</v>
-      </c>
-      <c r="AG15" s="3">
-        <v>30100</v>
       </c>
       <c r="AH15" s="3">
         <v>30100</v>
       </c>
       <c r="AI15" s="3">
+        <v>30100</v>
+      </c>
+      <c r="AJ15" s="3">
         <v>28100</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>24500</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1604,216 +1629,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1541500</v>
+      </c>
+      <c r="E17" s="3">
         <v>1514300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1425300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1332000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1357600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1447100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1434500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1357400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1597000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1803000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1902000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1884000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2019500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1933500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1850700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1703200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1753000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1654400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1370000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1328500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1428400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1413600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1257200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1150000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1287200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1335800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1279200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1195100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1312800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1492500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1261300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1224400</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1414000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1333600</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>143600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-108200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>187000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>92600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>71700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>34100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>212400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>88700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>118000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>172000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>237000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>221000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>513600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>622400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>415700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>322500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>398300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>259300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>238700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>84400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>300300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>257600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>241400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>153600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>129900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>206400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>212000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>102300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>168500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>27100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>193100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>92600</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>90300</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>174700</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1850,8 +1882,9 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1876,24 +1909,24 @@
       <c r="J20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L20" s="3">
         <v>-30000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-151000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-77000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-71000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-160100</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
         <v>0</v>
       </c>
@@ -1954,424 +1987,439 @@
       <c r="AJ20" s="3">
         <v>0</v>
       </c>
+      <c r="AK20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>195600</v>
+      </c>
+      <c r="E21" s="3">
         <v>-55000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>239100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>142700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>121300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>81400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>258500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>134200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>131000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>62000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>202000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>191000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>393000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>661600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>456600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>360800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>436600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>297600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>279700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>115900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>331700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>289300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>274300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>186500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>163300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>238100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>243000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>132000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>200300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>63100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>223300</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>122700</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>118400</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>199300</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>43700</v>
+      </c>
+      <c r="E22" s="3">
         <v>36200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>35400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>34300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>33300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>35800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>34300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>29100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>30000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>24000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>19000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>20000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>20100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>19200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>16200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>16500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>15900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>16000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>13400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>12100</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>11700</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>12200</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>11900</v>
       </c>
       <c r="Z22" s="3">
         <v>11900</v>
       </c>
       <c r="AA22" s="3">
+        <v>11900</v>
+      </c>
+      <c r="AB22" s="3">
         <v>11000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>10800</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>10000</v>
-      </c>
-      <c r="AD22" s="3">
-        <v>9200</v>
       </c>
       <c r="AE22" s="3">
         <v>9200</v>
       </c>
       <c r="AF22" s="3">
+        <v>9200</v>
+      </c>
+      <c r="AG22" s="3">
         <v>9100</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>9000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>8700</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>8800</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>7800</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>99900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-144400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>151600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>58300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>38400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-1700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>178100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>59600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>58000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-3000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>141000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>130000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>333400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>603200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>399400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>306000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>382300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>243400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>225300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>72300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>288500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>245300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>229500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>141700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>118900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>195600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>202000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>93100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>159300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>18000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>184200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>83900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>81500</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>166900</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>27000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-41000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>35200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>11600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>4100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>41700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>13600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>4000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-6000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>31000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>32000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>72700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>152700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>96000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>71600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>100900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>59800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>53600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>8500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>63900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>57200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>42200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>31900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>25700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>44100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>46900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>16900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>52700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-3200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>62300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>25800</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>500</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>59500</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2474,216 +2522,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>72900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-103400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>116400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>46700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>34300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-1200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>136400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>46000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>54000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>3000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>110000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>98000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>260700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>450500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>303400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>234500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>281400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>183600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>171700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>63800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>224600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>188200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>187300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>109800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>93200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>151500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>155100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>76200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>106600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>21200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>121900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>58100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>81000</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>107400</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>72400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-104000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>116000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>46700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>34100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-1700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>138500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>45900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>54000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>109000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>98000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>259800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>445300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>302300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>233600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>280300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>182300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>170700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>63200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>224000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>187200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>186700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>109600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>91600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>151500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>155100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>76200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>107000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>21400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>122300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>58300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>81000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>107300</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2786,8 +2843,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2854,8 +2914,8 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>5</v>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>5</v>
@@ -2872,12 +2932,12 @@
       <c r="AD29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AF29" s="3">
         <v>114100</v>
       </c>
-      <c r="AF29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AG29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2890,8 +2950,11 @@
       <c r="AJ29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AK29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2994,8 +3057,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3098,8 +3164,11 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3124,24 +3193,24 @@
       <c r="J32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L32" s="3">
         <v>30000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>151000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>77000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>71000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>160100</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
         <v>0</v>
       </c>
@@ -3202,112 +3271,118 @@
       <c r="AJ32" s="3">
         <v>0</v>
       </c>
+      <c r="AK32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>72400</v>
+      </c>
+      <c r="E33" s="3">
         <v>-104000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>116000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>46700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>34100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-1700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>138500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>45900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>54000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>109000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>98000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>259800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>445300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>302300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>233600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>280300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>182300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>170700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>63200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>224000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>187200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>186700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>109600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>91600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>151500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>155100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>76200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>221100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>21400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>122300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>58300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>81000</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>107300</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3410,221 +3485,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>72400</v>
+      </c>
+      <c r="E35" s="3">
         <v>-104000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>116000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>46700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>34100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-1700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>138500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>45900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>54000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>109000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>98000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>259800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>445300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>302300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>233600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>280300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>182300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>170700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>63200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>224000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>187200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>186700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>109600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>91600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>151500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>155100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>76200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>221100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>21400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>122300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>58300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>81000</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>107300</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43738</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42916</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42825</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3661,8 +3745,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3699,139 +3784,143 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1718100</v>
+      </c>
+      <c r="E41" s="3">
         <v>2953400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2048600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1506400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3605300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1579100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2245900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1983400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1224000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2361000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1745000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1704000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1228000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1954000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2222700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2026000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1275500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1512400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1523300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1050000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1486000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1711000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1412000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1337100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1467100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>2205300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1226500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1176600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1387200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1141900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1166800</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1047500</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1006100</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1443300</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>85400</v>
+      </c>
+      <c r="E42" s="3">
         <v>55400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>56400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>77100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>55800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>55300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>55900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>53500</v>
       </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
         <v>0</v>
       </c>
@@ -3907,35 +3996,38 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1126100</v>
+      </c>
+      <c r="E43" s="3">
         <v>1429300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1192400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1268200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1221600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1077600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1106900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>980300</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
-      </c>
       <c r="L43" s="3">
         <v>0</v>
       </c>
@@ -4011,8 +4103,11 @@
       <c r="AJ43" s="3">
         <v>0</v>
       </c>
+      <c r="AK43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4037,8 +4132,8 @@
       <c r="J44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -4115,8 +4210,11 @@
       <c r="AJ44" s="3">
         <v>0</v>
       </c>
+      <c r="AK44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4141,8 +4239,8 @@
       <c r="J45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
+      <c r="K45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="L45" s="3">
         <v>0</v>
@@ -4219,35 +4317,38 @@
       <c r="AJ45" s="3">
         <v>0</v>
       </c>
+      <c r="AK45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2929600</v>
+      </c>
+      <c r="E46" s="3">
         <v>4438100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3297400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2851700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4882700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2712000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3408700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3017200</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
       <c r="L46" s="3">
         <v>0</v>
       </c>
@@ -4323,320 +4424,332 @@
       <c r="AJ46" s="3">
         <v>0</v>
       </c>
+      <c r="AK46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>7864800</v>
+      </c>
+      <c r="E47" s="3">
         <v>7641800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>7696100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>7697500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>7786100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>7837100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>8224800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>8307600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>9799000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>10234000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>10657000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>11249000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>11613000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>11450200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>9954100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>9253100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>8349200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>7823500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>7593200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>7445500</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>7212300</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>7277700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>7200600</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>6991800</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>6638500</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>6637000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>6196700</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>5893500</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>5728100</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>5743600</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>5789900</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>5493600</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>5508500</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>5489500</v>
       </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>966000</v>
+      </c>
+      <c r="E48" s="3">
         <v>1013100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>996900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>984000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>982100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>967900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>943600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>907000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>885000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>851000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>824000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>766000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>755000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>716200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>705300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>700400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>715000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>714800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>741000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>783900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>738200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>740300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>756400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>767600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>457800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>457500</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>446300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>435900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>439600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>438100</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>433000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>429000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>434100</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>430600</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2603400</v>
+      </c>
+      <c r="E49" s="3">
         <v>2613800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2609600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2611100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2613700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2610300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2620700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2634200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1992000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2016000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2023000</v>
-      </c>
-      <c r="N49" s="3">
-        <v>1806000</v>
       </c>
       <c r="O49" s="3">
         <v>1806000</v>
       </c>
       <c r="P49" s="3">
+        <v>1806000</v>
+      </c>
+      <c r="Q49" s="3">
         <v>1604900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1556000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1558200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1573100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1552000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1591900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1565500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1242700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1242600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1246700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1247800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1253500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1256700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1271200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1229400</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1212900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1220600</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1109800</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1095800</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>1096300</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>1066200</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4739,8 +4852,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4843,37 +4959,40 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>466600</v>
+      </c>
+      <c r="E52" s="3">
         <v>809500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>507200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>503400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>465700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>495800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>478600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>463000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>54000</v>
-      </c>
-      <c r="L52" s="3">
-        <v>14000</v>
       </c>
       <c r="M52" s="3">
         <v>14000</v>
@@ -4885,7 +5004,7 @@
         <v>14000</v>
       </c>
       <c r="P52" s="3">
-        <v>14500</v>
+        <v>14000</v>
       </c>
       <c r="Q52" s="3">
         <v>14500</v>
@@ -4897,10 +5016,10 @@
         <v>14500</v>
       </c>
       <c r="T52" s="3">
+        <v>14500</v>
+      </c>
+      <c r="U52" s="3">
         <v>216600</v>
-      </c>
-      <c r="U52" s="3">
-        <v>18300</v>
       </c>
       <c r="V52" s="3">
         <v>18300</v>
@@ -4909,7 +5028,7 @@
         <v>18300</v>
       </c>
       <c r="X52" s="3">
-        <v>16600</v>
+        <v>18300</v>
       </c>
       <c r="Y52" s="3">
         <v>16600</v>
@@ -4921,7 +5040,7 @@
         <v>16600</v>
       </c>
       <c r="AB52" s="3">
-        <v>22800</v>
+        <v>16600</v>
       </c>
       <c r="AC52" s="3">
         <v>22800</v>
@@ -4933,7 +5052,7 @@
         <v>22800</v>
       </c>
       <c r="AF52" s="3">
-        <v>20000</v>
+        <v>22800</v>
       </c>
       <c r="AG52" s="3">
         <v>20000</v>
@@ -4945,10 +5064,13 @@
         <v>20000</v>
       </c>
       <c r="AJ52" s="3">
+        <v>20000</v>
+      </c>
+      <c r="AK52" s="3">
         <v>22000</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5051,112 +5173,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>14908600</v>
+      </c>
+      <c r="E54" s="3">
         <v>16566400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>15157300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>14697800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>16802800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>14677600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>15730900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>15383500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>14955000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>16486000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>16262000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>16527000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>16451000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>16686100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>15426900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>14431900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>12796000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>12638800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>12288000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>11675500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>11519200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>11804100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>11443200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>11160300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>10630600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>11380100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>9959400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>9546800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>9573200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>9347000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>9314300</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>8874400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>8831800</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>9246500</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5193,8 +5321,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5231,139 +5360,143 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1260100</v>
+      </c>
+      <c r="E57" s="3">
         <v>2127200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2159200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2006600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1345700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2110400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2111900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2035000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>915000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1115000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1015000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1051000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1262000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1252000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1070800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1113400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>979700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>830100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>781500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>664000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>820400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>812500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>709300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>631500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>778700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>826700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>770700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>709600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>793200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>741600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>697000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>675800</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>794000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>813900</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>726000</v>
+      </c>
+      <c r="E58" s="3">
         <v>878200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>641500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>688800</v>
       </c>
-      <c r="G58" s="3">
-        <v>638800</v>
-      </c>
       <c r="H58" s="3">
+        <v>553300</v>
+      </c>
+      <c r="I58" s="3">
         <v>530400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>585700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>502900</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
       <c r="L58" s="3">
         <v>0</v>
       </c>
@@ -5439,139 +5572,145 @@
       <c r="AJ58" s="3">
         <v>0</v>
       </c>
+      <c r="AK58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5248400</v>
+      </c>
+      <c r="E59" s="3">
         <v>6086900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>5633200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5318500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>7484300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>5621300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>6377900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>6204700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>7124000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>8324000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>7723000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>7346000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>6651000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>7043200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>6920600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>6154000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>4804500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>4918800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>4925200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>4850100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>4748700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>5305000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>5265900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>5344000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>4837900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>5581000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>4326100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>4187700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>4104100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>4079900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>4208900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>3926300</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>3815700</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>4302200</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>7937800</v>
+      </c>
+      <c r="E60" s="3">
         <v>9092300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>8433900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>8013900</v>
       </c>
-      <c r="G60" s="3">
-        <v>10124600</v>
-      </c>
       <c r="H60" s="3">
+        <v>10039100</v>
+      </c>
+      <c r="I60" s="3">
         <v>8262100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>9075500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>8742600</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
       <c r="L60" s="3">
         <v>0</v>
       </c>
@@ -5647,112 +5786,118 @@
       <c r="AJ60" s="3">
         <v>0</v>
       </c>
+      <c r="AK60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1694300</v>
+      </c>
+      <c r="E61" s="3">
         <v>2089900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1636700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1631400</v>
       </c>
-      <c r="G61" s="3">
-        <v>1555000</v>
-      </c>
       <c r="H61" s="3">
+        <v>1640500</v>
+      </c>
+      <c r="I61" s="3">
         <v>1647000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1656500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1659100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2012000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1988000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2075000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2205000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2186000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2242500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1619200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1655000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1526900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1538300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1489200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1288800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1006600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>961800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>919700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>858600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>808300</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>821800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>832600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>731500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>732800</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>734100</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>734500</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>735500</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>736700</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>737900</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5777,23 +5922,23 @@
       <c r="J62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K62" s="3">
+      <c r="K62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L62" s="3">
         <v>19000</v>
-      </c>
-      <c r="L62" s="3">
-        <v>314000</v>
       </c>
       <c r="M62" s="3">
         <v>314000</v>
       </c>
       <c r="N62" s="3">
-        <v>345000</v>
+        <v>314000</v>
       </c>
       <c r="O62" s="3">
         <v>345000</v>
       </c>
       <c r="P62" s="3">
-        <v>291200</v>
+        <v>345000</v>
       </c>
       <c r="Q62" s="3">
         <v>291200</v>
@@ -5805,10 +5950,10 @@
         <v>291200</v>
       </c>
       <c r="T62" s="3">
+        <v>291200</v>
+      </c>
+      <c r="U62" s="3">
         <v>414400</v>
-      </c>
-      <c r="U62" s="3">
-        <v>266100</v>
       </c>
       <c r="V62" s="3">
         <v>266100</v>
@@ -5817,7 +5962,7 @@
         <v>266100</v>
       </c>
       <c r="X62" s="3">
-        <v>217100</v>
+        <v>266100</v>
       </c>
       <c r="Y62" s="3">
         <v>217100</v>
@@ -5829,7 +5974,7 @@
         <v>217100</v>
       </c>
       <c r="AB62" s="3">
-        <v>219300</v>
+        <v>217100</v>
       </c>
       <c r="AC62" s="3">
         <v>219300</v>
@@ -5841,7 +5986,7 @@
         <v>219300</v>
       </c>
       <c r="AF62" s="3">
-        <v>242200</v>
+        <v>219300</v>
       </c>
       <c r="AG62" s="3">
         <v>242200</v>
@@ -5853,10 +5998,13 @@
         <v>242200</v>
       </c>
       <c r="AJ62" s="3">
+        <v>242200</v>
+      </c>
+      <c r="AK62" s="3">
         <v>133100</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5959,8 +6107,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6063,8 +6214,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6167,112 +6321,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>9981600</v>
+      </c>
+      <c r="E66" s="3">
         <v>11455800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>10324700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>9891900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>11940000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>10135600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>10944000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>10604600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>10290000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>11978000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>11346000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>11164000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>10684000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>11088900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>10163100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>9476600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>7886000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>7915000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>7722600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>7316100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>7098700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>7562000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>7358300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>7282200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>6888800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>7705900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>6389900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>6076300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>6093300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>6053200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>6120900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>5802000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>5823600</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>6224200</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6309,8 +6469,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6413,8 +6574,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6517,8 +6681,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6621,8 +6788,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6725,112 +6895,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3617300</v>
+      </c>
+      <c r="E72" s="3">
         <v>3601400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>3761900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3701600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3710600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>3739000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>3796200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>3712300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>3721000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>3722000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>3775000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>3721000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>3680000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>3476900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>3088600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2837200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2655500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2426900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2294600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2173700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>2161000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>1985100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1845900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1707100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1644200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1600300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1496600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>1384700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1311100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>1129000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>1150600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>1066700</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>1046800</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>1012500</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6933,8 +7109,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7037,8 +7216,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7141,112 +7323,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4908500</v>
+      </c>
+      <c r="E76" s="3">
         <v>5092200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4813600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4787100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4848100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4527200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4772400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4756500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4665000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4508000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4916000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>5363000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>5767000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>5597100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>5263700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>4955300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>4910000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>4723800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>4565400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>4359300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>4420500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>4242100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>4084900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>3878000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>3741900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>3674200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>3569500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>3470500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>3480000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>3293900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>3193400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>3072500</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>3008200</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>3022300</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7349,221 +7537,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43738</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42916</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42825</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>72400</v>
+      </c>
+      <c r="E81" s="3">
         <v>-104000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>116000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>46700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>34100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-1700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>138500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>45900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>54000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>109000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>98000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>259800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>445300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>302300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>233600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>280300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>182300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>170700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>63200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>224000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>187200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>186700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>109600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>91600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>151500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>155100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>76200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>221100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>21400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>122300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>58300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>81000</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>107300</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7600,112 +7797,116 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>37100</v>
+      </c>
+      <c r="E83" s="3">
         <v>34400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>33500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>32000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>30800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>29700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>27700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>26100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>43000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>41000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>42000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>41000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>39500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>39200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>40900</v>
-      </c>
-      <c r="R83" s="3">
-        <v>38300</v>
       </c>
       <c r="S83" s="3">
         <v>38300</v>
       </c>
       <c r="T83" s="3">
+        <v>38300</v>
+      </c>
+      <c r="U83" s="3">
         <v>38200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>41000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>31400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>31500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>31700</v>
-      </c>
-      <c r="Y83" s="3">
-        <v>32900</v>
       </c>
       <c r="Z83" s="3">
         <v>32900</v>
       </c>
       <c r="AA83" s="3">
+        <v>32900</v>
+      </c>
+      <c r="AB83" s="3">
         <v>33400</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>31700</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>31100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>29700</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>31800</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>36000</v>
-      </c>
-      <c r="AG83" s="3">
-        <v>30100</v>
       </c>
       <c r="AH83" s="3">
         <v>30100</v>
       </c>
       <c r="AI83" s="3">
+        <v>30100</v>
+      </c>
+      <c r="AJ83" s="3">
         <v>28100</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>24500</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7808,8 +8009,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7912,8 +8116,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8016,8 +8223,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8120,8 +8330,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8224,112 +8437,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>324600</v>
+      </c>
+      <c r="E89" s="3">
         <v>236900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>266700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>69300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-41700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>219300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>269000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-92300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>247000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>304000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>189000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>40000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>344000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>399000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>253100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>223900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>425200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>291500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>343800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>24200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>301400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>310600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>266600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>34500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>308300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>230800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>210900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>43200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>176600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>220900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>228500</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>6100</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>237200</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>105800</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8366,112 +8585,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-58400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-51500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-56700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-51700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-58100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-65800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-76400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-63100</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-71000</v>
       </c>
       <c r="L91" s="3">
         <v>-71000</v>
       </c>
       <c r="M91" s="3">
+        <v>-71000</v>
+      </c>
+      <c r="N91" s="3">
         <v>-75000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-43000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-49900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-43500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-39000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-28600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-22500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-33600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-28800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-29200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-28800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-24200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-26600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-27400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-30900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-31600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-33400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-22300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-31100</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-33500</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-39700</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-29900</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-28500</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-42800</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8574,8 +8797,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8678,112 +8904,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-33100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-295000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>100800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-231400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>414700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-61100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-181000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>426900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-140000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-62000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-86000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-107000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-565000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-1296100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-752600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-779300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-319500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-390100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-12700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-692800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-27200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-57700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-76700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-290600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-205900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-446800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-279300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-288700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>5000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-76400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-292000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-23700</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-194200</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-145100</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8820,112 +9052,116 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>55500</v>
+      </c>
+      <c r="E96" s="3">
         <v>55600</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>54700</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>54900</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>54500</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>54700</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>53600</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>53800</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-53000</v>
-      </c>
-      <c r="L96" s="3">
-        <v>-54000</v>
       </c>
       <c r="M96" s="3">
         <v>-54000</v>
       </c>
       <c r="N96" s="3">
+        <v>-54000</v>
+      </c>
+      <c r="O96" s="3">
         <v>-56000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-55900</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-56000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-50100</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-51000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-50900</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-49100</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-49000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-49700</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-47200</v>
-      </c>
-      <c r="X96" s="3">
-        <v>-47100</v>
       </c>
       <c r="Y96" s="3">
         <v>-47100</v>
       </c>
       <c r="Z96" s="3">
+        <v>-47100</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-47000</v>
-      </c>
-      <c r="AA96" s="3">
-        <v>-46900</v>
       </c>
       <c r="AB96" s="3">
         <v>-46900</v>
       </c>
       <c r="AC96" s="3">
+        <v>-46900</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-42400</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-42300</v>
-      </c>
-      <c r="AE96" s="3">
-        <v>-42100</v>
       </c>
       <c r="AF96" s="3">
         <v>-42100</v>
       </c>
       <c r="AG96" s="3">
+        <v>-42100</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-37600</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-37500</v>
-      </c>
-      <c r="AI96" s="3">
-        <v>-37300</v>
       </c>
       <c r="AJ96" s="3">
         <v>-37300</v>
       </c>
+      <c r="AK96" s="3">
+        <v>-37300</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9028,8 +9264,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9132,8 +9371,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9236,316 +9478,328 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1509200</v>
+      </c>
+      <c r="E100" s="3">
         <v>957000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>175000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-1932200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1648000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-820000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>171400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>423700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1250000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>385000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-54000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>543000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-507400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>634100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>694200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1305100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-351800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>83300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>137800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>244600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-503200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>49600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-115400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>124000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-836700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>1197000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>120500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>33900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>63100</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-172600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>179800</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>57700</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-475400</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>241200</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E101" s="3">
         <v>-5000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>3100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>1600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>6200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-10600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-8600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>6000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-11000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-8000</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
       <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3">
         <v>2800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-5600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>2000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>800</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>9200</v>
-      </c>
-      <c r="T101" s="3">
-        <v>4400</v>
       </c>
       <c r="U101" s="3">
         <v>4400</v>
       </c>
       <c r="V101" s="3">
+        <v>4400</v>
+      </c>
+      <c r="W101" s="3">
         <v>-11900</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>4000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-3400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>2000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-3900</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-2200</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-2300</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>1000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>600</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>3300</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>3000</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>1300</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-4800</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1235300</v>
+      </c>
+      <c r="E102" s="3">
         <v>904800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>542200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-2098900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2026200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-666800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>262500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>759900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-1137000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>616000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>41000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>476000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-725500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-268700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>196700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>750600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-236900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-11000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>473400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-436000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-225000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>299000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>74900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-130100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-738200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>978800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>49900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-210600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>245300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-24800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>119300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>41300</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-437200</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>201500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FAF_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FAF_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="92">
   <si>
     <t>FAF</t>
   </si>
@@ -656,295 +656,302 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43738</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42916</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1582300</v>
+      </c>
+      <c r="E8" s="3">
         <v>1685100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1406100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1612300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1424600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1429300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1481200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1646900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1446100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1715000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1975000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2139000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2105000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2533100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2555900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2266400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2025700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2151300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1913700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1608700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1412900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1728700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1671200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1498600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1303600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1417100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1542200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1491200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1297400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1481300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1519600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1454400</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1317000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1504300</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1508300</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>595600</v>
+      </c>
+      <c r="E9" s="3">
         <v>637100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>638500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>571700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>517300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>528800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>622500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>585900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>551300</v>
       </c>
-      <c r="L9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M9" s="3" t="s">
         <v>5</v>
       </c>
@@ -1020,38 +1027,41 @@
       <c r="AK9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>986700</v>
+      </c>
+      <c r="E10" s="3">
         <v>1048000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>767600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1040600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>907300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>900500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>858700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1061000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>894800</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="M10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1127,8 +1137,11 @@
       <c r="AK10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1166,8 +1179,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1273,8 +1287,11 @@
       <c r="AK12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1380,8 +1397,11 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1409,39 +1429,39 @@
       <c r="K14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>5</v>
+      <c r="N14" s="3">
+        <v>0</v>
       </c>
       <c r="O14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>5</v>
+      <c r="R14" s="3">
+        <v>0</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T14" s="3">
+      <c r="T14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="U14" s="3">
         <v>-18300</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>73300</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="W14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1457,8 +1477,8 @@
       <c r="AA14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
+      <c r="AB14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AC14" s="3">
         <v>0</v>
@@ -1487,115 +1507,121 @@
       <c r="AK14" s="3">
         <v>0</v>
       </c>
+      <c r="AL14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>52500</v>
+      </c>
+      <c r="E15" s="3">
         <v>52000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>53200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>52100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>50100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>49600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>47300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>46100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>45500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>43000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>41000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>42000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>41000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>39500</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>39200</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>40900</v>
-      </c>
-      <c r="S15" s="3">
-        <v>38300</v>
       </c>
       <c r="T15" s="3">
         <v>38300</v>
       </c>
       <c r="U15" s="3">
+        <v>38300</v>
+      </c>
+      <c r="V15" s="3">
         <v>38200</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>41000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>31400</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>31500</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>31700</v>
-      </c>
-      <c r="Z15" s="3">
-        <v>32900</v>
       </c>
       <c r="AA15" s="3">
         <v>32900</v>
       </c>
       <c r="AB15" s="3">
+        <v>32900</v>
+      </c>
+      <c r="AC15" s="3">
         <v>33400</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>31700</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>31100</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>29700</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>31800</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>36000</v>
-      </c>
-      <c r="AH15" s="3">
-        <v>30100</v>
       </c>
       <c r="AI15" s="3">
         <v>30100</v>
       </c>
       <c r="AJ15" s="3">
+        <v>30100</v>
+      </c>
+      <c r="AK15" s="3">
         <v>28100</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>24500</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1630,222 +1656,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1450500</v>
+      </c>
+      <c r="E17" s="3">
         <v>1541500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1514300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1425300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1332000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1357600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1447100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1434500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1357400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1597000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1803000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1902000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1884000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2019500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1933500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1850700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1703200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1753000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1654400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1370000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1328500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1428400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1413600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1257200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1150000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1287200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1335800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1279200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1195100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1312800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1492500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1261300</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1224400</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1414000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1333600</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>131800</v>
+      </c>
+      <c r="E18" s="3">
         <v>143600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-108200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>187000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>92600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>71700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>34100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>212400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>88700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>118000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>172000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>237000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>221000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>513600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>622400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>415700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>322500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>398300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>259300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>238700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>84400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>300300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>257600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>241400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>153600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>129900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>206400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>212000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>102300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>168500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>27100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>193100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>92600</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>90300</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>174700</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1883,8 +1916,9 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1912,24 +1946,24 @@
       <c r="K20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M20" s="3">
         <v>-30000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-151000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-77000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-71000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-160100</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
         <v>0</v>
       </c>
@@ -1990,436 +2024,451 @@
       <c r="AK20" s="3">
         <v>0</v>
       </c>
+      <c r="AL20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>184300</v>
+      </c>
+      <c r="E21" s="3">
         <v>195600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-55000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>239100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>142700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>121300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>81400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>258500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>134200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>131000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>62000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>202000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>191000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>393000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>661600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>456600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>360800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>436600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>297600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>279700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>115900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>331700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>289300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>274300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>186500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>163300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>238100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>243000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>132000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>200300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>63100</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>223300</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>122700</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>118400</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>199300</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>35200</v>
+      </c>
+      <c r="E22" s="3">
         <v>43700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>36200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>35400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>34300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>33300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>35800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>34300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>29100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>30000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>24000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>19000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>20000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>20100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>19200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>16200</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>16500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>15900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>16000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>13400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>12100</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>11700</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>12200</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>11900</v>
       </c>
       <c r="AA22" s="3">
         <v>11900</v>
       </c>
       <c r="AB22" s="3">
+        <v>11900</v>
+      </c>
+      <c r="AC22" s="3">
         <v>11000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>10800</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>10000</v>
-      </c>
-      <c r="AE22" s="3">
-        <v>9200</v>
       </c>
       <c r="AF22" s="3">
         <v>9200</v>
       </c>
       <c r="AG22" s="3">
+        <v>9200</v>
+      </c>
+      <c r="AH22" s="3">
         <v>9100</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>9000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>8700</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>8800</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>7800</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>96600</v>
+      </c>
+      <c r="E23" s="3">
         <v>99900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-144400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>151600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>58300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>38400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-1700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>178100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>59600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>58000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-3000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>141000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>130000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>333400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>603200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>399400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>306000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>382300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>243400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>225300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>72300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>288500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>245300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>229500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>141700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>118900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>195600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>202000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>93100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>159300</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>18000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>184200</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>83900</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>81500</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>166900</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>21800</v>
+      </c>
+      <c r="E24" s="3">
         <v>27000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-41000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>35200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>11600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>4100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>41700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>13600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>4000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-6000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>31000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>32000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>72700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>152700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>96000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>71600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>100900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>59800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>53600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>8500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>63900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>57200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>42200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>31900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>25700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>44100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>46900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>16900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>52700</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-3200</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>62300</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>25800</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>500</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>59500</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2525,222 +2574,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>74800</v>
+      </c>
+      <c r="E26" s="3">
         <v>72900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-103400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>116400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>46700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>34300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-1200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>136400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>46000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>54000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>3000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>110000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>98000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>260700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>450500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>303400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>234500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>281400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>183600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>171700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>63800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>224600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>188200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>187300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>109800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>93200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>151500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>155100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>76200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>106600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>21200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>121900</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>58100</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>81000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>107400</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>74200</v>
+      </c>
+      <c r="E27" s="3">
         <v>72400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-104000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>116000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>46700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>34100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-1700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>138500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>45900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>54000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>109000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>98000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>259800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>445300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>302300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>233600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>280300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>182300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>170700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>63200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>224000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>187200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>186700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>109600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>91600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>151500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>155100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>76200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>107000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>21400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>122300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>58300</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>81000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>107300</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2846,8 +2904,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2917,8 +2978,8 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>5</v>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>5</v>
@@ -2935,12 +2996,12 @@
       <c r="AE29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AF29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AG29" s="3">
         <v>114100</v>
       </c>
-      <c r="AG29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AH29" s="3" t="s">
         <v>5</v>
       </c>
@@ -2953,8 +3014,11 @@
       <c r="AK29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AL29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3060,8 +3124,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3167,8 +3234,11 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3196,24 +3266,24 @@
       <c r="K32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M32" s="3">
         <v>30000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>151000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>77000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>71000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>160100</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
         <v>0</v>
       </c>
@@ -3274,115 +3344,121 @@
       <c r="AK32" s="3">
         <v>0</v>
       </c>
+      <c r="AL32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>74200</v>
+      </c>
+      <c r="E33" s="3">
         <v>72400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-104000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>116000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>46700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>34100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-1700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>138500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>45900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>54000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>109000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>98000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>259800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>445300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>302300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>233600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>280300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>182300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>170700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>63200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>224000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>187200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>186700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>109600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>91600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>151500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>155100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>76200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>221100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>21400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>122300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>58300</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>81000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>107300</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3488,227 +3564,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>74200</v>
+      </c>
+      <c r="E35" s="3">
         <v>72400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-104000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>116000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>46700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>34100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-1700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>138500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>45900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>54000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>109000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>98000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>259800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>445300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>302300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>233600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>280300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>182300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>170700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>63200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>224000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>187200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>186700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>109600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>91600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>151500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>155100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>76200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>221100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>21400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>122300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>58300</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>81000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>107300</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43738</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42916</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3746,8 +3831,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3785,145 +3871,149 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2045100</v>
+      </c>
+      <c r="E41" s="3">
         <v>1718100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2953400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2048600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1506400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3605300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>1579100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2245900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1983400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1224000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2361000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1745000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1704000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1228000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1954000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>2222700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2026000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1275500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1512400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1523300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1050000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1486000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1711000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1412000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1337100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1467100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2205300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1226500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1176600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1387200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1141900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1166800</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1047500</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1006100</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>1443300</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>62800</v>
+      </c>
+      <c r="E42" s="3">
         <v>85400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>55400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>56400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>77100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>55800</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>55300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>55900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>53500</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
@@ -3999,38 +4089,41 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1248300</v>
+      </c>
+      <c r="E43" s="3">
         <v>1126100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1429300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1192400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1268200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1221600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1077600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1106900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>980300</v>
       </c>
-      <c r="L43" s="3">
-        <v>0</v>
-      </c>
       <c r="M43" s="3">
         <v>0</v>
       </c>
@@ -4106,8 +4199,11 @@
       <c r="AK43" s="3">
         <v>0</v>
       </c>
+      <c r="AL43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4135,8 +4231,8 @@
       <c r="K44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -4213,8 +4309,11 @@
       <c r="AK44" s="3">
         <v>0</v>
       </c>
+      <c r="AL44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4242,8 +4341,8 @@
       <c r="K45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L45" s="3">
-        <v>0</v>
+      <c r="L45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M45" s="3">
         <v>0</v>
@@ -4320,38 +4419,41 @@
       <c r="AK45" s="3">
         <v>0</v>
       </c>
+      <c r="AL45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3356200</v>
+      </c>
+      <c r="E46" s="3">
         <v>2929600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4438100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3297400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2851700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4882700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2712000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3408700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3017200</v>
       </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -4427,329 +4529,341 @@
       <c r="AK46" s="3">
         <v>0</v>
       </c>
+      <c r="AL46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>8017200</v>
+      </c>
+      <c r="E47" s="3">
         <v>7864800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>7641800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>7696100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>7697500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>7786100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>7837100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>8224800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>8307600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>9799000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>10234000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>10657000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>11249000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>11613000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>11450200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>9954100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>9253100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>8349200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>7823500</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>7593200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>7445500</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>7212300</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>7277700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>7200600</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>6991800</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>6638500</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>6637000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>6196700</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>5893500</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>5728100</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>5743600</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>5789900</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>5493600</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>5508500</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>5489500</v>
       </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>951000</v>
+      </c>
+      <c r="E48" s="3">
         <v>966000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>1013100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>996900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>984000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>982100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>967900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>943600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>907000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>885000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>851000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>824000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>766000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>755000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>716200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>705300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>700400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>715000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>714800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>741000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>783900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>738200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>740300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>756400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>767600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>457800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>457500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>446300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>435900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>439600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>438100</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>433000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>429000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>434100</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>430600</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2609600</v>
+      </c>
+      <c r="E49" s="3">
         <v>2603400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2613800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2609600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2611100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2613700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2610300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2620700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2634200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1992000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2016000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2023000</v>
-      </c>
-      <c r="O49" s="3">
-        <v>1806000</v>
       </c>
       <c r="P49" s="3">
         <v>1806000</v>
       </c>
       <c r="Q49" s="3">
+        <v>1806000</v>
+      </c>
+      <c r="R49" s="3">
         <v>1604900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1556000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1558200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1573100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1552000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1591900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1565500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1242700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1242600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1246700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1247800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1253500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1256700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1271200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1229400</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1212900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1220600</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1109800</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>1095800</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>1096300</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>1066200</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4855,8 +4969,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4962,40 +5079,43 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>519600</v>
+      </c>
+      <c r="E52" s="3">
         <v>466600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>809500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>507200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>503400</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>465700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>495800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>478600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>463000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>54000</v>
-      </c>
-      <c r="M52" s="3">
-        <v>14000</v>
       </c>
       <c r="N52" s="3">
         <v>14000</v>
@@ -5007,7 +5127,7 @@
         <v>14000</v>
       </c>
       <c r="Q52" s="3">
-        <v>14500</v>
+        <v>14000</v>
       </c>
       <c r="R52" s="3">
         <v>14500</v>
@@ -5019,10 +5139,10 @@
         <v>14500</v>
       </c>
       <c r="U52" s="3">
+        <v>14500</v>
+      </c>
+      <c r="V52" s="3">
         <v>216600</v>
-      </c>
-      <c r="V52" s="3">
-        <v>18300</v>
       </c>
       <c r="W52" s="3">
         <v>18300</v>
@@ -5031,7 +5151,7 @@
         <v>18300</v>
       </c>
       <c r="Y52" s="3">
-        <v>16600</v>
+        <v>18300</v>
       </c>
       <c r="Z52" s="3">
         <v>16600</v>
@@ -5043,7 +5163,7 @@
         <v>16600</v>
       </c>
       <c r="AC52" s="3">
-        <v>22800</v>
+        <v>16600</v>
       </c>
       <c r="AD52" s="3">
         <v>22800</v>
@@ -5055,7 +5175,7 @@
         <v>22800</v>
       </c>
       <c r="AG52" s="3">
-        <v>20000</v>
+        <v>22800</v>
       </c>
       <c r="AH52" s="3">
         <v>20000</v>
@@ -5067,10 +5187,13 @@
         <v>20000</v>
       </c>
       <c r="AK52" s="3">
+        <v>20000</v>
+      </c>
+      <c r="AL52" s="3">
         <v>22000</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5176,115 +5299,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>15497400</v>
+      </c>
+      <c r="E54" s="3">
         <v>14908600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>16566400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>15157300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>14697800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>16802800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>14677600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>15730900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>15383500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>14955000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>16486000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>16262000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>16527000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>16451000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>16686100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>15426900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>14431900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>12796000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>12638800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>12288000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>11675500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>11519200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>11804100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>11443200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>11160300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>10630600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>11380100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>9959400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>9546800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>9573200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>9347000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>9314300</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>8874400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>8831800</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>9246500</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5322,8 +5451,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5361,145 +5491,149 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1911000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1260100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2127200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2159200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2006600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1345700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2110400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2111900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2035000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>915000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1115000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1015000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1051000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1262000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1252000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1070800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1113400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>979700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>830100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>781500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>664000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>820400</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>812500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>709300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>631500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>778700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>826700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>770700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>709600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>793200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>741600</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>697000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>675800</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>794000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>813900</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>735800</v>
+      </c>
+      <c r="E58" s="3">
         <v>726000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>878200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>641500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>688800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>553300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>530400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>585700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>502900</v>
       </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -5575,145 +5709,151 @@
       <c r="AK58" s="3">
         <v>0</v>
       </c>
+      <c r="AL58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5698500</v>
+      </c>
+      <c r="E59" s="3">
         <v>5248400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>6086900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5633200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>5318500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>7484300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>5621300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>6377900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>6204700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>7124000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>8324000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>7723000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>7346000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>6651000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>7043200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>6920600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>6154000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>4804500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>4918800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>4925200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>4850100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>4748700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>5305000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>5265900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>5344000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>4837900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>5581000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>4326100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>4187700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>4104100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>4079900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>4208900</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>3926300</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>3815700</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>4302200</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>8345300</v>
+      </c>
+      <c r="E60" s="3">
         <v>7937800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>9092300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>8433900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>8013900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>10039100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>8262100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>9075500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>8742600</v>
       </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -5789,115 +5929,121 @@
       <c r="AK60" s="3">
         <v>0</v>
       </c>
+      <c r="AL60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1775900</v>
+      </c>
+      <c r="E61" s="3">
         <v>1694300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2089900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1636700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1631400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1640500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1647000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1656500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1659100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2012000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1988000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2075000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2205000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2186000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2242500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1619200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1655000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1526900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1538300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1489200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1288800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1006600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>961800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>919700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>858600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>808300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>821800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>832600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>731500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>732800</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>734100</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>734500</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>735500</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>736700</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>737900</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -5925,23 +6071,23 @@
       <c r="K62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="L62" s="3">
+      <c r="L62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M62" s="3">
         <v>19000</v>
-      </c>
-      <c r="M62" s="3">
-        <v>314000</v>
       </c>
       <c r="N62" s="3">
         <v>314000</v>
       </c>
       <c r="O62" s="3">
-        <v>345000</v>
+        <v>314000</v>
       </c>
       <c r="P62" s="3">
         <v>345000</v>
       </c>
       <c r="Q62" s="3">
-        <v>291200</v>
+        <v>345000</v>
       </c>
       <c r="R62" s="3">
         <v>291200</v>
@@ -5953,10 +6099,10 @@
         <v>291200</v>
       </c>
       <c r="U62" s="3">
+        <v>291200</v>
+      </c>
+      <c r="V62" s="3">
         <v>414400</v>
-      </c>
-      <c r="V62" s="3">
-        <v>266100</v>
       </c>
       <c r="W62" s="3">
         <v>266100</v>
@@ -5965,7 +6111,7 @@
         <v>266100</v>
       </c>
       <c r="Y62" s="3">
-        <v>217100</v>
+        <v>266100</v>
       </c>
       <c r="Z62" s="3">
         <v>217100</v>
@@ -5977,7 +6123,7 @@
         <v>217100</v>
       </c>
       <c r="AC62" s="3">
-        <v>219300</v>
+        <v>217100</v>
       </c>
       <c r="AD62" s="3">
         <v>219300</v>
@@ -5989,7 +6135,7 @@
         <v>219300</v>
       </c>
       <c r="AG62" s="3">
-        <v>242200</v>
+        <v>219300</v>
       </c>
       <c r="AH62" s="3">
         <v>242200</v>
@@ -6001,10 +6147,13 @@
         <v>242200</v>
       </c>
       <c r="AK62" s="3">
+        <v>242200</v>
+      </c>
+      <c r="AL62" s="3">
         <v>133100</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6110,8 +6259,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6217,8 +6369,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6324,115 +6479,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>10456500</v>
+      </c>
+      <c r="E66" s="3">
         <v>9981600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>11455800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>10324700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>9891900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>11940000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>10135600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>10944000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>10604600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>10290000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>11978000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>11346000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>11164000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>10684000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>11088900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>10163100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>9476600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>7886000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>7915000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>7722600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>7316100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>7098700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>7562000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>7358300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>7282200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>6888800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>7705900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>6389900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>6076300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>6093300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>6053200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>6120900</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>5802000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>5823600</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>6224200</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6470,8 +6631,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6577,8 +6739,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6684,8 +6849,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6791,8 +6959,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6898,115 +7069,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3634800</v>
+      </c>
+      <c r="E72" s="3">
         <v>3617300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>3601400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3761900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3701600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>3710600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>3739000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>3796200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>3712300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>3721000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>3722000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>3775000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>3721000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>3680000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>3476900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>3088600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2837200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2655500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2426900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2294600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>2173700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>2161000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1985100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1845900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1707100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1644200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1600300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>1496600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1384700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>1311100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>1129000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>1150600</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>1066700</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>1046800</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>1012500</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7112,8 +7289,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7219,8 +7399,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7326,115 +7509,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5019300</v>
+      </c>
+      <c r="E76" s="3">
         <v>4908500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5092200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4813600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4787100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4848100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4527200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4772400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4756500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4665000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4508000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4916000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>5363000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>5767000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>5597100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>5263700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>4955300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>4910000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>4723800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>4565400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>4359300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>4420500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>4242100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>4084900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>3878000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>3741900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>3674200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>3569500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>3470500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>3480000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>3293900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>3193400</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>3072500</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>3008200</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>3022300</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7540,227 +7729,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43738</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42916</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42825</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>74200</v>
+      </c>
+      <c r="E81" s="3">
         <v>72400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-104000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>116000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>46700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>34100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-1700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>138500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>45900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>54000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>109000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>98000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>259800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>445300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>302300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>233600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>280300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>182300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>170700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>63200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>224000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>187200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>186700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>109600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>91600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>151500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>155100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>76200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>221100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>21400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>122300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>58300</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>81000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>107300</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7798,115 +7996,119 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>37800</v>
+      </c>
+      <c r="E83" s="3">
         <v>37100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>34400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>33500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>32000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>30800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>29700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>27700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>26100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>43000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>41000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>42000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>41000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>39500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>39200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>40900</v>
-      </c>
-      <c r="S83" s="3">
-        <v>38300</v>
       </c>
       <c r="T83" s="3">
         <v>38300</v>
       </c>
       <c r="U83" s="3">
+        <v>38300</v>
+      </c>
+      <c r="V83" s="3">
         <v>38200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>41000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>31400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>31500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>31700</v>
-      </c>
-      <c r="Z83" s="3">
-        <v>32900</v>
       </c>
       <c r="AA83" s="3">
         <v>32900</v>
       </c>
       <c r="AB83" s="3">
+        <v>32900</v>
+      </c>
+      <c r="AC83" s="3">
         <v>33400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>31700</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>31100</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>29700</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>31800</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>36000</v>
-      </c>
-      <c r="AH83" s="3">
-        <v>30100</v>
       </c>
       <c r="AI83" s="3">
         <v>30100</v>
       </c>
       <c r="AJ83" s="3">
+        <v>30100</v>
+      </c>
+      <c r="AK83" s="3">
         <v>28100</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>24500</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8012,8 +8214,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8119,8 +8324,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8226,8 +8434,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8333,8 +8544,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8440,115 +8654,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-52800</v>
+      </c>
+      <c r="E89" s="3">
         <v>324600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>236900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>266700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>69300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-41700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>219300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>269000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-92300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>247000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>304000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>189000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>40000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>344000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>399000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>253100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>223900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>425200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>291500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>343800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>24200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>301400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>310600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>266600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>34500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>308300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>230800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>210900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>43200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>176600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>220900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>228500</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>6100</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>237200</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>105800</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8586,115 +8806,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-41700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-58400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-51500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-56700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-51700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-58100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-65800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-76400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-63100</v>
-      </c>
-      <c r="L91" s="3">
-        <v>-71000</v>
       </c>
       <c r="M91" s="3">
         <v>-71000</v>
       </c>
       <c r="N91" s="3">
+        <v>-71000</v>
+      </c>
+      <c r="O91" s="3">
         <v>-75000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-43000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-49900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-43500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-39000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-28600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-22500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-33600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-28800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-29200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-28800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-24200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-26600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-27400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-30900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-31600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-33400</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-22300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-31100</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-33500</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-39700</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-29900</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-28500</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-42800</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8800,8 +9024,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8907,115 +9134,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-234500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-33100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-295000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>100800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-231400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>414700</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-61100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-181000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>426900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-140000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-62000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-86000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-107000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-565000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1296100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-752600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-779300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-319500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-390100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-12700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-692800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-27200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-57700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-76700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-290600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-205900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-446800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-279300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-288700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>5000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-76400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-292000</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-23700</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-194200</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-145100</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9053,115 +9286,119 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>55700</v>
+      </c>
+      <c r="E96" s="3">
         <v>55500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>55600</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>54700</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>54900</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>54500</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>54700</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>53600</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>53800</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-53000</v>
-      </c>
-      <c r="M96" s="3">
-        <v>-54000</v>
       </c>
       <c r="N96" s="3">
         <v>-54000</v>
       </c>
       <c r="O96" s="3">
+        <v>-54000</v>
+      </c>
+      <c r="P96" s="3">
         <v>-56000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-55900</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-56000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-50100</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-51000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-50900</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-49100</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-49000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-49700</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-47200</v>
-      </c>
-      <c r="Y96" s="3">
-        <v>-47100</v>
       </c>
       <c r="Z96" s="3">
         <v>-47100</v>
       </c>
       <c r="AA96" s="3">
+        <v>-47100</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-47000</v>
-      </c>
-      <c r="AB96" s="3">
-        <v>-46900</v>
       </c>
       <c r="AC96" s="3">
         <v>-46900</v>
       </c>
       <c r="AD96" s="3">
+        <v>-46900</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-42400</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-42300</v>
-      </c>
-      <c r="AF96" s="3">
-        <v>-42100</v>
       </c>
       <c r="AG96" s="3">
         <v>-42100</v>
       </c>
       <c r="AH96" s="3">
+        <v>-42100</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-37600</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-37500</v>
-      </c>
-      <c r="AJ96" s="3">
-        <v>-37300</v>
       </c>
       <c r="AK96" s="3">
         <v>-37300</v>
       </c>
+      <c r="AL96" s="3">
+        <v>-37300</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9267,8 +9504,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9374,8 +9614,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9481,325 +9724,337 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>612300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1509200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>957000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>175000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1932200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1648000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-820000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>171400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>423700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1250000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>385000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-54000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>543000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-507400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>634100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>694200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1305100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-351800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>83300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>137800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>244600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-503200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>49600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-115400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>124000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-836700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>1197000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>120500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>33900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>63100</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-172600</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>179800</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>57700</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-475400</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>241200</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-4600</v>
+      </c>
+      <c r="E101" s="3">
         <v>5200</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-5000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>3100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>1600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>6200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-10600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-8600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>6000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-11000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-8000</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
       <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3">
         <v>2800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-5600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>2000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>800</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>9200</v>
-      </c>
-      <c r="U101" s="3">
-        <v>4400</v>
       </c>
       <c r="V101" s="3">
         <v>4400</v>
       </c>
       <c r="W101" s="3">
+        <v>4400</v>
+      </c>
+      <c r="X101" s="3">
         <v>-11900</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>4000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-3400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>400</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>2000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-3900</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-2200</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-2300</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>1000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>600</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>3300</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>3000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>1300</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-4800</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>327000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1235300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>904800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>542200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-2098900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2026200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-666800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>262500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>759900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-1137000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>616000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>41000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>476000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-725500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-268700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>196700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>750600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-236900</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-11000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>473400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-436000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-225000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>299000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>74900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-130100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-738200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>978800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>49900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-210600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>245300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-24800</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>119300</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>41300</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-437200</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>201500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FAF_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FAF_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="92">
   <si>
     <t>FAF</t>
   </si>
@@ -656,305 +656,312 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43738</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42825</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1841300</v>
+      </c>
+      <c r="E8" s="3">
         <v>1582300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1685100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1406100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1612300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1424600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1429300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1481200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1646900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1446100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1715000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1975000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2139000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2105000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2533100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2555900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2266400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2025700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2151300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1913700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1608700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1412900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1728700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1671200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1498600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1303600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1417100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1542200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1491200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1297400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1481300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1519600</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1454400</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1317000</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1504300</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>1508300</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>655400</v>
+      </c>
+      <c r="E9" s="3">
         <v>595600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>637100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>638500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>571700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>517300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>528800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>622500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>585900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>551300</v>
       </c>
-      <c r="M9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N9" s="3" t="s">
         <v>5</v>
       </c>
@@ -1030,41 +1037,44 @@
       <c r="AL9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1185900</v>
+      </c>
+      <c r="E10" s="3">
         <v>986700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1048000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>767600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1040600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>907300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>900500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>858700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1061000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>894800</v>
       </c>
-      <c r="M10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="N10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1140,8 +1150,11 @@
       <c r="AL10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1180,8 +1193,9 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1290,8 +1304,11 @@
       <c r="AL12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1400,8 +1417,11 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1432,39 +1452,39 @@
       <c r="L14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>5</v>
+      <c r="O14" s="3">
+        <v>0</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>5</v>
+      <c r="S14" s="3">
+        <v>0</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="U14" s="3">
+      <c r="U14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V14" s="3">
         <v>-18300</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>73300</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="X14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1480,8 +1500,8 @@
       <c r="AB14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
+      <c r="AC14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AD14" s="3">
         <v>0</v>
@@ -1510,118 +1530,124 @@
       <c r="AL14" s="3">
         <v>0</v>
       </c>
+      <c r="AM14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>53000</v>
+      </c>
+      <c r="E15" s="3">
         <v>52500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>52000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>53200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>52100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>50100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>49600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>47300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>46100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>45500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>43000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>41000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>42000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>41000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>39500</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>39200</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>40900</v>
-      </c>
-      <c r="T15" s="3">
-        <v>38300</v>
       </c>
       <c r="U15" s="3">
         <v>38300</v>
       </c>
       <c r="V15" s="3">
+        <v>38300</v>
+      </c>
+      <c r="W15" s="3">
         <v>38200</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>41000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>31400</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>31500</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>31700</v>
-      </c>
-      <c r="AA15" s="3">
-        <v>32900</v>
       </c>
       <c r="AB15" s="3">
         <v>32900</v>
       </c>
       <c r="AC15" s="3">
+        <v>32900</v>
+      </c>
+      <c r="AD15" s="3">
         <v>33400</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>31700</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>31100</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>29700</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>31800</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>36000</v>
-      </c>
-      <c r="AI15" s="3">
-        <v>30100</v>
       </c>
       <c r="AJ15" s="3">
         <v>30100</v>
       </c>
       <c r="AK15" s="3">
+        <v>30100</v>
+      </c>
+      <c r="AL15" s="3">
         <v>28100</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>24500</v>
       </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1657,228 +1683,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1608100</v>
+      </c>
+      <c r="E17" s="3">
         <v>1450500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1541500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1514300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1425300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1332000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1357600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1447100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1434500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1357400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1597000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1803000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1902000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1884000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2019500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1933500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1850700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1703200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1753000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1654400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1370000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1328500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1428400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1413600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1257200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1150000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1287200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1335800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1279200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1195100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1312800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1492500</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1261300</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1224400</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1414000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>1333600</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>233200</v>
+      </c>
+      <c r="E18" s="3">
         <v>131800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>143600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-108200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>187000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>92600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>71700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>34100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>212400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>88700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>118000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>172000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>237000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>221000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>513600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>622400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>415700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>322500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>398300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>259300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>238700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>84400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>300300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>257600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>241400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>153600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>129900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>206400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>212000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>102300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>168500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>27100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>193100</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>92600</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>90300</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>174700</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1917,8 +1950,9 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1949,24 +1983,24 @@
       <c r="L20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M20" s="3">
+      <c r="M20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N20" s="3">
         <v>-30000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-151000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-77000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-71000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-160100</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
         <v>0</v>
       </c>
@@ -2027,448 +2061,463 @@
       <c r="AL20" s="3">
         <v>0</v>
       </c>
+      <c r="AM20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>286200</v>
+      </c>
+      <c r="E21" s="3">
         <v>184300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>195600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-55000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>239100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>142700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>121300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>81400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>258500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>134200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>131000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>62000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>202000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>191000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>393000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>661600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>456600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>360800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>436600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>297600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>279700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>115900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>331700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>289300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>274300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>186500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>163300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>238100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>243000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>132000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>200300</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>63100</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>223300</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>122700</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>118400</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>199300</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>38000</v>
+      </c>
+      <c r="E22" s="3">
         <v>35200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>43700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>36200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>35400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>34300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>33300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>35800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>34300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>29100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>30000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>24000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>19000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>20000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>20100</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>19200</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>16200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>16500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>15900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>16000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>13400</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>12100</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>11700</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>12200</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>11900</v>
       </c>
       <c r="AB22" s="3">
         <v>11900</v>
       </c>
       <c r="AC22" s="3">
+        <v>11900</v>
+      </c>
+      <c r="AD22" s="3">
         <v>11000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>10800</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>10000</v>
-      </c>
-      <c r="AF22" s="3">
-        <v>9200</v>
       </c>
       <c r="AG22" s="3">
         <v>9200</v>
       </c>
       <c r="AH22" s="3">
+        <v>9200</v>
+      </c>
+      <c r="AI22" s="3">
         <v>9100</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>9000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>8700</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>8800</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>7800</v>
       </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>195200</v>
+      </c>
+      <c r="E23" s="3">
         <v>96600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>99900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-144400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>151600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>58300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>38400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-1700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>178100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>59600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>58000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-3000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>141000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>130000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>333400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>603200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>399400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>306000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>382300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>243400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>225300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>72300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>288500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>245300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>229500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>141700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>118900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>195600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>202000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>93100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>159300</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>18000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>184200</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>83900</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>81500</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>166900</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>48100</v>
+      </c>
+      <c r="E24" s="3">
         <v>21800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>27000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-41000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>35200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>11600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>4100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>41700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>13600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>4000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-6000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>31000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>32000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>72700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>152700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>96000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>71600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>100900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>59800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>53600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>8500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>63900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>57200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>42200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>31900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>25700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>44100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>46900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>16900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>52700</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-3200</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>62300</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>25800</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>500</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>59500</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2577,228 +2626,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>147100</v>
+      </c>
+      <c r="E26" s="3">
         <v>74800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>72900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-103400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>116400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>46700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>34300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-1200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>136400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>46000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>54000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>3000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>110000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>98000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>260700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>450500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>303400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>234500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>281400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>183600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>171700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>63800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>224600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>188200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>187300</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>109800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>93200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>151500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>155100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>76200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>106600</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>21200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>121900</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>58100</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>81000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>107400</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>146100</v>
+      </c>
+      <c r="E27" s="3">
         <v>74200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>72400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-104000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>116000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>46700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>34100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-1700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>138500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>45900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>54000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>109000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>98000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>259800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>445300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>302300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>233600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>280300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>182300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>170700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>63200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>224000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>187200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>186700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>109600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>91600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>151500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>155100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>76200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>107000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>21400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>122300</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>58300</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>81000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>107300</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2907,8 +2965,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2981,8 +3042,8 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-      <c r="AA29" s="3" t="s">
-        <v>5</v>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>5</v>
@@ -2999,12 +3060,12 @@
       <c r="AF29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AH29" s="3">
         <v>114100</v>
       </c>
-      <c r="AH29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AI29" s="3" t="s">
         <v>5</v>
       </c>
@@ -3017,8 +3078,11 @@
       <c r="AL29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AM29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3127,8 +3191,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3237,8 +3304,11 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3269,24 +3339,24 @@
       <c r="L32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M32" s="3">
+      <c r="M32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N32" s="3">
         <v>30000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>151000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>77000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>71000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>160100</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
         <v>0</v>
       </c>
@@ -3347,118 +3417,124 @@
       <c r="AL32" s="3">
         <v>0</v>
       </c>
+      <c r="AM32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>146100</v>
+      </c>
+      <c r="E33" s="3">
         <v>74200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>72400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-104000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>116000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>46700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>34100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-1700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>138500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>45900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>54000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>109000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>98000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>259800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>445300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>302300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>233600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>280300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>182300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>170700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>63200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>224000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>187200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>186700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>109600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>91600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>151500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>155100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>76200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>221100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>21400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>122300</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>58300</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>81000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>107300</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3567,233 +3643,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>146100</v>
+      </c>
+      <c r="E35" s="3">
         <v>74200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>72400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-104000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>116000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>46700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>34100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-1700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>138500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>45900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>54000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>109000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>98000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>259800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>445300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>302300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>233600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>280300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>182300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>170700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>63200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>224000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>187200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>186700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>109600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>91600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>151500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>155100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>76200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>221100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>21400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>122300</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>58300</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>81000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>107300</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43738</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42825</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3832,8 +3917,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3872,151 +3958,155 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2031200</v>
+      </c>
+      <c r="E41" s="3">
         <v>2045100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>1718100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2953400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2048600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1506400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3605300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1579100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>2245900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1983400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1224000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2361000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1745000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1704000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1228000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1954000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>2222700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>2026000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1275500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1512400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1523300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1050000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1486000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1711000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1412000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1337100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1467100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2205300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1226500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1176600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1387200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1141900</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1166800</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1047500</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>1006100</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>1443300</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>82700</v>
+      </c>
+      <c r="E42" s="3">
         <v>62800</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>85400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>55400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>56400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>77100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>55800</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>55300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>55900</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>53500</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
       <c r="N42" s="3">
         <v>0</v>
       </c>
@@ -4092,41 +4182,44 @@
       <c r="AL42" s="3">
         <v>0</v>
       </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1414000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1248300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1126100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1429300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1192400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1268200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1221600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1077600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1106900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>980300</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
-      </c>
       <c r="N43" s="3">
         <v>0</v>
       </c>
@@ -4202,8 +4295,11 @@
       <c r="AL43" s="3">
         <v>0</v>
       </c>
+      <c r="AM43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4234,8 +4330,8 @@
       <c r="L44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M44" s="3">
-        <v>0</v>
+      <c r="M44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N44" s="3">
         <v>0</v>
@@ -4312,8 +4408,11 @@
       <c r="AL44" s="3">
         <v>0</v>
       </c>
+      <c r="AM44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4344,8 +4443,8 @@
       <c r="L45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M45" s="3">
-        <v>0</v>
+      <c r="M45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="N45" s="3">
         <v>0</v>
@@ -4422,41 +4521,44 @@
       <c r="AL45" s="3">
         <v>0</v>
       </c>
+      <c r="AM45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3527900</v>
+      </c>
+      <c r="E46" s="3">
         <v>3356200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2929600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4438100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3297400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2851700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4882700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2712000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3408700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3017200</v>
       </c>
-      <c r="M46" s="3">
-        <v>0</v>
-      </c>
       <c r="N46" s="3">
         <v>0</v>
       </c>
@@ -4532,338 +4634,350 @@
       <c r="AL46" s="3">
         <v>0</v>
       </c>
+      <c r="AM46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>8625500</v>
+      </c>
+      <c r="E47" s="3">
         <v>8017200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>7864800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>7641800</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>7696100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>7697500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>7786100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>7837100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>8224800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>8307600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>9799000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>10234000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>10657000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>11249000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>11613000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>11450200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>9954100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>9253100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>8349200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>7823500</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>7593200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>7445500</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>7212300</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>7277700</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>7200600</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>6991800</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>6638500</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>6637000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>6196700</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>5893500</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>5728100</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>5743600</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>5789900</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>5493600</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>5508500</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>5489500</v>
       </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>924100</v>
+      </c>
+      <c r="E48" s="3">
         <v>951000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>966000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>1013100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>996900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>984000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>982100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>967900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>943600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>907000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>885000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>851000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>824000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>766000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>755000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>716200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>705300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>700400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>715000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>714800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>741000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>783900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>738200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>740300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>756400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>767600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>457800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>457500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>446300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>435900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>439600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>438100</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>433000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>429000</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>434100</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>430600</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2612200</v>
+      </c>
+      <c r="E49" s="3">
         <v>2609600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2603400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2613800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2609600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2611100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2613700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2610300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2620700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2634200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1992000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2016000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2023000</v>
-      </c>
-      <c r="P49" s="3">
-        <v>1806000</v>
       </c>
       <c r="Q49" s="3">
         <v>1806000</v>
       </c>
       <c r="R49" s="3">
+        <v>1806000</v>
+      </c>
+      <c r="S49" s="3">
         <v>1604900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1556000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1558200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1573100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1552000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1591900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1565500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1242700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1242600</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1246700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1247800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1253500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1256700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1271200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1229400</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1212900</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1220600</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>1109800</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>1095800</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>1096300</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>1066200</v>
       </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4972,8 +5086,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5082,43 +5199,46 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>540400</v>
+      </c>
+      <c r="E52" s="3">
         <v>519600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>466600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>809500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>507200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>503400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>465700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>495800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>478600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>463000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>54000</v>
-      </c>
-      <c r="N52" s="3">
-        <v>14000</v>
       </c>
       <c r="O52" s="3">
         <v>14000</v>
@@ -5130,7 +5250,7 @@
         <v>14000</v>
       </c>
       <c r="R52" s="3">
-        <v>14500</v>
+        <v>14000</v>
       </c>
       <c r="S52" s="3">
         <v>14500</v>
@@ -5142,10 +5262,10 @@
         <v>14500</v>
       </c>
       <c r="V52" s="3">
+        <v>14500</v>
+      </c>
+      <c r="W52" s="3">
         <v>216600</v>
-      </c>
-      <c r="W52" s="3">
-        <v>18300</v>
       </c>
       <c r="X52" s="3">
         <v>18300</v>
@@ -5154,7 +5274,7 @@
         <v>18300</v>
       </c>
       <c r="Z52" s="3">
-        <v>16600</v>
+        <v>18300</v>
       </c>
       <c r="AA52" s="3">
         <v>16600</v>
@@ -5166,7 +5286,7 @@
         <v>16600</v>
       </c>
       <c r="AD52" s="3">
-        <v>22800</v>
+        <v>16600</v>
       </c>
       <c r="AE52" s="3">
         <v>22800</v>
@@ -5178,7 +5298,7 @@
         <v>22800</v>
       </c>
       <c r="AH52" s="3">
-        <v>20000</v>
+        <v>22800</v>
       </c>
       <c r="AI52" s="3">
         <v>20000</v>
@@ -5190,10 +5310,13 @@
         <v>20000</v>
       </c>
       <c r="AL52" s="3">
+        <v>20000</v>
+      </c>
+      <c r="AM52" s="3">
         <v>22000</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5302,118 +5425,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>16273900</v>
+      </c>
+      <c r="E54" s="3">
         <v>15497400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>14908600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>16566400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>15157300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>14697800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>16802800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>14677600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>15730900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>15383500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>14955000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>16486000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>16262000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>16527000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>16451000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>16686100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>15426900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>14431900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>12796000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>12638800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>12288000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>11675500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>11519200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>11804100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>11443200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>11160300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>10630600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>11380100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>9959400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>9546800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>9573200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>9347000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>9314300</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>8874400</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>8831800</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>9246500</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5452,8 +5581,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5492,151 +5622,155 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>2072900</v>
+      </c>
+      <c r="E57" s="3">
         <v>1911000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1260100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2127200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>2159200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2006600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1345700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2110400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2111900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2035000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>915000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1115000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1015000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1051000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1262000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1252000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1070800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1113400</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>979700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>830100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>781500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>664000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>820400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>812500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>709300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>631500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>778700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>826700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>770700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>709600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>793200</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>741600</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>697000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>675800</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>794000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>813900</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>883800</v>
+      </c>
+      <c r="E58" s="3">
         <v>735800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>726000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>878200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>641500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>688800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>553300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>530400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>585700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>502900</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
@@ -5712,151 +5846,157 @@
       <c r="AL58" s="3">
         <v>0</v>
       </c>
+      <c r="AM58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>6055000</v>
+      </c>
+      <c r="E59" s="3">
         <v>5698500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>5248400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>6086900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>5633200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>5318500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>7484300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>5621300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>6377900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>6204700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>7124000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>8324000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>7723000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>7346000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>6651000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>7043200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>6920600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>6154000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>4804500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>4918800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>4925200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>4850100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>4748700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>5305000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>5265900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>5344000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>4837900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>5581000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>4326100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>4187700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>4104100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>4079900</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>4208900</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>3926300</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>3815700</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>4302200</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>9011700</v>
+      </c>
+      <c r="E60" s="3">
         <v>8345300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>7937800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>9092300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>8433900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>8013900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>10039100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>8262100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>9075500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>8742600</v>
       </c>
-      <c r="M60" s="3">
-        <v>0</v>
-      </c>
       <c r="N60" s="3">
         <v>0</v>
       </c>
@@ -5932,118 +6072,124 @@
       <c r="AL60" s="3">
         <v>0</v>
       </c>
+      <c r="AM60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1769500</v>
+      </c>
+      <c r="E61" s="3">
         <v>1775900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1694300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2089900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1636700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1631400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1640500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1647000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1656500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1659100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2012000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1988000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2075000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2205000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2186000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2242500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1619200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1655000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1526900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1538300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1489200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1288800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1006600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>961800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>919700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>858600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>808300</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>821800</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>832600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>731500</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>732800</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>734100</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>734500</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>735500</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>736700</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>737900</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -6074,23 +6220,23 @@
       <c r="L62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="M62" s="3">
+      <c r="M62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="N62" s="3">
         <v>19000</v>
-      </c>
-      <c r="N62" s="3">
-        <v>314000</v>
       </c>
       <c r="O62" s="3">
         <v>314000</v>
       </c>
       <c r="P62" s="3">
-        <v>345000</v>
+        <v>314000</v>
       </c>
       <c r="Q62" s="3">
         <v>345000</v>
       </c>
       <c r="R62" s="3">
-        <v>291200</v>
+        <v>345000</v>
       </c>
       <c r="S62" s="3">
         <v>291200</v>
@@ -6102,10 +6248,10 @@
         <v>291200</v>
       </c>
       <c r="V62" s="3">
+        <v>291200</v>
+      </c>
+      <c r="W62" s="3">
         <v>414400</v>
-      </c>
-      <c r="W62" s="3">
-        <v>266100</v>
       </c>
       <c r="X62" s="3">
         <v>266100</v>
@@ -6114,7 +6260,7 @@
         <v>266100</v>
       </c>
       <c r="Z62" s="3">
-        <v>217100</v>
+        <v>266100</v>
       </c>
       <c r="AA62" s="3">
         <v>217100</v>
@@ -6126,7 +6272,7 @@
         <v>217100</v>
       </c>
       <c r="AD62" s="3">
-        <v>219300</v>
+        <v>217100</v>
       </c>
       <c r="AE62" s="3">
         <v>219300</v>
@@ -6138,7 +6284,7 @@
         <v>219300</v>
       </c>
       <c r="AH62" s="3">
-        <v>242200</v>
+        <v>219300</v>
       </c>
       <c r="AI62" s="3">
         <v>242200</v>
@@ -6150,10 +6296,13 @@
         <v>242200</v>
       </c>
       <c r="AL62" s="3">
+        <v>242200</v>
+      </c>
+      <c r="AM62" s="3">
         <v>133100</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6262,8 +6411,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6372,8 +6524,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6482,118 +6637,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>11124600</v>
+      </c>
+      <c r="E66" s="3">
         <v>10456500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>9981600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>11455800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>10324700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>9891900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>11940000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>10135600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>10944000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>10604600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>10290000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>11978000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>11346000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>11164000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>10684000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>11088900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>10163100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>9476600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>7886000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>7915000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>7722600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>7316100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>7098700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>7562000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>7358300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>7282200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>6888800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>7705900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>6389900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>6076300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>6093300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>6053200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>6120900</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>5802000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>5823600</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>6224200</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6632,8 +6793,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6742,8 +6904,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6852,8 +7017,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6962,8 +7130,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7072,118 +7243,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3724500</v>
+      </c>
+      <c r="E72" s="3">
         <v>3634800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>3617300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3601400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3761900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>3701600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>3710600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>3739000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>3796200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>3712300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>3721000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>3722000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>3775000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>3721000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>3680000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>3476900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>3088600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2837200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2655500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2426900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>2294600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>2173700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>2161000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1985100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1845900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1707100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1644200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>1600300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1496600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>1384700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>1311100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>1129000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>1150600</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>1066700</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>1046800</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>1012500</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7292,8 +7469,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7402,8 +7582,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7512,118 +7695,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5126200</v>
+      </c>
+      <c r="E76" s="3">
         <v>5019300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4908500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5092200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4813600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4787100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4848100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4527200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4772400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4756500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4665000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4508000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4916000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>5363000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>5767000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>5597100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>5263700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>4955300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>4910000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>4723800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>4565400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>4359300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>4420500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>4242100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>4084900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>3878000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>3741900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>3674200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>3569500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>3470500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>3480000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>3293900</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>3193400</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>3072500</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>3008200</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>3022300</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7732,233 +7921,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43738</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42916</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42825</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>146100</v>
+      </c>
+      <c r="E81" s="3">
         <v>74200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>72400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-104000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>116000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>46700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>34100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-1700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>138500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>45900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>54000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>109000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>98000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>259800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>445300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>302300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>233600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>280300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>182300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>170700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>63200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>224000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>187200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>186700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>109600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>91600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>151500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>155100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>76200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>221100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>21400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>122300</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>58300</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>81000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>107300</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7997,118 +8195,122 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>40900</v>
+      </c>
+      <c r="E83" s="3">
         <v>37800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>37100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>34400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>33500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>32000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>30800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>29700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>27700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>26100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>43000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>41000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>42000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>41000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>39500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>39200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>40900</v>
-      </c>
-      <c r="T83" s="3">
-        <v>38300</v>
       </c>
       <c r="U83" s="3">
         <v>38300</v>
       </c>
       <c r="V83" s="3">
+        <v>38300</v>
+      </c>
+      <c r="W83" s="3">
         <v>38200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>41000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>31400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>31500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>31700</v>
-      </c>
-      <c r="AA83" s="3">
-        <v>32900</v>
       </c>
       <c r="AB83" s="3">
         <v>32900</v>
       </c>
       <c r="AC83" s="3">
+        <v>32900</v>
+      </c>
+      <c r="AD83" s="3">
         <v>33400</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>31700</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>31100</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>29700</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>31800</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>36000</v>
-      </c>
-      <c r="AI83" s="3">
-        <v>30100</v>
       </c>
       <c r="AJ83" s="3">
         <v>30100</v>
       </c>
       <c r="AK83" s="3">
+        <v>30100</v>
+      </c>
+      <c r="AL83" s="3">
         <v>28100</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>24500</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8217,8 +8419,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8327,8 +8532,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8437,8 +8645,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8547,8 +8758,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8657,118 +8871,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>361800</v>
+      </c>
+      <c r="E89" s="3">
         <v>-52800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>324600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>236900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>266700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>69300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-41700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>219300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>269000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-92300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>247000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>304000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>189000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>40000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>344000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>399000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>253100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>223900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>425200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>291500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>343800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>24200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>301400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>310600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>266600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>34500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>308300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>230800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>210900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>43200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>176600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>220900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>228500</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>6100</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>237200</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>105800</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8807,118 +9027,122 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-52400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-41700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-58400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-51500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-56700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-51700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-58100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-65800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-76400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-63100</v>
-      </c>
-      <c r="M91" s="3">
-        <v>-71000</v>
       </c>
       <c r="N91" s="3">
         <v>-71000</v>
       </c>
       <c r="O91" s="3">
+        <v>-71000</v>
+      </c>
+      <c r="P91" s="3">
         <v>-75000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-43000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-49900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-43500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-39000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-28600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-22500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-33600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-28800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-29200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-28800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-24200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-26600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-27400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-30900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-31600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-33400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-22300</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-31100</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-33500</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-39700</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-29900</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-28500</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-42800</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9027,8 +9251,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9137,118 +9364,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-723200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-234500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-33100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-295000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>100800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-231400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>414700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-61100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-181000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>426900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-140000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-62000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-86000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-107000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-565000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1296100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-752600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-779300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-319500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-390100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-12700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-692800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-27200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-57700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-76700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-290600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-205900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-446800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-279300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-288700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>5000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-76400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-292000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-23700</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-194200</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-145100</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9287,118 +9520,122 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>55300</v>
+      </c>
+      <c r="E96" s="3">
         <v>55700</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>55500</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>55600</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>54700</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>54900</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>54500</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>54700</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>53600</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>53800</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-53000</v>
-      </c>
-      <c r="N96" s="3">
-        <v>-54000</v>
       </c>
       <c r="O96" s="3">
         <v>-54000</v>
       </c>
       <c r="P96" s="3">
+        <v>-54000</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-56000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-55900</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-56000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-50100</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-51000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-50900</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-49100</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-49000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-49700</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-47200</v>
-      </c>
-      <c r="Z96" s="3">
-        <v>-47100</v>
       </c>
       <c r="AA96" s="3">
         <v>-47100</v>
       </c>
       <c r="AB96" s="3">
+        <v>-47100</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-47000</v>
-      </c>
-      <c r="AC96" s="3">
-        <v>-46900</v>
       </c>
       <c r="AD96" s="3">
         <v>-46900</v>
       </c>
       <c r="AE96" s="3">
+        <v>-46900</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-42400</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-42300</v>
-      </c>
-      <c r="AG96" s="3">
-        <v>-42100</v>
       </c>
       <c r="AH96" s="3">
         <v>-42100</v>
       </c>
       <c r="AI96" s="3">
+        <v>-42100</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-37600</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-37500</v>
-      </c>
-      <c r="AK96" s="3">
-        <v>-37300</v>
       </c>
       <c r="AL96" s="3">
         <v>-37300</v>
       </c>
+      <c r="AM96" s="3">
+        <v>-37300</v>
+      </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9507,8 +9744,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9617,8 +9857,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9727,334 +9970,346 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>335500</v>
+      </c>
+      <c r="E100" s="3">
         <v>612300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-1509200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>957000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>175000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1932200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1648000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-820000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>171400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>423700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1250000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>385000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-54000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>543000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-507400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>634100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>694200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1305100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-351800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>83300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>137800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>244600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-503200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>49600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-115400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>124000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-836700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>1197000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>120500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>33900</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>63100</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-172600</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>179800</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>57700</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-475400</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>241200</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E101" s="3">
         <v>-4600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>5200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-5000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>3100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>1600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>6200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-10600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-8600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>6000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-11000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-8000</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
       <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3">
         <v>2800</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-5600</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>2000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>800</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>9200</v>
-      </c>
-      <c r="V101" s="3">
-        <v>4400</v>
       </c>
       <c r="W101" s="3">
         <v>4400</v>
       </c>
       <c r="X101" s="3">
+        <v>4400</v>
+      </c>
+      <c r="Y101" s="3">
         <v>-11900</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>4000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-3400</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>400</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>2000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-3900</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-2200</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-2300</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>1000</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>600</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>3300</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>3000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>1300</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-4800</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-13900</v>
+      </c>
+      <c r="E102" s="3">
         <v>327000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1235300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>904800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>542200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2098900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2026200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-666800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>262500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>759900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-1137000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>616000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>41000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>476000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-725500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-268700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>196700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>750600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-236900</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-11000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>473400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-436000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-225000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>299000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>74900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-130100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-738200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>978800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>49900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-210600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>245300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-24800</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>119300</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>41300</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-437200</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>201500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FAF_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FAF_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="92">
   <si>
     <t>FAF</t>
   </si>
@@ -656,325 +656,331 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43738</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42916</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42825</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2049700</v>
+      </c>
+      <c r="E8" s="3">
         <v>1978900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1841300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1582300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1685100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1406100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1612300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1424600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1429300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1481200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1646900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1446100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1715000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1975000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2139000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2105000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2533100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2555900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2266400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2025700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2151300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1913700</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1608700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1412900</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1728700</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1671200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1498600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1303600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1417100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1542200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1491200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1297400</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1481300</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1519600</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1454400</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>1317000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>1504300</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>1508300</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>718700</v>
+      </c>
+      <c r="E9" s="3">
         <v>730900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>655400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>595600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>637100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>638500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>571700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>517300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>528800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>622500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>585900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>551300</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P9" s="3" t="s">
         <v>5</v>
       </c>
@@ -1050,47 +1056,50 @@
       <c r="AN9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AO9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1331000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1248000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1185900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>986700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1048000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>767600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1040600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>907300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>900500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>858700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1061000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>894800</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="P10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1166,8 +1175,11 @@
       <c r="AN10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AO10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1208,8 +1220,9 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1324,8 +1337,11 @@
       <c r="AN12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AO12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1440,8 +1456,11 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1478,39 +1497,39 @@
       <c r="N14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>5</v>
+      <c r="Q14" s="3">
+        <v>0</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>5</v>
+      <c r="U14" s="3">
+        <v>0</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="W14" s="3">
+      <c r="W14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="X14" s="3">
         <v>-18300</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>73300</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Z14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1526,8 +1545,8 @@
       <c r="AD14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
+      <c r="AE14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AF14" s="3">
         <v>0</v>
@@ -1556,124 +1575,130 @@
       <c r="AN14" s="3">
         <v>0</v>
       </c>
+      <c r="AO14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>55900</v>
+      </c>
+      <c r="E15" s="3">
         <v>54800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>53000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>52500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>52000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>53200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>52100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>50100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>49600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>47300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>46100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>45500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>43000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>41000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>42000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>41000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>39500</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>39200</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>40900</v>
-      </c>
-      <c r="V15" s="3">
-        <v>38300</v>
       </c>
       <c r="W15" s="3">
         <v>38300</v>
       </c>
       <c r="X15" s="3">
+        <v>38300</v>
+      </c>
+      <c r="Y15" s="3">
         <v>38200</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>41000</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>31400</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>31500</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>31700</v>
-      </c>
-      <c r="AC15" s="3">
-        <v>32900</v>
       </c>
       <c r="AD15" s="3">
         <v>32900</v>
       </c>
       <c r="AE15" s="3">
+        <v>32900</v>
+      </c>
+      <c r="AF15" s="3">
         <v>33400</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>31700</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>31100</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>29700</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>31800</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>36000</v>
-      </c>
-      <c r="AK15" s="3">
-        <v>30100</v>
       </c>
       <c r="AL15" s="3">
         <v>30100</v>
       </c>
       <c r="AM15" s="3">
+        <v>30100</v>
+      </c>
+      <c r="AN15" s="3">
         <v>28100</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>24500</v>
       </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1711,240 +1736,247 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1718400</v>
+      </c>
+      <c r="E17" s="3">
         <v>1692000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1608100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1450500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1541500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1514300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1425300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1332000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1357600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1447100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1434500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1357400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1597000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1803000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1902000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1884000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2019500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1933500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1850700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1703200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1753000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1654400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1370000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1328500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1428400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1413600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1257200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1150000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1287200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1335800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1279200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1195100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1312800</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1492500</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1261300</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>1224400</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>1414000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>1333600</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>331300</v>
+      </c>
+      <c r="E18" s="3">
         <v>286900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>233200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>131800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>143600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-108200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>187000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>92600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>71700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>34100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>212400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>88700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>118000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>172000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>237000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>221000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>513600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>622400</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>415700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>322500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>398300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>259300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>238700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>84400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>300300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>257600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>241400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>153600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>129900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>206400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>212000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>102300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>168500</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>27100</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>193100</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>92600</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>90300</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>174700</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1985,8 +2017,9 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2023,24 +2056,24 @@
       <c r="N20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P20" s="3">
         <v>-30000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-151000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-77000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-71000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-160100</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
         <v>0</v>
       </c>
@@ -2101,472 +2134,487 @@
       <c r="AN20" s="3">
         <v>0</v>
       </c>
+      <c r="AO20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>387200</v>
+      </c>
+      <c r="E21" s="3">
         <v>341700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>286200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>184300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>195600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-55000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>239100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>142700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>121300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>81400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>258500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>134200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>131000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>62000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>202000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>191000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>393000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>661600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>456600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>360800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>436600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>297600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>279700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>115900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>331700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>289300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>274300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>186500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>163300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>238100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>243000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>132000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>200300</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>63100</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>223300</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>122700</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>118400</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>199300</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>43900</v>
+      </c>
+      <c r="E22" s="3">
         <v>39900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>38000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>35200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>43700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>36200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>35400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>34300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>33300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>35800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>34300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>29100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>30000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>24000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>19000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>20000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>20100</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>19200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>16200</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>16500</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>15900</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>16000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>13400</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>12100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>11700</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>12200</v>
-      </c>
-      <c r="AC22" s="3">
-        <v>11900</v>
       </c>
       <c r="AD22" s="3">
         <v>11900</v>
       </c>
       <c r="AE22" s="3">
+        <v>11900</v>
+      </c>
+      <c r="AF22" s="3">
         <v>11000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>10800</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>10000</v>
-      </c>
-      <c r="AH22" s="3">
-        <v>9200</v>
       </c>
       <c r="AI22" s="3">
         <v>9200</v>
       </c>
       <c r="AJ22" s="3">
+        <v>9200</v>
+      </c>
+      <c r="AK22" s="3">
         <v>9100</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>9000</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>8700</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>8800</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>7800</v>
       </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>287400</v>
+      </c>
+      <c r="E23" s="3">
         <v>247000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>195200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>96600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>99900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-144400</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>151600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>58300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>38400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-1700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>178100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>59600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>58000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>141000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>130000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>333400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>603200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>399400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>306000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>382300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>243400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>225300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>72300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>288500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>245300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>229500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>141700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>118900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>195600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>202000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>93100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>159300</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>18000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>184200</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>83900</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>81500</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>166900</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>74000</v>
+      </c>
+      <c r="E24" s="3">
         <v>57100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>48100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>21800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>27000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-41000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>35200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>11600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>4100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>41700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>13600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>4000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-6000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>31000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>32000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>72700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>152700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>96000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>71600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>100900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>59800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>53600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>8500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>63900</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>57200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>42200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>31900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>25700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>44100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>46900</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>16900</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>52700</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-3200</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>62300</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>25800</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>500</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>59500</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2681,240 +2729,249 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>213400</v>
+      </c>
+      <c r="E26" s="3">
         <v>189900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>147100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>74800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>72900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-103400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>116400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>46700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>34300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-1200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>136400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>46000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>54000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>3000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>110000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>98000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>260700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>450500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>303400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>234500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>281400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>183600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>171700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>63800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>224600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>188200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>187300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>109800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>93200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>151500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>155100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>76200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>106600</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>21200</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>121900</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>58100</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>81000</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>107400</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>211900</v>
+      </c>
+      <c r="E27" s="3">
         <v>189600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>146100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>74200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>72400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-104000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>116000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>46700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>34100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-1700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>138500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>45900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>54000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>2000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>109000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>98000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>259800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>445300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>302300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>233600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>280300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>182300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>170700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>63200</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>224000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>187200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>186700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>109600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>91600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>151500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>155100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>76200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>107000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>21400</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>122300</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>58300</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>81000</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>107300</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3029,8 +3086,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3109,8 +3169,8 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>5</v>
+      <c r="AC29" s="3">
+        <v>0</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>5</v>
@@ -3127,12 +3187,12 @@
       <c r="AH29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AI29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AJ29" s="3">
         <v>114100</v>
       </c>
-      <c r="AJ29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AK29" s="3" t="s">
         <v>5</v>
       </c>
@@ -3145,8 +3205,11 @@
       <c r="AN29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AO29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3261,8 +3324,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3377,8 +3443,11 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3415,24 +3484,24 @@
       <c r="N32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P32" s="3">
         <v>30000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>151000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>77000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>71000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>160100</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
         <v>0</v>
       </c>
@@ -3493,124 +3562,130 @@
       <c r="AN32" s="3">
         <v>0</v>
       </c>
+      <c r="AO32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>211900</v>
+      </c>
+      <c r="E33" s="3">
         <v>189600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>146100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>74200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>72400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-104000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>116000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>46700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>34100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>138500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>45900</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>54000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>2000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>109000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>98000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>259800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>445300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>302300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>233600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>280300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>182300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>170700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>63200</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>224000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>187200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>186700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>109600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>91600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>151500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>155100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>76200</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>221100</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>21400</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>122300</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>58300</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>81000</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>107300</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3725,245 +3800,254 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>211900</v>
+      </c>
+      <c r="E35" s="3">
         <v>189600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>146100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>74200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>72400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-104000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>116000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>46700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>34100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>138500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>45900</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>54000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>2000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>109000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>98000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>259800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>445300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>302300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>233600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>280300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>182300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>170700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>63200</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>224000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>187200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>186700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>109600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>91600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>151500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>155100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>76200</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>221100</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>21400</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>122300</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>58300</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>81000</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>107300</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43738</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42916</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42825</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4004,8 +4088,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4046,163 +4131,167 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1387300</v>
+      </c>
+      <c r="E41" s="3">
         <v>2911500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2031200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2045100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1718100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2953400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2048600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>1506400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3605300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1579100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2245900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1983400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1224000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2361000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1745000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1704000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1228000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1954000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>2222700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2026000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1275500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1512400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1523300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1050000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1486000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1711000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1412000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1337100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1467100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2205300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1226500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1176600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1387200</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1141900</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>1166800</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>1047500</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>1006100</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>1443300</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>78500</v>
+      </c>
+      <c r="E42" s="3">
         <v>80000</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>82700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>62800</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>85400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>55400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>56400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>77100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>55800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>55300</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>55900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>53500</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
       <c r="P42" s="3">
         <v>0</v>
       </c>
@@ -4278,47 +4367,50 @@
       <c r="AN42" s="3">
         <v>0</v>
       </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1483700</v>
+      </c>
+      <c r="E43" s="3">
         <v>1638000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1414000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1248300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1126100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1429300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1192400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1268200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1221600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1077600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1106900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>980300</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
-      </c>
       <c r="P43" s="3">
         <v>0</v>
       </c>
@@ -4394,8 +4486,11 @@
       <c r="AN43" s="3">
         <v>0</v>
       </c>
+      <c r="AO43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4432,8 +4527,8 @@
       <c r="N44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P44" s="3">
         <v>0</v>
@@ -4510,8 +4605,11 @@
       <c r="AN44" s="3">
         <v>0</v>
       </c>
+      <c r="AO44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4548,8 +4646,8 @@
       <c r="N45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O45" s="3">
-        <v>0</v>
+      <c r="O45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="P45" s="3">
         <v>0</v>
@@ -4626,47 +4724,50 @@
       <c r="AN45" s="3">
         <v>0</v>
       </c>
+      <c r="AO45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2949500</v>
+      </c>
+      <c r="E46" s="3">
         <v>4629500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>3527900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3356200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2929600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4438100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3297400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>2851700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>4882700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>2712000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3408700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3017200</v>
       </c>
-      <c r="O46" s="3">
-        <v>0</v>
-      </c>
       <c r="P46" s="3">
         <v>0</v>
       </c>
@@ -4742,356 +4843,368 @@
       <c r="AN46" s="3">
         <v>0</v>
       </c>
+      <c r="AO46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>9145500</v>
+      </c>
+      <c r="E47" s="3">
         <v>8826400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>8625500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>8017200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>7864800</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>7641800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>7696100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>7697500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>7786100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>7837100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>8224800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>8307600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>9799000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>10234000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>10657000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>11249000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>11613000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>11450200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>9954100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>9253100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>8349200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>7823500</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>7593200</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>7445500</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>7212300</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>7277700</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>7200600</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>6991800</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>6638500</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>6637000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>6196700</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>5893500</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>5728100</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>5743600</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>5789900</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>5493600</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>5508500</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>5489500</v>
       </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>891900</v>
+      </c>
+      <c r="E48" s="3">
         <v>902300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>924100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>951000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>966000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>1013100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>996900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>984000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>982100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>967900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>943600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>907000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>885000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>851000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>824000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>766000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>755000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>716200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>705300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>700400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>715000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>714800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>741000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>783900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>738200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>740300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>756400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>767600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>457800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>457500</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>446300</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>435900</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>439600</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>438100</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>433000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>429000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>434100</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>430600</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2606000</v>
+      </c>
+      <c r="E49" s="3">
         <v>2609200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2612200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2609600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2603400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2613800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2609600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2611100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2613700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2610300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2620700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2634200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1992000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2016000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2023000</v>
-      </c>
-      <c r="R49" s="3">
-        <v>1806000</v>
       </c>
       <c r="S49" s="3">
         <v>1806000</v>
       </c>
       <c r="T49" s="3">
+        <v>1806000</v>
+      </c>
+      <c r="U49" s="3">
         <v>1604900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1556000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1558200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1573100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1552000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1591900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1565500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1242700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1242600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1246700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1247800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1253500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1256700</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1271200</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1229400</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>1212900</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>1220600</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>1109800</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>1095800</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>1096300</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>1066200</v>
       </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5206,8 +5319,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5322,49 +5438,52 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>590800</v>
+      </c>
+      <c r="E52" s="3">
         <v>598800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>540400</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>519600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>466600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>809500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>507200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>503400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>465700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>495800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>478600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>463000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>54000</v>
-      </c>
-      <c r="P52" s="3">
-        <v>14000</v>
       </c>
       <c r="Q52" s="3">
         <v>14000</v>
@@ -5376,7 +5495,7 @@
         <v>14000</v>
       </c>
       <c r="T52" s="3">
-        <v>14500</v>
+        <v>14000</v>
       </c>
       <c r="U52" s="3">
         <v>14500</v>
@@ -5388,10 +5507,10 @@
         <v>14500</v>
       </c>
       <c r="X52" s="3">
+        <v>14500</v>
+      </c>
+      <c r="Y52" s="3">
         <v>216600</v>
-      </c>
-      <c r="Y52" s="3">
-        <v>18300</v>
       </c>
       <c r="Z52" s="3">
         <v>18300</v>
@@ -5400,7 +5519,7 @@
         <v>18300</v>
       </c>
       <c r="AB52" s="3">
-        <v>16600</v>
+        <v>18300</v>
       </c>
       <c r="AC52" s="3">
         <v>16600</v>
@@ -5412,7 +5531,7 @@
         <v>16600</v>
       </c>
       <c r="AF52" s="3">
-        <v>22800</v>
+        <v>16600</v>
       </c>
       <c r="AG52" s="3">
         <v>22800</v>
@@ -5424,7 +5543,7 @@
         <v>22800</v>
       </c>
       <c r="AJ52" s="3">
-        <v>20000</v>
+        <v>22800</v>
       </c>
       <c r="AK52" s="3">
         <v>20000</v>
@@ -5436,10 +5555,13 @@
         <v>20000</v>
       </c>
       <c r="AN52" s="3">
+        <v>20000</v>
+      </c>
+      <c r="AO52" s="3">
         <v>22000</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5554,124 +5676,130 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>16228800</v>
+      </c>
+      <c r="E54" s="3">
         <v>17610000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>16273900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>15497400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>14908600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>16566400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>15157300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>14697800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>16802800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>14677600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>15730900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>15383500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>14955000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>16486000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>16262000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>16527000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>16451000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>16686100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>15426900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>14431900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>12796000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>12638800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>12288000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>11675500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>11519200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>11804100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>11443200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>11160300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>10630600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>11380100</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>9959400</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>9546800</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>9573200</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>9347000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>9314300</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>8874400</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>8831800</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>9246500</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5712,8 +5840,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5754,163 +5883,167 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1217300</v>
+      </c>
+      <c r="E57" s="3">
         <v>2126100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2072900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1911000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1260100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>2127200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2159200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2006600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1345700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2110400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2111900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2035000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>915000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1115000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1015000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1051000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1262000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1252000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1070800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1113400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>979700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>830100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>781500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>664000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>820400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>812500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>709300</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>631500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>778700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>826700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>770700</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>709600</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>793200</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>741600</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>697000</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>675800</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>794000</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>813900</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>984400</v>
+      </c>
+      <c r="E58" s="3">
         <v>1078400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>883800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>735800</v>
       </c>
-      <c r="G58" s="3">
-        <v>726000</v>
-      </c>
       <c r="H58" s="3">
+        <v>643800</v>
+      </c>
+      <c r="I58" s="3">
         <v>878200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>641500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>688800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>553300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>530400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>585700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>502900</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
       <c r="P58" s="3">
         <v>0</v>
       </c>
@@ -5986,163 +6119,169 @@
       <c r="AN58" s="3">
         <v>0</v>
       </c>
+      <c r="AO58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5528300</v>
+      </c>
+      <c r="E59" s="3">
         <v>6952600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>6055000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5698500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>5248400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>6086900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>5633200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>5318500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>7484300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>5621300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>6377900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>6204700</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>7124000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>8324000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>7723000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>7346000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>6651000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>7043200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>6920600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>6154000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>4804500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>4918800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>4925200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>4850100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>4748700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>5305000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>5265900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>5344000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>4837900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>5581000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>4326100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>4187700</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>4104100</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>4079900</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>4208900</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>3926300</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>3815700</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>4302200</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>8492100</v>
+      </c>
+      <c r="E60" s="3">
         <v>10157100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>9011700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>8345300</v>
       </c>
-      <c r="G60" s="3">
-        <v>7937800</v>
-      </c>
       <c r="H60" s="3">
+        <v>7855600</v>
+      </c>
+      <c r="I60" s="3">
         <v>9092300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>8433900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>8013900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>10039100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>8262100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>9075500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>8742600</v>
       </c>
-      <c r="O60" s="3">
-        <v>0</v>
-      </c>
       <c r="P60" s="3">
         <v>0</v>
       </c>
@@ -6218,124 +6357,130 @@
       <c r="AN60" s="3">
         <v>0</v>
       </c>
+      <c r="AO60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1685700</v>
+      </c>
+      <c r="E61" s="3">
         <v>1766900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1769500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1775900</v>
       </c>
-      <c r="G61" s="3">
-        <v>1694300</v>
-      </c>
       <c r="H61" s="3">
+        <v>1776500</v>
+      </c>
+      <c r="I61" s="3">
         <v>2089900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1636700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1631400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1640500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1647000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1656500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1659100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2012000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1988000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2075000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2205000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2186000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2242500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1619200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1655000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1526900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1538300</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1489200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1288800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1006600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>961800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>919700</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>858600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>808300</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>821800</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>832600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>731500</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>732800</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>734100</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>734500</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>735500</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>736700</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>737900</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -6372,23 +6517,23 @@
       <c r="N62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O62" s="3">
+      <c r="O62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P62" s="3">
         <v>19000</v>
-      </c>
-      <c r="P62" s="3">
-        <v>314000</v>
       </c>
       <c r="Q62" s="3">
         <v>314000</v>
       </c>
       <c r="R62" s="3">
-        <v>345000</v>
+        <v>314000</v>
       </c>
       <c r="S62" s="3">
         <v>345000</v>
       </c>
       <c r="T62" s="3">
-        <v>291200</v>
+        <v>345000</v>
       </c>
       <c r="U62" s="3">
         <v>291200</v>
@@ -6400,10 +6545,10 @@
         <v>291200</v>
       </c>
       <c r="X62" s="3">
+        <v>291200</v>
+      </c>
+      <c r="Y62" s="3">
         <v>414400</v>
-      </c>
-      <c r="Y62" s="3">
-        <v>266100</v>
       </c>
       <c r="Z62" s="3">
         <v>266100</v>
@@ -6412,7 +6557,7 @@
         <v>266100</v>
       </c>
       <c r="AB62" s="3">
-        <v>217100</v>
+        <v>266100</v>
       </c>
       <c r="AC62" s="3">
         <v>217100</v>
@@ -6424,7 +6569,7 @@
         <v>217100</v>
       </c>
       <c r="AF62" s="3">
-        <v>219300</v>
+        <v>217100</v>
       </c>
       <c r="AG62" s="3">
         <v>219300</v>
@@ -6436,7 +6581,7 @@
         <v>219300</v>
       </c>
       <c r="AJ62" s="3">
-        <v>242200</v>
+        <v>219300</v>
       </c>
       <c r="AK62" s="3">
         <v>242200</v>
@@ -6448,10 +6593,13 @@
         <v>242200</v>
       </c>
       <c r="AN62" s="3">
+        <v>242200</v>
+      </c>
+      <c r="AO62" s="3">
         <v>133100</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6566,8 +6714,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6682,8 +6833,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6798,124 +6952,130 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>10704500</v>
+      </c>
+      <c r="E66" s="3">
         <v>12284800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>11124600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>10456500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>9981600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>11455800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>10324700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>9891900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>11940000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>10135600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>10944000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>10604600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>10290000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>11978000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>11346000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>11164000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>10684000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>11088900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>10163100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>9476600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>7886000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>7915000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>7722600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>7316100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>7098700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>7562000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>7358300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>7282200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>6888800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>7705900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>6389900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>6076300</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>6093300</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>6053200</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>6120900</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>5802000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>5823600</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>6224200</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6956,8 +7116,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7072,8 +7233,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7188,8 +7352,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7304,8 +7471,11 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7420,124 +7590,130 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4011800</v>
+      </c>
+      <c r="E72" s="3">
         <v>3857100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>3724500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3634800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3617300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>3601400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>3761900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>3701600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>3710600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>3739000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>3796200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>3712300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>3721000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>3722000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>3775000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>3721000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>3680000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>3476900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>3088600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2837200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>2655500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>2426900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>2294600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>2173700</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>2161000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1985100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1845900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>1707100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1644200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>1600300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>1496600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>1384700</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>1311100</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>1129000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>1150600</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>1066700</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>1046800</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>1012500</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7652,8 +7828,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7768,8 +7947,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7884,124 +8066,130 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5499500</v>
+      </c>
+      <c r="E76" s="3">
         <v>5301100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5126200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5019300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4908500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>5092200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4813600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4787100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4848100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4527200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4772400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4756500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4665000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4508000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4916000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>5363000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>5767000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>5597100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>5263700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>4955300</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>4910000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>4723800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>4565400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>4359300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>4420500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>4242100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>4084900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>3878000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>3741900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>3674200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>3569500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>3470500</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>3480000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>3293900</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>3193400</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>3072500</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>3008200</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>3022300</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8116,245 +8304,254 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43738</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42916</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42825</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>211900</v>
+      </c>
+      <c r="E81" s="3">
         <v>189600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>146100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>74200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>72400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-104000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>116000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>46700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>34100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>138500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>45900</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>54000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>2000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>109000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>98000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>259800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>445300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>302300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>233600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>280300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>182300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>170700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>63200</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>224000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>187200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>186700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>109600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>91600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>151500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>155100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>76200</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>221100</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>21400</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>122300</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>58300</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>81000</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>107300</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8395,124 +8592,128 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>41800</v>
+      </c>
+      <c r="E83" s="3">
         <v>42500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>40900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>37800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>37100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>34400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>33500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>32000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>30800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>29700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>27700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>26100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>43000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>41000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>42000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>41000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>39500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>39200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>40900</v>
-      </c>
-      <c r="V83" s="3">
-        <v>38300</v>
       </c>
       <c r="W83" s="3">
         <v>38300</v>
       </c>
       <c r="X83" s="3">
+        <v>38300</v>
+      </c>
+      <c r="Y83" s="3">
         <v>38200</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>41000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>31400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>31500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>31700</v>
-      </c>
-      <c r="AC83" s="3">
-        <v>32900</v>
       </c>
       <c r="AD83" s="3">
         <v>32900</v>
       </c>
       <c r="AE83" s="3">
+        <v>32900</v>
+      </c>
+      <c r="AF83" s="3">
         <v>33400</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>31700</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>31100</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>29700</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>31800</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>36000</v>
-      </c>
-      <c r="AK83" s="3">
-        <v>30100</v>
       </c>
       <c r="AL83" s="3">
         <v>30100</v>
       </c>
       <c r="AM83" s="3">
+        <v>30100</v>
+      </c>
+      <c r="AN83" s="3">
         <v>28100</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>24500</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8627,8 +8828,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8743,8 +8947,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8859,8 +9066,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8975,8 +9185,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9091,124 +9304,130 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>369300</v>
+      </c>
+      <c r="E89" s="3">
         <v>272500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>361800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-52800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>324600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>236900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>266700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>69300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-41700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>219300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>269000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-92300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>247000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>304000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>189000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>40000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>344000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>399000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>253100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>223900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>425200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>291500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>343800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>24200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>301400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>310600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>266600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>34500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>308300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>230800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>210900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>43200</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>176600</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>220900</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>228500</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>6100</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>237200</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>105800</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9249,124 +9468,128 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-44800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-49400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-52400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-41700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-58400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-51500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-56700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-51700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-58100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-65800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-76400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-63100</v>
-      </c>
-      <c r="O91" s="3">
-        <v>-71000</v>
       </c>
       <c r="P91" s="3">
         <v>-71000</v>
       </c>
       <c r="Q91" s="3">
+        <v>-71000</v>
+      </c>
+      <c r="R91" s="3">
         <v>-75000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-43000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-49900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-43500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-39000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-28600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-22500</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-33600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-28800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-29200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-28800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-24200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-26600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-27400</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-30900</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-31600</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-33400</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-22300</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-31100</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-33500</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-39700</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-29900</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-28500</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-42800</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9481,8 +9704,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9597,124 +9823,130 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-144500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-353700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-723200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-234500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-33100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-295000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>100800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-231400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>414700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-61100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-181000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>426900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-140000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-62000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-86000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-107000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-565000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-1296100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-752600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-779300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-319500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-390100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-12700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-692800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-27200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-57700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-76700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-290600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-205900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-446800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-279300</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-288700</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>5000</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-76400</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-292000</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-23700</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-194200</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-145100</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9755,8 +9987,9 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9764,115 +9997,118 @@
         <v>56000</v>
       </c>
       <c r="E96" s="3">
+        <v>56000</v>
+      </c>
+      <c r="F96" s="3">
         <v>55300</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>55700</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>55500</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>55600</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>54700</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>54900</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>54500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>54700</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>53600</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>53800</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-53000</v>
-      </c>
-      <c r="P96" s="3">
-        <v>-54000</v>
       </c>
       <c r="Q96" s="3">
         <v>-54000</v>
       </c>
       <c r="R96" s="3">
+        <v>-54000</v>
+      </c>
+      <c r="S96" s="3">
         <v>-56000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-55900</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-56000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-50100</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-51000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-50900</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-49100</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-49000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-49700</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-47200</v>
-      </c>
-      <c r="AB96" s="3">
-        <v>-47100</v>
       </c>
       <c r="AC96" s="3">
         <v>-47100</v>
       </c>
       <c r="AD96" s="3">
+        <v>-47100</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-47000</v>
-      </c>
-      <c r="AE96" s="3">
-        <v>-46900</v>
       </c>
       <c r="AF96" s="3">
         <v>-46900</v>
       </c>
       <c r="AG96" s="3">
+        <v>-46900</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-42400</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-42300</v>
-      </c>
-      <c r="AI96" s="3">
-        <v>-42100</v>
       </c>
       <c r="AJ96" s="3">
         <v>-42100</v>
       </c>
       <c r="AK96" s="3">
+        <v>-42100</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-37600</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-37500</v>
-      </c>
-      <c r="AM96" s="3">
-        <v>-37300</v>
       </c>
       <c r="AN96" s="3">
         <v>-37300</v>
       </c>
+      <c r="AO96" s="3">
+        <v>-37300</v>
+      </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9987,8 +10223,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10103,8 +10342,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10219,352 +10461,364 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-1751500</v>
+      </c>
+      <c r="E100" s="3">
         <v>964900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>335500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>612300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-1509200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>957000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>175000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1932200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1648000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-820000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>171400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>423700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1250000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>385000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-54000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>543000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-507400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>634100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>694200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>1305100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-351800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>83300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>137800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>244600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-503200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>49600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-115400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>124000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-836700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>1197000</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>120500</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>33900</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>63100</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-172600</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>179800</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>57700</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-475400</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>241200</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-17600</v>
+      </c>
+      <c r="E101" s="3">
         <v>5900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-4600</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>5200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-5000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>3100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>1600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>6200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-10600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-8600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>6000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-11000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-8000</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
-      </c>
       <c r="S101" s="3">
+        <v>0</v>
+      </c>
+      <c r="T101" s="3">
         <v>2800</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-5600</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>2000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>800</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>9200</v>
-      </c>
-      <c r="X101" s="3">
-        <v>4400</v>
       </c>
       <c r="Y101" s="3">
         <v>4400</v>
       </c>
       <c r="Z101" s="3">
+        <v>4400</v>
+      </c>
+      <c r="AA101" s="3">
         <v>-11900</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>4000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-3400</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>400</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>2000</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-3900</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-2200</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-2300</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>1000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>600</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>3300</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>3000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>1300</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-4800</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1524200</v>
+      </c>
+      <c r="E102" s="3">
         <v>880300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-13900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>327000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1235300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>904800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>542200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-2098900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>2026200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-666800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>262500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>759900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-1137000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>616000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>41000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>476000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-725500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-268700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>196700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>750600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-236900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-11000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>473400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-436000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-225000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>299000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>74900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-130100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-738200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>978800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>49900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-210600</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>245300</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-24800</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>119300</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>41300</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-437200</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>201500</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/FAF_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FAF_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="92">
   <si>
     <t>FAF</t>
   </si>
@@ -656,334 +656,341 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43738</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42916</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42825</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1838000</v>
+      </c>
+      <c r="E8" s="3">
         <v>2049700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1978900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1841300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1582300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1685100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1406100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1612300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1424600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1429300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1481200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1646900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1446100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1715000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1975000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2139000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2105000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2533100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2555900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2266400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2025700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2151300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1913700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1608700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1412900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1728700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1671200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1498600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1303600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1417100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1542200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1491200</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>1297400</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1481300</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1519600</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>1454400</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>1317000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>1504300</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>1508300</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>680000</v>
+      </c>
+      <c r="E9" s="3">
         <v>718700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>730900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>655400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>595600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>637100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>638500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>571700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>517300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>528800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>622500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>585900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>551300</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q9" s="3" t="s">
         <v>5</v>
       </c>
@@ -1059,50 +1066,53 @@
       <c r="AO9" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AP9" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1158000</v>
+      </c>
+      <c r="E10" s="3">
         <v>1331000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1248000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1185900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>986700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1048000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>767600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1040600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>907300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>900500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>858700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1061000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>894800</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>5</v>
       </c>
@@ -1178,8 +1188,11 @@
       <c r="AO10" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AP10" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1221,8 +1234,9 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1340,8 +1354,11 @@
       <c r="AO12" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AP12" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1459,8 +1476,11 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1500,39 +1520,39 @@
       <c r="O14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>5</v>
+      <c r="R14" s="3">
+        <v>0</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>5</v>
+      <c r="V14" s="3">
+        <v>0</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="X14" s="3">
+      <c r="X14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y14" s="3">
         <v>-18300</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>73300</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AA14" s="3" t="s">
         <v>5</v>
       </c>
@@ -1548,8 +1568,8 @@
       <c r="AE14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
+      <c r="AF14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="AG14" s="3">
         <v>0</v>
@@ -1578,127 +1598,133 @@
       <c r="AO14" s="3">
         <v>0</v>
       </c>
+      <c r="AP14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>54600</v>
+      </c>
+      <c r="E15" s="3">
         <v>55900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>54800</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>53000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>52500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>52000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>53200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>52100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>50100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>49600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>47300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>46100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>45500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>43000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>41000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>42000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>41000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>39500</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>39200</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>40900</v>
-      </c>
-      <c r="W15" s="3">
-        <v>38300</v>
       </c>
       <c r="X15" s="3">
         <v>38300</v>
       </c>
       <c r="Y15" s="3">
+        <v>38300</v>
+      </c>
+      <c r="Z15" s="3">
         <v>38200</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>41000</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>31400</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>31500</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>31700</v>
-      </c>
-      <c r="AD15" s="3">
-        <v>32900</v>
       </c>
       <c r="AE15" s="3">
         <v>32900</v>
       </c>
       <c r="AF15" s="3">
+        <v>32900</v>
+      </c>
+      <c r="AG15" s="3">
         <v>33400</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>31700</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>31100</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>29700</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>31800</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>36000</v>
-      </c>
-      <c r="AL15" s="3">
-        <v>30100</v>
       </c>
       <c r="AM15" s="3">
         <v>30100</v>
       </c>
       <c r="AN15" s="3">
+        <v>30100</v>
+      </c>
+      <c r="AO15" s="3">
         <v>28100</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>24500</v>
       </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1737,246 +1763,253 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1634300</v>
+      </c>
+      <c r="E17" s="3">
         <v>1718400</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1692000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1608100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1450500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1541500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1514300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1425300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1332000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1357600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1447100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1434500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1357400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1597000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1803000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1902000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1884000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2019500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1933500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1850700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1703200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>1753000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1654400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1370000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1328500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1428400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1413600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1257200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1150000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1287200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1335800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1279200</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1195100</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1312800</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1492500</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>1261300</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>1224400</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>1414000</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>1333600</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>203700</v>
+      </c>
+      <c r="E18" s="3">
         <v>331300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>286900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>233200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>131800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>143600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-108200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>187000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>92600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>71700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>34100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>212400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>88700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>118000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>172000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>237000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>221000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>513600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>622400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>415700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>322500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>398300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>259300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>238700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>84400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>300300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>257600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>241400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>153600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>129900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>206400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>212000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>102300</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>168500</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>27100</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>193100</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>92600</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>90300</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>174700</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2018,8 +2051,9 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2059,24 +2093,24 @@
       <c r="O20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P20" s="3">
+      <c r="P20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-30000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-151000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-77000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-71000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-160100</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
         <v>0</v>
       </c>
@@ -2137,484 +2171,499 @@
       <c r="AO20" s="3">
         <v>0</v>
       </c>
+      <c r="AP20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>258300</v>
+      </c>
+      <c r="E21" s="3">
         <v>387200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>341700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>286200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>184300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>195600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-55000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>239100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>142700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>121300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>81400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>258500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>134200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>131000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>62000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>202000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>191000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>393000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>661600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>456600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>360800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>436600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>297600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>279700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>115900</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>331700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>289300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>274300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>186500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>163300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>238100</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>243000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>132000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>200300</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>63100</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>223300</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>122700</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>118400</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>199300</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>41900</v>
+      </c>
+      <c r="E22" s="3">
         <v>43900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>39900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>38000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>35200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>43700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>36200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>35400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>34300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>33300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>35800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>34300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>29100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>30000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>24000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>19000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>20000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>20100</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>19200</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>16200</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>16500</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>15900</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>16000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>13400</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>12100</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>11700</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>12200</v>
-      </c>
-      <c r="AD22" s="3">
-        <v>11900</v>
       </c>
       <c r="AE22" s="3">
         <v>11900</v>
       </c>
       <c r="AF22" s="3">
+        <v>11900</v>
+      </c>
+      <c r="AG22" s="3">
         <v>11000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>10800</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>10000</v>
-      </c>
-      <c r="AI22" s="3">
-        <v>9200</v>
       </c>
       <c r="AJ22" s="3">
         <v>9200</v>
       </c>
       <c r="AK22" s="3">
+        <v>9200</v>
+      </c>
+      <c r="AL22" s="3">
         <v>9100</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>9000</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>8700</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>8800</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>7800</v>
       </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>161800</v>
+      </c>
+      <c r="E23" s="3">
         <v>287400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>247000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>195200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>96600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>99900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-144400</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>151600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>58300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>38400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>178100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>59600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>58000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-3000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>141000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>130000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>333400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>603200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>399400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>306000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>382300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>243400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>225300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>72300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>288500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>245300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>229500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>141700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>118900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>195600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>202000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>93100</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>159300</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>18000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>184200</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>83900</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>81500</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>166900</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>37000</v>
+      </c>
+      <c r="E24" s="3">
         <v>74000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>57100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>48100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>21800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>27000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-41000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>35200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>11600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>4100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>41700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>13600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>4000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-6000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>31000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>32000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>72700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>152700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>96000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>71600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>100900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>59800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>53600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>8500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>63900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>57200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>42200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>31900</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>25700</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>44100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>46900</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>16900</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>52700</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>-3200</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>62300</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>25800</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>500</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>59500</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2732,246 +2781,255 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>124800</v>
+      </c>
+      <c r="E26" s="3">
         <v>213400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>189900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>147100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>74800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>72900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-103400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>116400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>46700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>34300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>136400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>46000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>54000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>3000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>110000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>98000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>260700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>450500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>303400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>234500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>281400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>183600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>171700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>63800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>224600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>188200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>187300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>109800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>93200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>151500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>155100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>76200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>106600</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>21200</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>121900</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>58100</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>81000</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>107400</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>125100</v>
+      </c>
+      <c r="E27" s="3">
         <v>211900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>189600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>146100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>74200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>72400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-104000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>116000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>46700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>34100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>138500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>45900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>54000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>2000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>109000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>98000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>259800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>445300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>302300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>233600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>280300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>182300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>170700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>63200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>224000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>187200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>186700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>109600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>91600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>151500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>155100</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>76200</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>107000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>21400</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>122300</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>58300</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>81000</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>107300</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3089,8 +3147,11 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3172,8 +3233,8 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-      <c r="AD29" s="3" t="s">
-        <v>5</v>
+      <c r="AD29" s="3">
+        <v>0</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>5</v>
@@ -3190,12 +3251,12 @@
       <c r="AI29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AJ29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="AK29" s="3">
         <v>114100</v>
       </c>
-      <c r="AK29" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="AL29" s="3" t="s">
         <v>5</v>
       </c>
@@ -3208,8 +3269,11 @@
       <c r="AO29" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="AP29" s="3" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3327,8 +3391,11 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3446,8 +3513,11 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3487,24 +3557,24 @@
       <c r="O32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P32" s="3">
+      <c r="P32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q32" s="3">
         <v>30000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>151000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>77000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>71000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>160100</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
         <v>0</v>
       </c>
@@ -3565,127 +3635,133 @@
       <c r="AO32" s="3">
         <v>0</v>
       </c>
+      <c r="AP32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>125100</v>
+      </c>
+      <c r="E33" s="3">
         <v>211900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>189600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>146100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>74200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>72400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-104000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>116000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>46700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>34100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>138500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>45900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>54000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>2000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>109000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>98000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>259800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>445300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>302300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>233600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>280300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>182300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>170700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>63200</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>224000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>187200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>186700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>109600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>91600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>151500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>155100</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>76200</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>221100</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>21400</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>122300</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>58300</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>81000</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>107300</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3803,251 +3879,260 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>125100</v>
+      </c>
+      <c r="E35" s="3">
         <v>211900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>189600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>146100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>74200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>72400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-104000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>116000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>46700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>34100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>138500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>45900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>54000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>2000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>109000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>98000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>259800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>445300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>302300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>233600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>280300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>182300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>170700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>63200</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>224000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>187200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>186700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>109600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>91600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>151500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>155100</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>76200</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>221100</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>21400</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>122300</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>58300</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>81000</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>107300</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43738</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42916</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42825</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4089,8 +4174,9 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4132,169 +4218,173 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>2436200</v>
+      </c>
+      <c r="E41" s="3">
         <v>1387300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>2911500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>2031200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>2045100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1718100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>2953400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>2048600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>1506400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3605300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1579100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2245900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1983400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1224000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2361000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1745000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>1704000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1228000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1954000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>2222700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>2026000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1275500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1512400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1523300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1050000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1486000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>1711000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1412000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1337100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1467100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>2205300</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>1226500</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1176600</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1387200</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>1141900</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>1166800</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>1047500</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>1006100</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>1443300</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>81900</v>
+      </c>
+      <c r="E42" s="3">
         <v>78500</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>80000</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>82700</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>62800</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>85400</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>55400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>56400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>77100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>55800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>55300</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>55900</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>53500</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
       <c r="Q42" s="3">
         <v>0</v>
       </c>
@@ -4370,50 +4460,53 @@
       <c r="AO42" s="3">
         <v>0</v>
       </c>
+      <c r="AP42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1645400</v>
+      </c>
+      <c r="E43" s="3">
         <v>1483700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1638000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1414000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1248300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1126100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1429300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1192400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1268200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1221600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1077600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1106900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>980300</v>
       </c>
-      <c r="P43" s="3">
-        <v>0</v>
-      </c>
       <c r="Q43" s="3">
         <v>0</v>
       </c>
@@ -4489,8 +4582,11 @@
       <c r="AO43" s="3">
         <v>0</v>
       </c>
+      <c r="AP43" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4530,8 +4626,8 @@
       <c r="O44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="P44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -4608,8 +4704,11 @@
       <c r="AO44" s="3">
         <v>0</v>
       </c>
+      <c r="AP44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4649,8 +4748,8 @@
       <c r="O45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P45" s="3">
-        <v>0</v>
+      <c r="P45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q45" s="3">
         <v>0</v>
@@ -4727,50 +4826,53 @@
       <c r="AO45" s="3">
         <v>0</v>
       </c>
+      <c r="AP45" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4163500</v>
+      </c>
+      <c r="E46" s="3">
         <v>2949500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4629500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3527900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3356200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>2929600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4438100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3297400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2851700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>4882700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2712000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3408700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3017200</v>
       </c>
-      <c r="P46" s="3">
-        <v>0</v>
-      </c>
       <c r="Q46" s="3">
         <v>0</v>
       </c>
@@ -4846,365 +4948,377 @@
       <c r="AO46" s="3">
         <v>0</v>
       </c>
+      <c r="AP46" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>9679600</v>
+      </c>
+      <c r="E47" s="3">
         <v>9145500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>8826400</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>8625500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>8017200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>7864800</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>7641800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>7696100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>7697500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>7786100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>7837100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>8224800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>8307600</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>9799000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>10234000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>10657000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>11249000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>11613000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>11450200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>9954100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>9253100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>8349200</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>7823500</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>7593200</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>7445500</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>7212300</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>7277700</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>7200600</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>6991800</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>6638500</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>6637000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>6196700</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>5893500</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>5728100</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>5743600</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>5789900</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>5493600</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>5508500</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>5489500</v>
       </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>866900</v>
+      </c>
+      <c r="E48" s="3">
         <v>891900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>902300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>924100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>951000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>966000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>1013100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>996900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>984000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>982100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>967900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>943600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>907000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>885000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>851000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>824000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>766000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>755000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>716200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>705300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>700400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>715000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>714800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>741000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>783900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>738200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>740300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>756400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>767600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>457800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>457500</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>446300</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>435900</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>439600</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>438100</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>433000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>429000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>434100</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>430600</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2600300</v>
+      </c>
+      <c r="E49" s="3">
         <v>2606000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2609200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2612200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2609600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2603400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2613800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2609600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2611100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2613700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2610300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2620700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2634200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1992000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2016000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2023000</v>
-      </c>
-      <c r="S49" s="3">
-        <v>1806000</v>
       </c>
       <c r="T49" s="3">
         <v>1806000</v>
       </c>
       <c r="U49" s="3">
+        <v>1806000</v>
+      </c>
+      <c r="V49" s="3">
         <v>1604900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1556000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1558200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1573100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1552000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1591900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1565500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1242700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1242600</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1246700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1247800</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1253500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1256700</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1271200</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>1229400</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>1212900</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>1220600</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>1109800</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>1095800</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>1096300</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>1066200</v>
       </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5322,8 +5436,11 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5441,52 +5558,55 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>616900</v>
+      </c>
+      <c r="E52" s="3">
         <v>590800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>598800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>540400</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>519600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>466600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>809500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>507200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>503400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>465700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>495800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>478600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>463000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>54000</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>14000</v>
       </c>
       <c r="R52" s="3">
         <v>14000</v>
@@ -5498,7 +5618,7 @@
         <v>14000</v>
       </c>
       <c r="U52" s="3">
-        <v>14500</v>
+        <v>14000</v>
       </c>
       <c r="V52" s="3">
         <v>14500</v>
@@ -5510,10 +5630,10 @@
         <v>14500</v>
       </c>
       <c r="Y52" s="3">
+        <v>14500</v>
+      </c>
+      <c r="Z52" s="3">
         <v>216600</v>
-      </c>
-      <c r="Z52" s="3">
-        <v>18300</v>
       </c>
       <c r="AA52" s="3">
         <v>18300</v>
@@ -5522,7 +5642,7 @@
         <v>18300</v>
       </c>
       <c r="AC52" s="3">
-        <v>16600</v>
+        <v>18300</v>
       </c>
       <c r="AD52" s="3">
         <v>16600</v>
@@ -5534,7 +5654,7 @@
         <v>16600</v>
       </c>
       <c r="AG52" s="3">
-        <v>22800</v>
+        <v>16600</v>
       </c>
       <c r="AH52" s="3">
         <v>22800</v>
@@ -5546,7 +5666,7 @@
         <v>22800</v>
       </c>
       <c r="AK52" s="3">
-        <v>20000</v>
+        <v>22800</v>
       </c>
       <c r="AL52" s="3">
         <v>20000</v>
@@ -5558,10 +5678,13 @@
         <v>20000</v>
       </c>
       <c r="AO52" s="3">
+        <v>20000</v>
+      </c>
+      <c r="AP52" s="3">
         <v>22000</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5679,127 +5802,133 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>17936600</v>
+      </c>
+      <c r="E54" s="3">
         <v>16228800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>17610000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>16273900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>15497400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>14908600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>16566400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>15157300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>14697800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>16802800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>14677600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>15730900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>15383500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>14955000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>16486000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>16262000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>16527000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>16451000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>16686100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>15426900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>14431900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>12796000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>12638800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>12288000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>11675500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>11519200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>11804100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>11443200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>11160300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>10630600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>11380100</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>9959400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>9546800</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>9573200</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>9347000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>9314300</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>8874400</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>8831800</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>9246500</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5841,8 +5970,9 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5884,169 +6014,173 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1958900</v>
+      </c>
+      <c r="E57" s="3">
         <v>1217300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>2126100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>2072900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1911000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1260100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>2127200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2159200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2006600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1345700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2110400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2111900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2035000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>915000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1115000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1015000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1051000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1262000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1252000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1070800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1113400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>979700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>830100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>781500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>664000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>820400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>812500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>709300</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>631500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>778700</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>826700</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>770700</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>709600</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>793200</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>741600</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>697000</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>675800</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>794000</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>813900</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1078600</v>
+      </c>
+      <c r="E58" s="3">
         <v>984400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1078400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>883800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>735800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>643800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>878200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>641500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>688800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>553300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>530400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>585700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>502900</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
@@ -6122,169 +6256,175 @@
       <c r="AO58" s="3">
         <v>0</v>
       </c>
+      <c r="AP58" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>7123000</v>
+      </c>
+      <c r="E59" s="3">
         <v>5528300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>6952600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>6055000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>5698500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>5248400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>6086900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>5633200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>5318500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>7484300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>5621300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>6377900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>6204700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>7124000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>8324000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>7723000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>7346000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>6651000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>7043200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>6920600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>6154000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>4804500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>4918800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>4925200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>4850100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>4748700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>5305000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>5265900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>5344000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>4837900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>5581000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>4326100</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>4187700</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>4104100</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>4079900</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>4208900</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>3926300</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>3815700</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>4302200</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>10160500</v>
+      </c>
+      <c r="E60" s="3">
         <v>8492100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>10157100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>9011700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>8345300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>7855600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>9092300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>8433900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>8013900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>10039100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>8262100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>9075500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>8742600</v>
       </c>
-      <c r="P60" s="3">
-        <v>0</v>
-      </c>
       <c r="Q60" s="3">
         <v>0</v>
       </c>
@@ -6360,127 +6500,133 @@
       <c r="AO60" s="3">
         <v>0</v>
       </c>
+      <c r="AP60" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1751900</v>
+      </c>
+      <c r="E61" s="3">
         <v>1685700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1766900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1769500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1775900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1776500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2089900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1636700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1631400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1640500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1647000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1656500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1659100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2012000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1988000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2075000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2205000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2186000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2242500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1619200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1655000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1526900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1538300</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1489200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1288800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1006600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>961800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>919700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>858600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>808300</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>821800</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>832600</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>731500</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>732800</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>734100</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>734500</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>735500</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>736700</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>737900</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -6520,23 +6666,23 @@
       <c r="O62" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="P62" s="3">
+      <c r="P62" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q62" s="3">
         <v>19000</v>
-      </c>
-      <c r="Q62" s="3">
-        <v>314000</v>
       </c>
       <c r="R62" s="3">
         <v>314000</v>
       </c>
       <c r="S62" s="3">
-        <v>345000</v>
+        <v>314000</v>
       </c>
       <c r="T62" s="3">
         <v>345000</v>
       </c>
       <c r="U62" s="3">
-        <v>291200</v>
+        <v>345000</v>
       </c>
       <c r="V62" s="3">
         <v>291200</v>
@@ -6548,10 +6694,10 @@
         <v>291200</v>
       </c>
       <c r="Y62" s="3">
+        <v>291200</v>
+      </c>
+      <c r="Z62" s="3">
         <v>414400</v>
-      </c>
-      <c r="Z62" s="3">
-        <v>266100</v>
       </c>
       <c r="AA62" s="3">
         <v>266100</v>
@@ -6560,7 +6706,7 @@
         <v>266100</v>
       </c>
       <c r="AC62" s="3">
-        <v>217100</v>
+        <v>266100</v>
       </c>
       <c r="AD62" s="3">
         <v>217100</v>
@@ -6572,7 +6718,7 @@
         <v>217100</v>
       </c>
       <c r="AG62" s="3">
-        <v>219300</v>
+        <v>217100</v>
       </c>
       <c r="AH62" s="3">
         <v>219300</v>
@@ -6584,7 +6730,7 @@
         <v>219300</v>
       </c>
       <c r="AK62" s="3">
-        <v>242200</v>
+        <v>219300</v>
       </c>
       <c r="AL62" s="3">
         <v>242200</v>
@@ -6596,10 +6742,13 @@
         <v>242200</v>
       </c>
       <c r="AO62" s="3">
+        <v>242200</v>
+      </c>
+      <c r="AP62" s="3">
         <v>133100</v>
       </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6717,8 +6866,11 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6836,8 +6988,11 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6955,127 +7110,133 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>12424400</v>
+      </c>
+      <c r="E66" s="3">
         <v>10704500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>12284800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>11124600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>10456500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>9981600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>11455800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>10324700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>9891900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>11940000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>10135600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>10944000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>10604600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>10290000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>11978000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>11346000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>11164000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>10684000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>11088900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>10163100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>9476600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>7886000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>7915000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>7722600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>7316100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>7098700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>7562000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>7358300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>7282200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>6888800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>7705900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>6389900</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>6076300</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>6093300</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>6053200</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>6120900</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>5802000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>5823600</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>6224200</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7117,8 +7278,9 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7236,8 +7398,11 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7355,8 +7520,11 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7474,8 +7642,11 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7593,127 +7764,133 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4079500</v>
+      </c>
+      <c r="E72" s="3">
         <v>4011800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>3857100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3724500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3634800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>3617300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>3601400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>3761900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>3701600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>3710600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>3739000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>3796200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>3712300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>3721000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>3722000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>3775000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>3721000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>3680000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>3476900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>3088600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>2837200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>2655500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>2426900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>2294600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>2173700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>2161000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1985100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>1845900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1707100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>1644200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>1600300</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>1496600</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>1384700</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>1311100</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>1129000</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>1150600</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>1066700</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>1046800</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>1012500</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7831,8 +8008,11 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7950,8 +8130,11 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8069,127 +8252,133 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>5489600</v>
+      </c>
+      <c r="E76" s="3">
         <v>5499500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>5301100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>5126200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>5019300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4908500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>5092200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4813600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4787100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4848100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4527200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4772400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4756500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4665000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4508000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>4916000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>5363000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>5767000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>5597100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>5263700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>4955300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>4910000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>4723800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>4565400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>4359300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>4420500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>4242100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>4084900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>3878000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>3741900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>3674200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>3569500</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>3470500</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>3480000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>3293900</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>3193400</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>3072500</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>3008200</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>3022300</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8307,251 +8496,260 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43738</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42916</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42825</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>125100</v>
+      </c>
+      <c r="E81" s="3">
         <v>211900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>189600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>146100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>74200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>72400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-104000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>116000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>46700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>34100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>138500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>45900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>54000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>2000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>109000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>98000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>259800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>445300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>302300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>233600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>280300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>182300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>170700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>63200</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>224000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>187200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>186700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>109600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>91600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>151500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>155100</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>76200</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>221100</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>21400</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>122300</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>58300</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>81000</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>107300</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8593,127 +8791,131 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>42900</v>
+      </c>
+      <c r="E83" s="3">
         <v>41800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>42500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>40900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>37800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>37100</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>34400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>33500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>32000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>30800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>29700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>27700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>26100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>43000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>41000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>42000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>41000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>39500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>39200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>40900</v>
-      </c>
-      <c r="W83" s="3">
-        <v>38300</v>
       </c>
       <c r="X83" s="3">
         <v>38300</v>
       </c>
       <c r="Y83" s="3">
+        <v>38300</v>
+      </c>
+      <c r="Z83" s="3">
         <v>38200</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>41000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>31400</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>31500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>31700</v>
-      </c>
-      <c r="AD83" s="3">
-        <v>32900</v>
       </c>
       <c r="AE83" s="3">
         <v>32900</v>
       </c>
       <c r="AF83" s="3">
+        <v>32900</v>
+      </c>
+      <c r="AG83" s="3">
         <v>33400</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>31700</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>31100</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>29700</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>31800</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>36000</v>
-      </c>
-      <c r="AL83" s="3">
-        <v>30100</v>
       </c>
       <c r="AM83" s="3">
         <v>30100</v>
       </c>
       <c r="AN83" s="3">
+        <v>30100</v>
+      </c>
+      <c r="AO83" s="3">
         <v>28100</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>24500</v>
       </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8831,8 +9033,11 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8950,8 +9155,11 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9069,8 +9277,11 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9188,8 +9399,11 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9307,127 +9521,133 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E89" s="3">
         <v>369300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>272500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>361800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-52800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>324600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>236900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>266700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>69300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-41700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>219300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>269000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-92300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>247000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>304000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>189000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>40000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>344000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>399000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>253100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>223900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>425200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>291500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>343800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>24200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>301400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>310600</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>266600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>34500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>308300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>230800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>210900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>43200</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>176600</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>220900</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>228500</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>6100</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>237200</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>105800</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9469,127 +9689,131 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-38300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-44800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-49400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-52400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-41700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-58400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-51500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-56700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-51700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-58100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-65800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-76400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-63100</v>
-      </c>
-      <c r="P91" s="3">
-        <v>-71000</v>
       </c>
       <c r="Q91" s="3">
         <v>-71000</v>
       </c>
       <c r="R91" s="3">
+        <v>-71000</v>
+      </c>
+      <c r="S91" s="3">
         <v>-75000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-43000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-49900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-43500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-39000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-28600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-22500</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-33600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-28800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-29200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-28800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-24200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-26600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-27400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-30900</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-31600</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-33400</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-22300</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-31100</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-33500</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-39700</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-29900</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-28500</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-42800</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9707,8 +9931,11 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9826,127 +10053,133 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-815700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-144500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-353700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-723200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-234500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-33100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-295000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>100800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-231400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>414700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-61100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-181000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>426900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-140000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-62000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-86000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-107000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-565000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-1296100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-752600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-779300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-319500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-390100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-12700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-692800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-27200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-57700</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-76700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-290600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-205900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-446800</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-279300</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-288700</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>5000</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-76400</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-292000</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-23700</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-194200</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-145100</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9988,127 +10221,131 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>56000</v>
+        <v>56200</v>
       </c>
       <c r="E96" s="3">
         <v>56000</v>
       </c>
       <c r="F96" s="3">
+        <v>56000</v>
+      </c>
+      <c r="G96" s="3">
         <v>55300</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>55700</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>55500</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>55600</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>54700</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>54900</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>54500</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>54700</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>53600</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>53800</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-53000</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>-54000</v>
       </c>
       <c r="R96" s="3">
         <v>-54000</v>
       </c>
       <c r="S96" s="3">
+        <v>-54000</v>
+      </c>
+      <c r="T96" s="3">
         <v>-56000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-55900</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-56000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-50100</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-51000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-50900</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="Z96" s="3">
         <v>-49100</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AA96" s="3">
         <v>-49000</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AB96" s="3">
         <v>-49700</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-47200</v>
-      </c>
-      <c r="AC96" s="3">
-        <v>-47100</v>
       </c>
       <c r="AD96" s="3">
         <v>-47100</v>
       </c>
       <c r="AE96" s="3">
+        <v>-47100</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-47000</v>
-      </c>
-      <c r="AF96" s="3">
-        <v>-46900</v>
       </c>
       <c r="AG96" s="3">
         <v>-46900</v>
       </c>
       <c r="AH96" s="3">
+        <v>-46900</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-42400</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-42300</v>
-      </c>
-      <c r="AJ96" s="3">
-        <v>-42100</v>
       </c>
       <c r="AK96" s="3">
         <v>-42100</v>
       </c>
       <c r="AL96" s="3">
+        <v>-42100</v>
+      </c>
+      <c r="AM96" s="3">
         <v>-37600</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-37500</v>
-      </c>
-      <c r="AN96" s="3">
-        <v>-37300</v>
       </c>
       <c r="AO96" s="3">
         <v>-37300</v>
       </c>
+      <c r="AP96" s="3">
+        <v>-37300</v>
+      </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10226,8 +10463,11 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10345,8 +10585,11 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10464,361 +10707,373 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1862700</v>
+      </c>
+      <c r="E100" s="3">
         <v>-1751500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>964900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>335500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>612300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-1509200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>957000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>175000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1932200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1648000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-820000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>171400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>423700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1250000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>385000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-54000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>543000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-507400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>634100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>694200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>1305100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-351800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>83300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>137800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>244600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-503200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>49600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-115400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>124000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-836700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>1197000</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>120500</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>33900</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>63100</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-172600</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>179800</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>57700</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-475400</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>241200</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-17600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>5900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-4600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>5200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-5000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>3100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>1600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>6200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-10600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-8600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>6000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-11000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-8000</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
-      </c>
       <c r="T101" s="3">
+        <v>0</v>
+      </c>
+      <c r="U101" s="3">
         <v>2800</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-5600</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>2000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>800</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>9200</v>
-      </c>
-      <c r="Y101" s="3">
-        <v>4400</v>
       </c>
       <c r="Z101" s="3">
         <v>4400</v>
       </c>
       <c r="AA101" s="3">
+        <v>4400</v>
+      </c>
+      <c r="AB101" s="3">
         <v>-11900</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>4000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-3400</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>400</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>2000</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-3900</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-2200</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-2300</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>1000</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>600</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>3300</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>3000</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>1300</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-4800</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1048900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1524200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>880300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-13900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>327000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1235300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>904800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>542200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2098900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2026200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-666800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>262500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>759900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1137000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>616000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>41000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>476000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-725500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-268700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>196700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>750600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-236900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-11000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>473400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-436000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-225000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>299000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>74900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-130100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-738200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>978800</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>49900</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-210600</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>245300</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-24800</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>119300</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>41300</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-437200</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>201500</v>
       </c>
     </row>
